--- a/data/industry_study/generated_revision/top100_fidcs_middle_market.xlsx
+++ b/data/industry_study/generated_revision/top100_fidcs_middle_market.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="R15e678e7de6f4240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 100 FIDCs" sheetId="2" r:id="R377a58c234e741ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="R94c6953f19e74020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 100 FIDCs" sheetId="2" r:id="R7fb71cc8fb0a461f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -89,24 +89,41 @@
     </x:fill>
   </x:fills>
   <x:borders count="4">
-    <x:border/>
     <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
       <x:bottom style="thin">
         <x:color rgb="FF151515"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
       <x:bottom style="thin">
         <x:color rgb="FFD7DADD"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
     <x:border>
+      <x:left/>
+      <x:right/>
       <x:top style="thin">
         <x:color rgb="FFD7DADD"/>
       </x:top>
       <x:bottom style="thin">
         <x:color rgb="FFD7DADD"/>
       </x:bottom>
+      <x:diagonal/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
@@ -505,7 +522,7 @@
     </x:row>
     <x:row r="2" ht="31.5" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>Competência 2026-06. Ranking global por PL ex-FIC, uma linha por CNPJ. O Top 100 recebe duas inclusões documentais de ofertas encerradas em 2026: Citi-Bayer Farmtech e Lavoro Farmtech.</x:v>
+        <x:v>Competência 2026-08. Ranking global por PL ex-FIC, uma linha por CNPJ. O Top 100 recebe duas inclusões documentais de ofertas encerradas em 2026: Citi-Bayer Farmtech e Lavoro Farmtech.</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -528,7 +545,7 @@
         <x:v>PL do Top 100</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>R$ 401,8 bi</x:v>
+        <x:v>R$ 408,8 bi</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
@@ -536,7 +553,7 @@
         <x:v>Participação no PL ex-FIC</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>48,9%</x:v>
+        <x:v>48,4%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
@@ -544,7 +561,7 @@
         <x:v>PL do Top 100 + 2</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>R$ 402,8 bi</x:v>
+        <x:v>R$ 409,7 bi</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
@@ -552,7 +569,7 @@
         <x:v>Participação do Top 100 + 2</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>49,0%</x:v>
+        <x:v>48,5%</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
@@ -682,7 +699,7 @@
     </x:row>
     <x:row r="2" ht="22.5" customHeight="1">
       <x:c r="A2" s="13" t="str">
-        <x:v>Ranking por PL ex-FIC em jun/26, com duas inclusões 2026 explicitamente identificadas. Lacunas permanecem N/D; perfis de devedor não são convertidos em nomes de sacados.</x:v>
+        <x:v>Ranking por PL ex-FIC em Ago/26, com duas inclusões documentais explicitamente identificadas. Lacunas permanecem N/D; perfis de devedor não são convertidos em nomes de sacados.</x:v>
       </x:c>
       <x:c r="B2" s="13"/>
       <x:c r="C2" s="13"/>
@@ -867,16 +884,16 @@
         <x:v>09.195.235/0001-50</x:v>
       </x:c>
       <x:c r="F5" s="22" t="str">
-        <x:v>FIDC DO SISTEMA PETROBRAS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DO SISTEMA PETROBRAS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G5" s="43" t="n">
-        <x:v>61254971563.01</x:v>
+        <x:v>58815322507.62</x:v>
       </x:c>
       <x:c r="H5" s="49" t="n">
-        <x:v>0.07457735374951541</x:v>
+        <x:v>0.06965301206862962</x:v>
       </x:c>
       <x:c r="I5" s="49" t="n">
-        <x:v>0.0015158049175739</x:v>
+        <x:v>0.0012711173696075</x:v>
       </x:c>
       <x:c r="J5" s="49" t="str">
         <x:v>N/D</x:v>
@@ -995,10 +1012,10 @@
         <x:v>TAPSO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G6" s="44" t="n">
-        <x:v>41496046291.59</x:v>
+        <x:v>33455157284.84</x:v>
       </x:c>
       <x:c r="H6" s="50" t="n">
-        <x:v>0.05052104742732339</x:v>
+        <x:v>0.03961981971308513</x:v>
       </x:c>
       <x:c r="I6" s="50" t="n">
         <x:v>1</x:v>
@@ -1120,10 +1137,10 @@
         <x:v>PAN AUTO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G7" s="45" t="n">
-        <x:v>17971763062.82</x:v>
+        <x:v>20198291907.77</x:v>
       </x:c>
       <x:c r="H7" s="51" t="n">
-        <x:v>0.021880453083872778</x:v>
+        <x:v>0.023920159067993482</x:v>
       </x:c>
       <x:c r="I7" s="51" t="n">
         <x:v>0</x:v>
@@ -1236,22 +1253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D8" s="38" t="n">
-        <x:v>62393679000183</x:v>
+        <x:v>63953619000130</x:v>
       </x:c>
       <x:c r="E8" s="24" t="str">
-        <x:v>62.393.679/0001-83</x:v>
+        <x:v>63.953.619/0001-30</x:v>
       </x:c>
       <x:c r="F8" s="24" t="str">
-        <x:v>CLOUDWALK BELA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO</x:v>
+        <x:v>CLASSE CONSIGNADO PRIVADO DO MT GLOBAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G8" s="44" t="n">
-        <x:v>10010957003.11</x:v>
+        <x:v>10699481597.570002</x:v>
       </x:c>
       <x:c r="H8" s="50" t="n">
-        <x:v>0.012188246320939709</x:v>
+        <x:v>0.012671036884088674</x:v>
       </x:c>
       <x:c r="I8" s="50" t="n">
-        <x:v>0.1553594542690687</x:v>
+        <x:v>0.0326072904035432</x:v>
       </x:c>
       <x:c r="J8" s="50" t="str">
         <x:v>N/D</x:v>
@@ -1290,55 +1307,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V8" s="24" t="str">
-        <x:v>CloudWalk Instituição de Pagamento.</x:v>
+        <x:v>Parati Crédito, Financiamento e Investimento S.A., como originadora e endossante das CCBs.</x:v>
       </x:c>
       <x:c r="W8" s="24" t="str">
-        <x:v>Emissores e instituições de pagamento responsáveis pela liquidação das transações capturadas no sistema CloudWalk.</x:v>
+        <x:v>Pessoas físicas empregadas por empresas privadas, devedoras dos empréstimos consignados.</x:v>
       </x:c>
       <x:c r="X8" s="24" t="str">
-        <x:v>Valores devidos pelos emissores à CloudWalk, como credenciadora, decorrentes de transações de cartão realizadas por estabelecimentos.</x:v>
+        <x:v>Parcelas de CCBs de empréstimo consignado privado, processadas na infraestrutura Dataprev e Caixa prevista no regulamento.</x:v>
       </x:c>
       <x:c r="Y8" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z8" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA8" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB8" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC8" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD8" s="24" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
-      </x:c>
-      <x:c r="AE8" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE8" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF8" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG8" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH8" s="24" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a estrutura econômica documental é de meios de pagamento.</x:v>
+        <x:v>O regulamento declara Tipo Financeiro e Foco Créditos Consignados para a Classe Consignado Privado.</x:v>
       </x:c>
       <x:c r="AI8" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62393679000183</x:v>
+        <x:v>FundosNet, Regulamento id 1222855 de 02/06/2026, páginas 3 e 15; deliberação id 1087883 de 08/01/2026.</x:v>
       </x:c>
       <x:c r="AJ8" s="24" t="str">
-        <x:v>1117954;1166893;993253</x:v>
+        <x:v>1222855;1087883</x:v>
       </x:c>
       <x:c r="AK8" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL8" s="24" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>p. 87 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM8" s="24" t="str">
         <x:v>N/D</x:v>
@@ -1361,22 +1378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D9" s="39" t="n">
-        <x:v>63953619000130</x:v>
+        <x:v>62393679000183</x:v>
       </x:c>
       <x:c r="E9" s="23" t="str">
-        <x:v>63.953.619/0001-30</x:v>
+        <x:v>62.393.679/0001-83</x:v>
       </x:c>
       <x:c r="F9" s="23" t="str">
-        <x:v>CLASSE CONSIGNADO PRIVADO DO MT GLOBAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESP LIMITADA</x:v>
+        <x:v>CLOUDWALK BELA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO</x:v>
       </x:c>
       <x:c r="G9" s="45" t="n">
-        <x:v>9407708295.27</x:v>
+        <x:v>10070614364.8</x:v>
       </x:c>
       <x:c r="H9" s="51" t="n">
-        <x:v>0.011453796673252841</x:v>
+        <x:v>0.011926290530822998</x:v>
       </x:c>
       <x:c r="I9" s="51" t="n">
-        <x:v>0.0134833710631275</x:v>
+        <x:v>0.1603537622701268</x:v>
       </x:c>
       <x:c r="J9" s="51" t="str">
         <x:v>N/D</x:v>
@@ -1415,55 +1432,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V9" s="23" t="str">
-        <x:v>Parati Crédito, Financiamento e Investimento S.A., como originadora e endossante das CCBs.</x:v>
+        <x:v>CloudWalk Instituição de Pagamento.</x:v>
       </x:c>
       <x:c r="W9" s="23" t="str">
-        <x:v>Pessoas físicas empregadas por empresas privadas, devedoras dos empréstimos consignados.</x:v>
+        <x:v>Emissores e instituições de pagamento responsáveis pela liquidação das transações capturadas no sistema CloudWalk.</x:v>
       </x:c>
       <x:c r="X9" s="23" t="str">
-        <x:v>Parcelas de CCBs de empréstimo consignado privado, processadas na infraestrutura Dataprev e Caixa prevista no regulamento.</x:v>
+        <x:v>Valores devidos pelos emissores à CloudWalk, como credenciadora, decorrentes de transações de cartão realizadas por estabelecimentos.</x:v>
       </x:c>
       <x:c r="Y9" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z9" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA9" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB9" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC9" s="23" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD9" s="23" t="str">
-        <x:v>Consignado/INSS</x:v>
-      </x:c>
-      <x:c r="AE9" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
+      </x:c>
+      <x:c r="AE9" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF9" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG9" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH9" s="23" t="str">
-        <x:v>O regulamento declara Tipo Financeiro e Foco Créditos Consignados para a Classe Consignado Privado.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a estrutura econômica documental é de meios de pagamento.</x:v>
       </x:c>
       <x:c r="AI9" s="23" t="str">
-        <x:v>FundosNet, Regulamento id 1222855 de 02/06/2026, páginas 3 e 15; deliberação id 1087883 de 08/01/2026.</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62393679000183</x:v>
       </x:c>
       <x:c r="AJ9" s="23" t="str">
-        <x:v>1222855;1087883</x:v>
+        <x:v>1117954;1166893;993253</x:v>
       </x:c>
       <x:c r="AK9" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL9" s="23" t="str">
-        <x:v>p. 87 — política/definição do lastro</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM9" s="23" t="str">
         <x:v>N/D</x:v>
@@ -1495,10 +1512,10 @@
         <x:v>ITAÚ CRÉDITO PRIVADO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G10" s="44" t="n">
-        <x:v>8719298749.48</x:v>
+        <x:v>8932735715.03</x:v>
       </x:c>
       <x:c r="H10" s="50" t="n">
-        <x:v>0.010615664503554363</x:v>
+        <x:v>0.010578739043456804</x:v>
       </x:c>
       <x:c r="I10" s="50" t="n">
         <x:v>0</x:v>
@@ -1620,10 +1637,10 @@
         <x:v>BTG PACTUAL CONSIGNADOS II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G11" s="45" t="n">
-        <x:v>8032044361.07</x:v>
+        <x:v>8239227134.05</x:v>
       </x:c>
       <x:c r="H11" s="51" t="n">
-        <x:v>0.009778938727139018</x:v>
+        <x:v>0.009757440111457582</x:v>
       </x:c>
       <x:c r="I11" s="51" t="n">
         <x:v>0</x:v>
@@ -1745,13 +1762,13 @@
         <x:v>AETOS ENERGIA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G12" s="44" t="n">
-        <x:v>7350884666.57</x:v>
+        <x:v>7959831126.05</x:v>
       </x:c>
       <x:c r="H12" s="50" t="n">
-        <x:v>0.008949633183434965</x:v>
+        <x:v>0.009426560798254298</x:v>
       </x:c>
       <x:c r="I12" s="50" t="n">
-        <x:v>0.1184810115182402</x:v>
+        <x:v>0.1110477241038992</x:v>
       </x:c>
       <x:c r="J12" s="50" t="str">
         <x:v>N/D</x:v>
@@ -1861,22 +1878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D13" s="39" t="n">
-        <x:v>26286939000158</x:v>
+        <x:v>28169275000172</x:v>
       </x:c>
       <x:c r="E13" s="23" t="str">
-        <x:v>26.286.939/0001-58</x:v>
+        <x:v>28.169.275/0001-72</x:v>
       </x:c>
       <x:c r="F13" s="23" t="str">
-        <x:v>CIELO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS PAGSEGURO I</x:v>
       </x:c>
       <x:c r="G13" s="45" t="n">
-        <x:v>6479950762.42</x:v>
+        <x:v>7174237038.23</x:v>
       </x:c>
       <x:c r="H13" s="51" t="n">
-        <x:v>0.007889279318191094</x:v>
+        <x:v>0.008496208091731584</x:v>
       </x:c>
       <x:c r="I13" s="51" t="n">
-        <x:v>0.8414931267075925</x:v>
+        <x:v>0.7364651414444897</x:v>
       </x:c>
       <x:c r="J13" s="51" t="str">
         <x:v>N/D</x:v>
@@ -1915,19 +1932,19 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V13" s="23" t="str">
-        <x:v>Estabelecimentos credenciados à Cielo.</x:v>
+        <x:v>Estabelecimentos credenciados ao sistema PagSeguro.</x:v>
       </x:c>
       <x:c r="W13" s="23" t="str">
-        <x:v>Cielo, como adquirente e devedora dos recebíveis cedidos pelos estabelecimentos.</x:v>
+        <x:v>PagSeguro, como devedor dos valores de liquidação devidos aos estabelecimentos.</x:v>
       </x:c>
       <x:c r="X13" s="23" t="str">
-        <x:v>Valores de liquidação de transações de pagamento/unidades de recebíveis processadas no Sistema Cielo.</x:v>
+        <x:v>Unidades/recebíveis de transações de pagamento a débito e crédito, à vista ou parceladas, capturadas e liquidadas pelo sistema PagSeguro.</x:v>
       </x:c>
       <x:c r="Y13" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z13" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA13" s="23" t="str">
         <x:v>Financeiro</x:v>
@@ -1939,7 +1956,7 @@
         <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD13" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="AE13" s="27" t="b">
         <x:v>0</x:v>
@@ -1951,13 +1968,13 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH13" s="23" t="str">
-        <x:v>O cadastro ANBIMA traz Financeiro/Multicarteira Financeiro; a estrutura documental é de meios de pagamento.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a estrutura econômica documental é de meios de pagamento.</x:v>
       </x:c>
       <x:c r="AI13" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26286939000158</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=28169275000172</x:v>
       </x:c>
       <x:c r="AJ13" s="23" t="str">
-        <x:v>1017493;1026980</x:v>
+        <x:v>1149521;1148251;773514</x:v>
       </x:c>
       <x:c r="AK13" s="23" t="str">
         <x:v>N/D</x:v>
@@ -1986,22 +2003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D14" s="38" t="n">
-        <x:v>53216449000158</x:v>
+        <x:v>26286939000158</x:v>
       </x:c>
       <x:c r="E14" s="24" t="str">
-        <x:v>53.216.449/0001-58</x:v>
+        <x:v>26.286.939/0001-58</x:v>
       </x:c>
       <x:c r="F14" s="24" t="str">
-        <x:v>RIO VERMELHO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADO</x:v>
+        <x:v>CIELO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G14" s="44" t="n">
-        <x:v>6390451812.87</x:v>
+        <x:v>6705565454.97</x:v>
       </x:c>
       <x:c r="H14" s="50" t="n">
-        <x:v>0.0077803151859665845</x:v>
+        <x:v>0.007941176068557636</x:v>
       </x:c>
       <x:c r="I14" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.84310494226191</x:v>
       </x:c>
       <x:c r="J14" s="50" t="str">
         <x:v>N/D</x:v>
@@ -2040,31 +2057,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V14" s="24" t="str">
-        <x:v>Pessoas físicas, jurídicas ou fundos que transfiram os direitos; nomes não identificados no regulamento.</x:v>
+        <x:v>Estabelecimentos credenciados à Cielo.</x:v>
       </x:c>
       <x:c r="W14" s="24" t="str">
-        <x:v>Entes públicos e demais pessoas físicas/jurídicas devedoras dos direitos adquiridos.</x:v>
+        <x:v>Cielo, como adquirente e devedora dos recebíveis cedidos pelos estabelecimentos.</x:v>
       </x:c>
       <x:c r="X14" s="24" t="str">
-        <x:v>Precatórios e créditos públicos; créditos vencidos; direitos litigiosos, penhorados, futuros e outros não padronizados permitidos.</x:v>
+        <x:v>Valores de liquidação de transações de pagamento/unidades de recebíveis processadas no Sistema Cielo.</x:v>
       </x:c>
       <x:c r="Y14" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z14" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA14" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB14" s="24" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC14" s="24" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD14" s="24" t="str">
-        <x:v>Não padronizado/NPL</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="AE14" s="26" t="b">
         <x:v>0</x:v>
@@ -2076,19 +2093,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH14" s="24" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental permite NPL e precatórios.</x:v>
+        <x:v>O cadastro ANBIMA traz Financeiro/Multicarteira Financeiro; a estrutura documental é de meios de pagamento.</x:v>
       </x:c>
       <x:c r="AI14" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53216449000158</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26286939000158</x:v>
       </x:c>
       <x:c r="AJ14" s="24" t="str">
-        <x:v>880741;587879</x:v>
+        <x:v>1017493;1026980</x:v>
       </x:c>
       <x:c r="AK14" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL14" s="24" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM14" s="24" t="str">
         <x:v>N/D</x:v>
@@ -2111,22 +2128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D15" s="39" t="n">
-        <x:v>28169275000172</x:v>
+        <x:v>42922136000107</x:v>
       </x:c>
       <x:c r="E15" s="23" t="str">
-        <x:v>28.169.275/0001-72</x:v>
+        <x:v>42.922.136/0001-07</x:v>
       </x:c>
       <x:c r="F15" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS PAGSEGURO I</x:v>
+        <x:v>MAREE I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO FINANCEIRO - RL</x:v>
       </x:c>
       <x:c r="G15" s="45" t="n">
-        <x:v>6234652185.61</x:v>
+        <x:v>6476101048.84</x:v>
       </x:c>
       <x:c r="H15" s="51" t="n">
-        <x:v>0.0075906306000508164</x:v>
+        <x:v>0.007669429075290311</x:v>
       </x:c>
       <x:c r="I15" s="51" t="n">
-        <x:v>0.6324501415323651</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="51" t="str">
         <x:v>N/D</x:v>
@@ -2165,13 +2182,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V15" s="23" t="str">
-        <x:v>Estabelecimentos credenciados ao sistema PagSeguro.</x:v>
+        <x:v>SHPP Brasil Instituição de Pagamento e Serviços de Pagamentos Ltda. — CNPJ 38.372.267/0001-82 — atua como originadora/correspondente; CCB são endossadas por instituições financeiras parceiras e recebíveis de pagamento são cedidos por estabelecimentos.</x:v>
       </x:c>
       <x:c r="W15" s="23" t="str">
-        <x:v>PagSeguro, como devedor dos valores de liquidação devidos aos estabelecimentos.</x:v>
+        <x:v>Pessoas físicas ou jurídicas tomadoras dos empréstimos e participantes das operações de pagamento, conforme o ativo.</x:v>
       </x:c>
       <x:c r="X15" s="23" t="str">
-        <x:v>Unidades/recebíveis de transações de pagamento a débito e crédito, à vista ou parceladas, capturadas e liquidadas pelo sistema PagSeguro.</x:v>
+        <x:v>CCB de empréstimos e unidades de recebíveis de transações de cartão realizadas em estabelecimentos.</x:v>
       </x:c>
       <x:c r="Y15" s="23" t="str">
         <x:v>Outros</x:v>
@@ -2183,37 +2200,37 @@
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB15" s="23" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC15" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD15" s="23" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
-      </x:c>
-      <x:c r="AE15" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Crédito PF parcelado / BNPL</x:v>
+      </x:c>
+      <x:c r="AE15" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF15" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG15" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH15" s="23" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a estrutura econômica documental é de meios de pagamento.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental combina crédito pessoal e meios de pagamento.</x:v>
       </x:c>
       <x:c r="AI15" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=28169275000172</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=42922136000107</x:v>
       </x:c>
       <x:c r="AJ15" s="23" t="str">
-        <x:v>1149521;1148251;773514</x:v>
+        <x:v>1159092</x:v>
       </x:c>
       <x:c r="AK15" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL15" s="23" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM15" s="23" t="str">
         <x:v>N/D</x:v>
@@ -2236,109 +2253,109 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D16" s="38" t="n">
-        <x:v>50906397000153</x:v>
+        <x:v>55720253000121</x:v>
       </x:c>
       <x:c r="E16" s="24" t="str">
-        <x:v>50.906.397/0001-53</x:v>
+        <x:v>55.720.253/0001-21</x:v>
       </x:c>
       <x:c r="F16" s="24" t="str">
-        <x:v>BTG PACTUAL CONSIGNADOS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>ITAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS RESPONSABILIDADE ILIMITADA</x:v>
       </x:c>
       <x:c r="G16" s="44" t="n">
-        <x:v>6007175688.48</x:v>
+        <x:v>6460522602.03</x:v>
       </x:c>
       <x:c r="H16" s="50" t="n">
-        <x:v>0.007313680096878776</x:v>
+        <x:v>0.007650980043687587</x:v>
       </x:c>
       <x:c r="I16" s="50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="50" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="K16" s="50" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="L16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="M16" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="N16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="O16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="P16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="Q16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="R16" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="S16" s="32" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="T16" s="32" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="U16" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="V16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="W16" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="X16" s="24" t="str">
+        <x:v>Precatórios/direitos judiciais</x:v>
+      </x:c>
+      <x:c r="Y16" s="24" t="str">
+        <x:v>Outros</x:v>
+      </x:c>
+      <x:c r="Z16" s="24" t="str">
+        <x:v>Multicarteira Outros</x:v>
+      </x:c>
+      <x:c r="AA16" s="24" t="str">
+        <x:v>Outros</x:v>
+      </x:c>
+      <x:c r="AB16" s="24" t="str">
+        <x:v>Poder Público</x:v>
+      </x:c>
+      <x:c r="AC16" s="24" t="str">
+        <x:v>Judicial/Precatórios/NPL</x:v>
+      </x:c>
+      <x:c r="AD16" s="24" t="str">
+        <x:v>Precatórios/direitos judiciais</x:v>
+      </x:c>
+      <x:c r="AE16" s="26" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J16" s="50" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="K16" s="50" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="L16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="M16" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="N16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="O16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="P16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="Q16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="R16" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="S16" s="32" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="T16" s="32" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="U16" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="V16" s="24" t="str">
-        <x:v>Instituições financeiras que concedam as CCB; nomes individuais não identificados no regulamento.</x:v>
-      </x:c>
-      <x:c r="W16" s="24" t="str">
-        <x:v>Pessoas físicas, incluindo beneficiários de INSS e trabalhadores com saldo de FGTS.</x:v>
-      </x:c>
-      <x:c r="X16" s="24" t="str">
-        <x:v>Parcelas vincendas de CCB de empréstimo pessoal com garantia do saque-aniversário FGTS ou consignação processada pela Dataprev.</x:v>
-      </x:c>
-      <x:c r="Y16" s="24" t="str">
-        <x:v>Financeiro</x:v>
-      </x:c>
-      <x:c r="Z16" s="24" t="str">
-        <x:v>Crédito Pessoal</x:v>
-      </x:c>
-      <x:c r="AA16" s="24" t="str">
-        <x:v>Financeiro</x:v>
-      </x:c>
-      <x:c r="AB16" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
-      </x:c>
-      <x:c r="AC16" s="24" t="str">
-        <x:v>Crédito PF</x:v>
-      </x:c>
-      <x:c r="AD16" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
-      </x:c>
-      <x:c r="AE16" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
       <x:c r="AF16" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG16" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH16" s="24" t="str">
-        <x:v>A leitura documental é compatível com Financeiro/Crédito Pessoal, com foco contratual mais específico.</x:v>
+        <x:v>Sem trecho citável no corpus consultado.</x:v>
       </x:c>
       <x:c r="AI16" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=50906397000153</x:v>
+        <x:v>FundosNet e CVM SRE consultados em 2026-07-24; documento primário não localizado</x:v>
       </x:c>
       <x:c r="AJ16" s="24" t="str">
-        <x:v>939418;483282</x:v>
+        <x:v>Nenhum documento primário localizado.</x:v>
       </x:c>
       <x:c r="AK16" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL16" s="24" t="str">
-        <x:v>p. 7 — política/definição do lastro</x:v>
+        <x:v>regulamento 1198083 p. 27</x:v>
       </x:c>
       <x:c r="AM16" s="24" t="str">
         <x:v>N/D</x:v>
@@ -2347,7 +2364,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO16" s="24" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
@@ -2361,19 +2378,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D17" s="39" t="n">
-        <x:v>29225241000110</x:v>
+        <x:v>53216449000158</x:v>
       </x:c>
       <x:c r="E17" s="23" t="str">
-        <x:v>29.225.241/0001-10</x:v>
+        <x:v>53.216.449/0001-58</x:v>
       </x:c>
       <x:c r="F17" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ALTERNATIVE ASSETS III RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>RIO VERMELHO FUNDO DE INVESTIMENTO EM PARTICIPAÇÕES MULTIESTRATÉGIA</x:v>
       </x:c>
       <x:c r="G17" s="45" t="n">
-        <x:v>5861437942.62</x:v>
+        <x:v>6390290390.09</x:v>
       </x:c>
       <x:c r="H17" s="51" t="n">
-        <x:v>0.00713624575725986</x:v>
+        <x:v>0.007567806392718836</x:v>
       </x:c>
       <x:c r="I17" s="51" t="n">
         <x:v>0</x:v>
@@ -2415,13 +2432,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V17" s="23" t="str">
-        <x:v>Pessoas jurídicas ou fundos que transfiram os direitos; nomes não identificados no regulamento.</x:v>
+        <x:v>Pessoas físicas, jurídicas ou fundos que transfiram os direitos; nomes não identificados no regulamento.</x:v>
       </x:c>
       <x:c r="W17" s="23" t="str">
-        <x:v>Pessoas físicas ou jurídicas, privadas ou públicas, obrigadas nos direitos adquiridos.</x:v>
+        <x:v>Entes públicos e demais pessoas físicas/jurídicas devedoras dos direitos adquiridos.</x:v>
       </x:c>
       <x:c r="X17" s="23" t="str">
-        <x:v>Créditos em litígio, precatórios e direitos vencidos/inadimplidos já performados.</x:v>
+        <x:v>Precatórios e créditos públicos; créditos vencidos; direitos litigiosos, penhorados, futuros e outros não padronizados permitidos.</x:v>
       </x:c>
       <x:c r="Y17" s="23" t="str">
         <x:v>Outros</x:v>
@@ -2433,13 +2450,13 @@
         <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB17" s="23" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC17" s="23" t="str">
         <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD17" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>Não padronizado/NPL</x:v>
       </x:c>
       <x:c r="AE17" s="27" t="b">
         <x:v>0</x:v>
@@ -2451,13 +2468,13 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH17" s="23" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental é de NPL/direitos judiciais.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental permite NPL e precatórios.</x:v>
       </x:c>
       <x:c r="AI17" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=29225241000110</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53216449000158</x:v>
       </x:c>
       <x:c r="AJ17" s="23" t="str">
-        <x:v>784984</x:v>
+        <x:v>880741;587879</x:v>
       </x:c>
       <x:c r="AK17" s="23" t="str">
         <x:v>N/D</x:v>
@@ -2486,22 +2503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D18" s="38" t="n">
-        <x:v>42922136000107</x:v>
+        <x:v>50906397000153</x:v>
       </x:c>
       <x:c r="E18" s="24" t="str">
-        <x:v>42.922.136/0001-07</x:v>
+        <x:v>50.906.397/0001-53</x:v>
       </x:c>
       <x:c r="F18" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MONEE I DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>BTG PACTUAL CONSIGNADOS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G18" s="44" t="n">
-        <x:v>5751418460.99</x:v>
+        <x:v>6111960853.79</x:v>
       </x:c>
       <x:c r="H18" s="50" t="n">
-        <x:v>0.007002298069562074</x:v>
+        <x:v>0.007238190066149372</x:v>
       </x:c>
       <x:c r="I18" s="50" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="50" t="str">
         <x:v>N/D</x:v>
@@ -2540,31 +2557,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V18" s="24" t="str">
-        <x:v>SHPP Brasil Instituição de Pagamento e Serviços de Pagamentos Ltda. — CNPJ 38.372.267/0001-82 — atua como originadora/correspondente; CCB são endossadas por instituições financeiras parceiras e recebíveis de pagamento são cedidos por estabelecimentos.</x:v>
+        <x:v>Instituições financeiras que concedam as CCB; nomes individuais não identificados no regulamento.</x:v>
       </x:c>
       <x:c r="W18" s="24" t="str">
-        <x:v>Pessoas físicas ou jurídicas tomadoras dos empréstimos e participantes das operações de pagamento, conforme o ativo.</x:v>
+        <x:v>Pessoas físicas, incluindo beneficiários de INSS e trabalhadores com saldo de FGTS.</x:v>
       </x:c>
       <x:c r="X18" s="24" t="str">
-        <x:v>CCB de empréstimos e unidades de recebíveis de transações de cartão realizadas em estabelecimentos.</x:v>
+        <x:v>Parcelas vincendas de CCB de empréstimo pessoal com garantia do saque-aniversário FGTS ou consignação processada pela Dataprev.</x:v>
       </x:c>
       <x:c r="Y18" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z18" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA18" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB18" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC18" s="24" t="str">
         <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD18" s="24" t="str">
-        <x:v>Crédito PF parcelado / BNPL</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="AE18" s="24" t="str">
         <x:v>N/D</x:v>
@@ -2576,19 +2593,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH18" s="24" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental combina crédito pessoal e meios de pagamento.</x:v>
+        <x:v>A leitura documental é compatível com Financeiro/Crédito Pessoal, com foco contratual mais específico.</x:v>
       </x:c>
       <x:c r="AI18" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=42922136000107</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=50906397000153</x:v>
       </x:c>
       <x:c r="AJ18" s="24" t="str">
-        <x:v>1159092</x:v>
+        <x:v>939418;483282</x:v>
       </x:c>
       <x:c r="AK18" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL18" s="24" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>p. 7 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM18" s="24" t="str">
         <x:v>N/D</x:v>
@@ -2611,22 +2628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D19" s="39" t="n">
-        <x:v>32527650000186</x:v>
+        <x:v>29225241000110</x:v>
       </x:c>
       <x:c r="E19" s="23" t="str">
-        <x:v>32.527.650/0001-86</x:v>
+        <x:v>29.225.241/0001-10</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS PICPAY I</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ALTERNATIVE ASSETS III RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G19" s="45" t="n">
-        <x:v>4762640671.11</x:v>
+        <x:v>5933688515.09</x:v>
       </x:c>
       <x:c r="H19" s="51" t="n">
-        <x:v>0.005798470377964967</x:v>
+        <x:v>0.0070270681198680235</x:v>
       </x:c>
       <x:c r="I19" s="51" t="n">
-        <x:v>0.1032942874088393</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J19" s="51" t="str">
         <x:v>N/D</x:v>
@@ -2665,31 +2682,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V19" s="23" t="str">
-        <x:v>Usuários finais do PicPay que transferem seus recebíveis à classe por mandato previsto no regulamento.</x:v>
+        <x:v>Pessoas jurídicas ou fundos que transfiram os direitos; nomes não identificados no regulamento.</x:v>
       </x:c>
       <x:c r="W19" s="23" t="str">
-        <x:v>PicPay, responsável pelos pagamentos devidos aos cedentes nas transações abrangidas.</x:v>
+        <x:v>Pessoas físicas ou jurídicas, privadas ou públicas, obrigadas nos direitos adquiridos.</x:v>
       </x:c>
       <x:c r="X19" s="23" t="str">
-        <x:v>Valores de transações de pagamento, cash-in e moeda eletrônica processados no sistema PicPay.</x:v>
+        <x:v>Créditos em litígio, precatórios e direitos vencidos/inadimplidos já performados.</x:v>
       </x:c>
       <x:c r="Y19" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z19" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA19" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB19" s="23" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Poder Público</x:v>
       </x:c>
       <x:c r="AC19" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD19" s="23" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="AE19" s="27" t="b">
         <x:v>0</x:v>
@@ -2701,19 +2718,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH19" s="23" t="str">
-        <x:v>O cadastro ANBIMA traz Financeiro/Multicarteira Financeiro; a estrutura documental é de meios de pagamento.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental é de NPL/direitos judiciais.</x:v>
       </x:c>
       <x:c r="AI19" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=32527650000186</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=29225241000110</x:v>
       </x:c>
       <x:c r="AJ19" s="23" t="str">
-        <x:v>1203914</x:v>
+        <x:v>784984</x:v>
       </x:c>
       <x:c r="AK19" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL19" s="23" t="str">
-        <x:v>p. 13 — política/definição do lastro</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM19" s="23" t="str">
         <x:v>N/D</x:v>
@@ -2736,22 +2753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D20" s="38" t="n">
-        <x:v>61285603000171</x:v>
+        <x:v>68522464000100</x:v>
       </x:c>
       <x:c r="E20" s="24" t="str">
-        <x:v>61.285.603/0001-71</x:v>
+        <x:v>68.522.464/0001-00</x:v>
       </x:c>
       <x:c r="F20" s="24" t="str">
-        <x:v>MAROBÁ FUNDO DE INVESTMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>TAPSO IV FUNDO DE INVESTIMENTOS EM DIREITOS CREDITÓRIOS RESPOSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G20" s="44" t="n">
-        <x:v>4467343585.25</x:v>
+        <x:v>4985976955.36</x:v>
       </x:c>
       <x:c r="H20" s="50" t="n">
-        <x:v>0.0054389489436805875</x:v>
+        <x:v>0.005904725133499101</x:v>
       </x:c>
       <x:c r="I20" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="50" t="str">
         <x:v>N/D</x:v>
@@ -2790,46 +2807,46 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V20" s="24" t="str">
-        <x:v>Itaú BBA</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W20" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X20" s="24" t="str">
-        <x:v>Multicarteira financeiro</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y20" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z20" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA20" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB20" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC20" s="24" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD20" s="24" t="str">
-        <x:v>Multicarteira financeiro</x:v>
-      </x:c>
-      <x:c r="AE20" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE20" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF20" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG20" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH20" s="24" t="str">
-        <x:v>Classificação cadastral ANBIMA disponível; documentação primária da operação não localizada.</x:v>
+        <x:v>Sem trecho citável no corpus consultado.</x:v>
       </x:c>
       <x:c r="AI20" s="24" t="str">
-        <x:v>FundosNet e CVM SRE consultados em 24/07/2026; regulamento, suplemento e informe de encerramento não foram localizados no corpus acessível.</x:v>
+        <x:v>FundosNet e CVM SRE consultados em 2026-07-24; documento primário não localizado</x:v>
       </x:c>
       <x:c r="AJ20" s="24" t="str">
         <x:v>Nenhum documento primário localizado.</x:v>
@@ -2838,7 +2855,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL20" s="24" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM20" s="24" t="str">
         <x:v>N/D</x:v>
@@ -2847,7 +2864,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO20" s="24" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="36" customHeight="1">
@@ -2861,22 +2878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D21" s="39" t="n">
-        <x:v>21126275000146</x:v>
+        <x:v>32527650000186</x:v>
       </x:c>
       <x:c r="E21" s="23" t="str">
-        <x:v>21.126.275/0001-46</x:v>
+        <x:v>32.527.650/0001-86</x:v>
       </x:c>
       <x:c r="F21" s="23" t="str">
-        <x:v>VENDA DE VEÍCULOS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS PICPAY I</x:v>
       </x:c>
       <x:c r="G21" s="45" t="n">
-        <x:v>4242510733.6</x:v>
+        <x:v>4670319122.88</x:v>
       </x:c>
       <x:c r="H21" s="51" t="n">
-        <x:v>0.00516521705410218</x:v>
+        <x:v>0.005530902158840782</x:v>
       </x:c>
       <x:c r="I21" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1272759196611239</x:v>
       </x:c>
       <x:c r="J21" s="51" t="str">
         <x:v>N/D</x:v>
@@ -2915,31 +2932,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V21" s="23" t="str">
-        <x:v>Nissan do Brasil Automóveis Ltda. e Renault do Brasil Ltda.</x:v>
+        <x:v>Usuários finais do PicPay que transferem seus recebíveis à classe por mandato previsto no regulamento.</x:v>
       </x:c>
       <x:c r="W21" s="23" t="str">
-        <x:v>Locadoras de veículos e concessionárias que compram veículos novos com pagamento diferido.</x:v>
+        <x:v>PicPay, responsável pelos pagamentos devidos aos cedentes nas transações abrangidas.</x:v>
       </x:c>
       <x:c r="X21" s="23" t="str">
-        <x:v>Direitos creditórios decorrentes da venda direta e da venda a prazo de veículos novos.</x:v>
+        <x:v>Valores de transações de pagamento, cash-in e moeda eletrônica processados no sistema PicPay.</x:v>
       </x:c>
       <x:c r="Y21" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z21" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA21" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB21" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC21" s="23" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD21" s="23" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="AE21" s="27" t="b">
         <x:v>0</x:v>
@@ -2951,19 +2968,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH21" s="23" t="str">
-        <x:v>O regulamento identifica cedentes, devedores, natureza econômica e garantias da carteira.</x:v>
+        <x:v>O cadastro ANBIMA traz Financeiro/Multicarteira Financeiro; a estrutura documental é de meios de pagamento.</x:v>
       </x:c>
       <x:c r="AI21" s="23" t="str">
-        <x:v>FundosNet, Regulamento id 1230588, 26/06/2026.</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=32527650000186</x:v>
       </x:c>
       <x:c r="AJ21" s="23" t="str">
-        <x:v>1230588</x:v>
+        <x:v>1203914</x:v>
       </x:c>
       <x:c r="AK21" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL21" s="23" t="str">
-        <x:v>p. 77 — política/definição do lastro</x:v>
+        <x:v>p. 13 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM21" s="23" t="str">
         <x:v>N/D</x:v>
@@ -2986,22 +3003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D22" s="38" t="n">
-        <x:v>34197588000137</x:v>
+        <x:v>61285603000171</x:v>
       </x:c>
       <x:c r="E22" s="24" t="str">
-        <x:v>34.197.588/0001-37</x:v>
+        <x:v>61.285.603/0001-71</x:v>
       </x:c>
       <x:c r="F22" s="24" t="str">
-        <x:v>DAY MAXX 2 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>MAROBÁ FUNDO DE INVESTMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G22" s="44" t="n">
-        <x:v>4015059128.44</x:v>
+        <x:v>4584487367.37</x:v>
       </x:c>
       <x:c r="H22" s="50" t="n">
-        <x:v>0.004888296856670308</x:v>
+        <x:v>0.005429254492084638</x:v>
       </x:c>
       <x:c r="I22" s="50" t="n">
-        <x:v>0.6338991217168864</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J22" s="50" t="str">
         <x:v>N/D</x:v>
@@ -3040,13 +3057,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V22" s="24" t="str">
-        <x:v>Pessoas físicas ou jurídicas que cedam os direitos; nomes não identificados no regulamento.</x:v>
+        <x:v>Itaú BBA</x:v>
       </x:c>
       <x:c r="W22" s="24" t="str">
-        <x:v>Pessoas físicas, jurídicas e entes públicos, conforme os direitos adquiridos.</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="X22" s="24" t="str">
-        <x:v>A política permite títulos de crédito; recebíveis mercantis, de transporte, industriais e de serviços; contratos futuros; precatórios federais; direitos não padronizados; créditos de cedentes em recuperação judicial; e até 100% do PL em cotas de outros FIDC, inclusive mezanino/júnior.</x:v>
+        <x:v>Multicarteira financeiro</x:v>
       </x:c>
       <x:c r="Y22" s="24" t="str">
         <x:v>Outros</x:v>
@@ -3055,34 +3072,34 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA22" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB22" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC22" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD22" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE22" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira financeiro</x:v>
+      </x:c>
+      <x:c r="AE22" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF22" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG22" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH22" s="24" t="str">
-        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental é ampla e inclui NPL/precatórios.</x:v>
+        <x:v>Classificação cadastral ANBIMA disponível; documentação primária da operação não localizada.</x:v>
       </x:c>
       <x:c r="AI22" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=34197588000137</x:v>
+        <x:v>FundosNet e CVM SRE consultados em 24/07/2026; regulamento, suplemento e informe de encerramento não foram localizados no corpus acessível.</x:v>
       </x:c>
       <x:c r="AJ22" s="24" t="str">
-        <x:v>974471</x:v>
+        <x:v>Nenhum documento primário localizado.</x:v>
       </x:c>
       <x:c r="AK22" s="24" t="str">
         <x:v>N/D</x:v>
@@ -3111,22 +3128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D23" s="39" t="n">
-        <x:v>54979779000168</x:v>
+        <x:v>49826785000145</x:v>
       </x:c>
       <x:c r="E23" s="23" t="str">
-        <x:v>54.979.779/0001-68</x:v>
+        <x:v>49.826.785/0001-45</x:v>
       </x:c>
       <x:c r="F23" s="23" t="str">
-        <x:v>FIDC ACR BEM BANCOS EMISSORES DE CARTÃO DE CRÉDITO - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>ASA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G23" s="45" t="n">
-        <x:v>3677016076.94</x:v>
+        <x:v>4231296076.69</x:v>
       </x:c>
       <x:c r="H23" s="51" t="n">
-        <x:v>0.004476732609867116</x:v>
+        <x:v>0.0050109819028442805</x:v>
       </x:c>
       <x:c r="I23" s="51" t="n">
-        <x:v>0.0301696997603437</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="51" t="str">
         <x:v>N/D</x:v>
@@ -3165,31 +3182,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V23" s="23" t="str">
-        <x:v>Stone Instituição de Pagamento S.A., como originadora e cedente dos recebíveis.</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W23" s="23" t="str">
-        <x:v>Emissores de cartões e demais instituições financeiras responsáveis pela liquidação das transações.</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="X23" s="23" t="str">
-        <x:v>Direitos creditórios oriundos de transações de pagamento processadas no sistema Stone.</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y23" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z23" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA23" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB23" s="23" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC23" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD23" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE23" s="27" t="b">
         <x:v>0</x:v>
@@ -3201,19 +3218,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH23" s="23" t="str">
-        <x:v>A documentação identifica a cadeia de pagamentos, os emissores de cartão como devedores e as ofertas encerradas.</x:v>
+        <x:v>Sem trecho citável no corpus consultado.</x:v>
       </x:c>
       <x:c r="AI23" s="23" t="str">
-        <x:v>FundosNet, Regulamento id 656484 de 09/05/2024 e Informe de Encerramento id 664301 de 15/05/2024.</x:v>
+        <x:v>FundosNet e CVM SRE consultados em 2026-07-24; documento primário não localizado</x:v>
       </x:c>
       <x:c r="AJ23" s="23" t="str">
-        <x:v>656484;664301</x:v>
+        <x:v>Nenhum documento primário localizado.</x:v>
       </x:c>
       <x:c r="AK23" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL23" s="23" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>p. 45 — política de investimento</x:v>
       </x:c>
       <x:c r="AM23" s="23" t="str">
         <x:v>N/D</x:v>
@@ -3222,7 +3239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO23" s="23" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="36" customHeight="1">
@@ -3236,22 +3253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D24" s="38" t="n">
-        <x:v>12817329000129</x:v>
+        <x:v>34197588000137</x:v>
       </x:c>
       <x:c r="E24" s="24" t="str">
-        <x:v>12.817.329/0001-29</x:v>
+        <x:v>34.197.588/0001-37</x:v>
       </x:c>
       <x:c r="F24" s="24" t="str">
-        <x:v>HAVAN FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO ECONÔMICO, FINANCEIRO E COMERCIAL</x:v>
+        <x:v>DAY MAXX 2 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G24" s="44" t="n">
-        <x:v>3666009327</x:v>
+        <x:v>3772944315.34</x:v>
       </x:c>
       <x:c r="H24" s="50" t="n">
-        <x:v>0.004463331994978846</x:v>
+        <x:v>0.004468171298331265</x:v>
       </x:c>
       <x:c r="I24" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.7056380854286087</x:v>
       </x:c>
       <x:c r="J24" s="50" t="str">
         <x:v>N/D</x:v>
@@ -3290,13 +3307,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V24" s="24" t="str">
-        <x:v>Havan</x:v>
+        <x:v>Pessoas físicas ou jurídicas que cedam os direitos; nomes não identificados no regulamento.</x:v>
       </x:c>
       <x:c r="W24" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Pessoas físicas, jurídicas e entes públicos, conforme os direitos adquiridos.</x:v>
       </x:c>
       <x:c r="X24" s="24" t="str">
-        <x:v>Multicarteira financeiro</x:v>
+        <x:v>A política permite títulos de crédito; recebíveis mercantis, de transporte, industriais e de serviços; contratos futuros; precatórios federais; direitos não padronizados; créditos de cedentes em recuperação judicial; e até 100% do PL em cotas de outros FIDC, inclusive mezanino/júnior.</x:v>
       </x:c>
       <x:c r="Y24" s="24" t="str">
         <x:v>Outros</x:v>
@@ -3305,34 +3322,34 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA24" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB24" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC24" s="24" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD24" s="24" t="str">
-        <x:v>Multicarteira financeiro</x:v>
-      </x:c>
-      <x:c r="AE24" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE24" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF24" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG24" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH24" s="24" t="str">
-        <x:v>Sem trecho citável no corpus consultado.</x:v>
+        <x:v>O cadastro ANBIMA traz Outros/Multicarteira Outros; a política documental é ampla e inclui NPL/precatórios.</x:v>
       </x:c>
       <x:c r="AI24" s="24" t="str">
-        <x:v>FundosNet e CVM SRE consultados em 2026-07-24; documento primário não localizado</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=34197588000137</x:v>
       </x:c>
       <x:c r="AJ24" s="24" t="str">
-        <x:v>Nenhum documento primário localizado.</x:v>
+        <x:v>974471</x:v>
       </x:c>
       <x:c r="AK24" s="24" t="str">
         <x:v>N/D</x:v>
@@ -3361,22 +3378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D25" s="39" t="n">
-        <x:v>50473039000102</x:v>
+        <x:v>54979779000168</x:v>
       </x:c>
       <x:c r="E25" s="23" t="str">
-        <x:v>50.473.039/0001-02</x:v>
+        <x:v>54.979.779/0001-68</x:v>
       </x:c>
       <x:c r="F25" s="23" t="str">
-        <x:v>SELLER FIDC SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FIDC ACR BEM BANCOS EMISSORES DE CARTÃO DE CRÉDITO - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G25" s="45" t="n">
-        <x:v>3656448188.16</x:v>
+        <x:v>3771058923.75</x:v>
       </x:c>
       <x:c r="H25" s="51" t="n">
-        <x:v>0.004451691398055452</x:v>
+        <x:v>0.004465938492362117</x:v>
       </x:c>
       <x:c r="I25" s="51" t="n">
-        <x:v>0.5133697454647598</x:v>
+        <x:v>0.0303918848813086</x:v>
       </x:c>
       <x:c r="J25" s="51" t="str">
         <x:v>N/D</x:v>
@@ -3415,19 +3432,19 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V25" s="23" t="str">
-        <x:v>Mercado Pago (originador) | Mercado Livre (cedente)</x:v>
+        <x:v>Stone</x:v>
       </x:c>
       <x:c r="W25" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X25" s="23" t="str">
-        <x:v>recebíveis com risco Grupo Mercado Livre</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="Y25" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z25" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA25" s="23" t="str">
         <x:v>Financeiro</x:v>
@@ -3439,7 +3456,7 @@
         <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD25" s="23" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="AE25" s="27" t="b">
         <x:v>0</x:v>
@@ -3451,7 +3468,7 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH25" s="23" t="str">
-        <x:v>Há recebíveis cedidos por lojistas e recebíveis de pagamento originados ou cedidos pelo Mercado Crédito.</x:v>
+        <x:v>O – DEFINICOES DA PARTE GERAL DO REGULAMENTO ........................................................................ 22 ANEXO I - DESCRITIVO DA CLASSE DO FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS ACR BEM BANCOS EMISSORES DE CARTAO DE CREDITO – RESPONSABILIDADE LIMITADA ............................................. 26 CAPITULO I - DA CLASSE, FORMA DE CONSTITUIC AO, PRAZO DE DURACAO E OBJETO .................................................................................................. 26 CAPITULO II - DO OBJETIVO DA CLASSE, DA POLITICA DE INVESTIMENTO E DA COMPOSICAO DA CARTEIRA ................................................................ 27 CAPITULO III - DAS CONDICOES DE CESSAO E DOS CRITERIOS DE ELEGIBILIDADE ......................</x:v>
       </x:c>
       <x:c r="AI25" s="23" t="str">
         <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
@@ -3486,19 +3503,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D26" s="38" t="n">
-        <x:v>29301202000155</x:v>
+        <x:v>66737102000100</x:v>
       </x:c>
       <x:c r="E26" s="24" t="str">
-        <x:v>29.301.202/0001-55</x:v>
+        <x:v>66.737.102/0001-00</x:v>
       </x:c>
       <x:c r="F26" s="24" t="str">
-        <x:v>RSCRED MULTIESTRÉGIA - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
+        <x:v>PAN CONSIGNADO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G26" s="44" t="n">
-        <x:v>3599850973.43</x:v>
+        <x:v>3765650088.95</x:v>
       </x:c>
       <x:c r="H26" s="50" t="n">
-        <x:v>0.004382784819594067</x:v>
+        <x:v>0.0044595329908781655</x:v>
       </x:c>
       <x:c r="I26" s="50" t="n">
         <x:v>1</x:v>
@@ -3540,55 +3557,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V26" s="24" t="str">
-        <x:v>Cedentes dos direitos judiciais contra o INCRA</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W26" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X26" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y26" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z26" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA26" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB26" s="24" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC26" s="24" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD26" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
-      </x:c>
-      <x:c r="AE26" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE26" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF26" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG26" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH26" s="24" t="str">
-        <x:v>O regulamento admite extensa lista de instrumentos, origens e setores. A leitura integral da cláusula sustenta Multicarteira Outros.</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI26" s="24" t="str">
-        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=66737102000100</x:v>
       </x:c>
       <x:c r="AJ26" s="24" t="str">
-        <x:v>Regulamento ids 762766 e 762773</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK26" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL26" s="24" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM26" s="24" t="str">
         <x:v>N/D</x:v>
@@ -3597,7 +3614,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO26" s="24" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="36" customHeight="1">
@@ -3611,19 +3628,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D27" s="39" t="n">
-        <x:v>48349509000170</x:v>
+        <x:v>12817329000129</x:v>
       </x:c>
       <x:c r="E27" s="23" t="str">
-        <x:v>48.349.509/0001-70</x:v>
+        <x:v>12.817.329/0001-29</x:v>
       </x:c>
       <x:c r="F27" s="23" t="str">
-        <x:v>OCCAM CRÉDITO CORPORATIVO 30 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>HAVAN FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO ECONÔMICO, FINANCEIRO E COMERCIAL</x:v>
       </x:c>
       <x:c r="G27" s="45" t="n">
-        <x:v>3470655083.68</x:v>
+        <x:v>3686239660.81</x:v>
       </x:c>
       <x:c r="H27" s="51" t="n">
-        <x:v>0.004225490034746146</x:v>
+        <x:v>0.0043654898865681645</x:v>
       </x:c>
       <x:c r="I27" s="51" t="n">
         <x:v>0</x:v>
@@ -3665,13 +3682,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V27" s="23" t="str">
-        <x:v>Múltiplos emissores e fundos investidos</x:v>
+        <x:v>Havan</x:v>
       </x:c>
       <x:c r="W27" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X27" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Multicarteira financeiro</x:v>
       </x:c>
       <x:c r="Y27" s="23" t="str">
         <x:v>Outros</x:v>
@@ -3680,40 +3697,40 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA27" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB27" s="23" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC27" s="23" t="str">
         <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD27" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE27" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Multicarteira financeiro</x:v>
+      </x:c>
+      <x:c r="AE27" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF27" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG27" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH27" s="23" t="str">
-        <x:v>Regulamento sem texto recuperável; proposta baseada na classificação ANBIMA preservada de 2025-12-29.</x:v>
+        <x:v>O regulamento reúne vendas varejistas à vista e parceladas, CCBs de renegociação, recebíveis de cartão e créditos contra devedores especiais de adquirência.</x:v>
       </x:c>
       <x:c r="AI27" s="23" t="str">
-        <x:v>Comentário explícito do usuário — tarefa de reclassificação</x:v>
+        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
       </x:c>
       <x:c r="AJ27" s="23" t="str">
-        <x:v>chat_task_reclassification_2026_07_31</x:v>
+        <x:v>IMG_8592</x:v>
       </x:c>
       <x:c r="AK27" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL27" s="23" t="str">
-        <x:v>Lista de mudanças aprovadas</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM27" s="23" t="str">
         <x:v>N/D</x:v>
@@ -3736,22 +3753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D28" s="38" t="n">
-        <x:v>17250006000110</x:v>
+        <x:v>48349509000170</x:v>
       </x:c>
       <x:c r="E28" s="24" t="str">
-        <x:v>17.250.006/0001-10</x:v>
+        <x:v>48.349.509/0001-70</x:v>
       </x:c>
       <x:c r="F28" s="24" t="str">
-        <x:v>RED FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS REAL LP DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>OCCAM CRÉDITO CORPORATIVO 30 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G28" s="44" t="n">
-        <x:v>3394314559.41</x:v>
+        <x:v>3658919018.85</x:v>
       </x:c>
       <x:c r="H28" s="50" t="n">
-        <x:v>0.00413254616196921</x:v>
+        <x:v>0.0043331349674241605</x:v>
       </x:c>
       <x:c r="I28" s="50" t="n">
-        <x:v>0.4787782384680989</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="50" t="str">
         <x:v>N/D</x:v>
@@ -3790,13 +3807,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V28" s="24" t="str">
-        <x:v>Múltiplos cedentes</x:v>
+        <x:v>Múltiplos emissores e fundos investidos</x:v>
       </x:c>
       <x:c r="W28" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X28" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y28" s="24" t="str">
         <x:v>Outros</x:v>
@@ -3805,40 +3822,40 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA28" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB28" s="24" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Crédito Corporativo</x:v>
       </x:c>
       <x:c r="AC28" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD28" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE28" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira outros</x:v>
+      </x:c>
+      <x:c r="AE28" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF28" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG28" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH28" s="24" t="str">
-        <x:v>A FINALIDADE DE REALIZAR A GESTAO DE CAIXA E DE LIQUIDEZ DO FUNDO. ARTIGO 39. O FUNDO ADQUIRIRA OS DIREITOS CREDITORIOS, DEVIDAMENTE REPRESENTADOS PELOS DOCUMENTOS COMPROBATORIOS, DECORRENTES DOS SEGMENTOS COMERCIAL, INDUSTRIAL, FINANCEIR O E DE PRESTACAO DE SERVICOS, QUE ATENDAM AOS CRITERIOS DE ELEGIBILIDADE E AS CONDICOES DE CESSAO. PARAGRAFO PRIMEIRO. OS DIREITOS CREDITORIOS PODERAO SER ADQUIRIDOS (I) DE FORMA PRIMARIA ; OU (II) EM MERCADO SECUNDARIO. PARAGRAFO SEGUNDO. OS DIREITOS CREDITORIOS SERAO ADQUIRIDOS PELO FUNDO JUNTAMENTE COM TODOS OS DIREITOS, PRIVILEGIOS, PREFERENCIAS, PRERROGATIVAS E ACOES ASSEGURADOS AOS SEUS TITULARES, NOS TERMOS DOS CONTRATOS DE CESSAO. PARAGRAFO TERCEIRO. NOS TERMOS DOS ARTIGOS 42, CAPUT E §1O, E 30, §5O, DO ANEXO NORMATIVO II A RESOLUCAO CVM 175, OBSERVADAS AS NORMAS QU</x:v>
+        <x:v>Regulamento sem texto recuperável; proposta baseada na classificação ANBIMA preservada de 2025-12-29.</x:v>
       </x:c>
       <x:c r="AI28" s="24" t="str">
-        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
+        <x:v>Comentário explícito do usuário — tarefa de reclassificação</x:v>
       </x:c>
       <x:c r="AJ28" s="24" t="str">
-        <x:v>Regulamento arquivado no FundosNET</x:v>
+        <x:v>chat_task_reclassification_2026_07_31</x:v>
       </x:c>
       <x:c r="AK28" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL28" s="24" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>Lista de mudanças aprovadas</x:v>
       </x:c>
       <x:c r="AM28" s="24" t="str">
         <x:v>N/D</x:v>
@@ -3861,19 +3878,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D29" s="39" t="n">
-        <x:v>49826785000145</x:v>
+        <x:v>29301202000155</x:v>
       </x:c>
       <x:c r="E29" s="23" t="str">
-        <x:v>49.826.785/0001-45</x:v>
+        <x:v>29.301.202/0001-55</x:v>
       </x:c>
       <x:c r="F29" s="23" t="str">
-        <x:v>ASA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>RSCRED MULTIESTRÉGIA - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
       </x:c>
       <x:c r="G29" s="45" t="n">
-        <x:v>3364983017.12</x:v>
+        <x:v>3599560973.43</x:v>
       </x:c>
       <x:c r="H29" s="51" t="n">
-        <x:v>0.004096835284148786</x:v>
+        <x:v>0.004262839226829116</x:v>
       </x:c>
       <x:c r="I29" s="51" t="n">
         <x:v>1</x:v>
@@ -3915,13 +3932,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V29" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Cedentes dos direitos judiciais contra o INCRA</x:v>
       </x:c>
       <x:c r="W29" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X29" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="Y29" s="23" t="str">
         <x:v>Outros</x:v>
@@ -3933,37 +3950,37 @@
         <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB29" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC29" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD29" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE29" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
+      </x:c>
+      <x:c r="AE29" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF29" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG29" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH29" s="23" t="str">
-        <x:v>O regulamento admite carteira ampla, incluindo créditos judiciais e precatórios, CCBs e outros instrumentos. Nenhuma família isolada representa o mandato completo.</x:v>
+        <x:v>O regulamento admite extensa lista de instrumentos, origens e setores. A leitura integral da cláusula sustenta Multicarteira Outros.</x:v>
       </x:c>
       <x:c r="AI29" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 1072129</x:v>
+        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
       </x:c>
       <x:c r="AJ29" s="23" t="str">
-        <x:v>1072129</x:v>
+        <x:v>Regulamento ids 762766 e 762773</x:v>
       </x:c>
       <x:c r="AK29" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL29" s="23" t="str">
-        <x:v>p. 45 — política de investimento</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM29" s="23" t="str">
         <x:v>N/D</x:v>
@@ -3972,7 +3989,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO29" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="36" customHeight="1">
@@ -3986,22 +4003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D30" s="38" t="n">
-        <x:v>60356171000180</x:v>
+        <x:v>62393829000159</x:v>
       </x:c>
       <x:c r="E30" s="24" t="str">
-        <x:v>60.356.171/0001-80</x:v>
+        <x:v>62.393.829/0001-59</x:v>
       </x:c>
       <x:c r="F30" s="24" t="str">
-        <x:v>CLOUDWALK PI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS COMERCIAIS MEDICI I - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G30" s="44" t="n">
-        <x:v>3254537202.75</x:v>
+        <x:v>3389462172.19</x:v>
       </x:c>
       <x:c r="H30" s="50" t="n">
-        <x:v>0.003962368540335967</x:v>
+        <x:v>0.004014026269347188</x:v>
       </x:c>
       <x:c r="I30" s="50" t="n">
-        <x:v>0.1612463408977896</x:v>
+        <x:v>0.0534980276932435</x:v>
       </x:c>
       <x:c r="J30" s="50" t="str">
         <x:v>N/D</x:v>
@@ -4040,55 +4057,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V30" s="24" t="str">
-        <x:v>Cloudwalk</x:v>
+        <x:v>Multicedente</x:v>
       </x:c>
       <x:c r="W30" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>BRF</x:v>
       </x:c>
       <x:c r="X30" s="24" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>Risco Sacado BRF</x:v>
       </x:c>
       <x:c r="Y30" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z30" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA30" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB30" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Crédito Corporativo</x:v>
       </x:c>
       <x:c r="AC30" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD30" s="24" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
-      </x:c>
-      <x:c r="AE30" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE30" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF30" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG30" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH30" s="24" t="str">
-        <x:v>A CloudWalk é definida como cedente dos recebíveis de transações de pagamento devidos pelos emissores.</x:v>
+        <x:v>INVESTIMENTO, DIVERSIFICACAO E COMPOSICAO DA CARTEIRA PREVISTAS NESTE CAPITULO SERAO OBSERVADAS DIARIAMENTE, COM BASE NO PATRIMONIO LIQUIDO DO DIA UTIL IMEDIATAMENTE ANTERIOR. 9. DIREITOS CREDITORIOS CARACTERISTICAS DOS DIREITOS CREDITORIOS OS DIREITOS CREDITORIOS A SEREM ADQUIRIDOS PELA CLASSE SAO DIREITOS CREDITORIOS PERFORMADOS, DECORRENTES DE OPERACOES DE COMPRA E VENDA DE PRODUTOS E PRESTACAO DE SERVICOS PELOS CEDENTES AS DEVEDORAS, REALIZADAS NO SEGMENTO COMERCIAL, BEM COMO RECEBIVEIS DE CARTAO DE CREDITO 9.1.1. A CLASSE NAO PODERA ADQUIRIR DIREITOS CREDITORIOS NAO PADRONIZADOS E/OU NAO PERFORMADOS, CUJA EXIGIBILIDADE AINDA DEPENDA DA CONTRAPRESTACAO PELOS RESPECTIVOS CEDENTES. 9.1.2. OS TERMOS DE CESSAO A SER EM FIRMADOS NA CESSAO DOS RECEBIVEIS DE CARTOES DE CREDITO COM CADA UMA DAS CREDENCIADORAS DEVERAO SER APRESENTADOS AOS COTISTAS SENIORES DE CADA SERIE INDIVIDUALMENTE ANTES DA FORMALIZACAO COM CADA CREDENC</x:v>
       </x:c>
       <x:c r="AI30" s="24" t="str">
-        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62393829000159</x:v>
       </x:c>
       <x:c r="AJ30" s="24" t="str">
-        <x:v>chat_task_acquiring_2026_07_31</x:v>
+        <x:v>Regulamento id 1231073 e correlatos</x:v>
       </x:c>
       <x:c r="AK30" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL30" s="24" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>p. 48 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM30" s="24" t="str">
         <x:v>N/D</x:v>
@@ -4111,19 +4128,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D31" s="39" t="n">
-        <x:v>7727002000126</x:v>
+        <x:v>21126275000146</x:v>
       </x:c>
       <x:c r="E31" s="23" t="str">
-        <x:v>07.727.002/0001-26</x:v>
+        <x:v>21.126.275/0001-46</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
-        <x:v>FIDC PCG - BRASIL MULTICARTEIRA</x:v>
+        <x:v>VENDA DE VEÍCULOS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G31" s="45" t="n">
-        <x:v>3140454721.87</x:v>
+        <x:v>3371226156.53</x:v>
       </x:c>
       <x:c r="H31" s="51" t="n">
-        <x:v>0.0038234741891328425</x:v>
+        <x:v>0.003992429968167592</x:v>
       </x:c>
       <x:c r="I31" s="51" t="n">
         <x:v>0</x:v>
@@ -4165,31 +4182,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V31" s="23" t="str">
-        <x:v>Múltiplos cedentes</x:v>
+        <x:v>Nissan, Renault e Geely (RCI)</x:v>
       </x:c>
       <x:c r="W31" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X31" s="23" t="str">
-        <x:v>Não padronizado/NPL</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="Y31" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z31" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AA31" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB31" s="23" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC31" s="23" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD31" s="23" t="str">
-        <x:v>Não padronizado/NPL</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="AE31" s="27" t="b">
         <x:v>0</x:v>
@@ -4201,19 +4218,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH31" s="23" t="str">
-        <x:v>RSIFICACAO; E (C) AVALIAR A ADERENCIA DO RISCO DE PERFORMANCE DOS DIREITOS DE CREDITO, SE HOUVER, A POLITICA DE INVESTIMENTO, OBSERVADO QUE O CUSTODIANTE PODERA SER SUBCONTRATADO PELO GESTOR PARA DESEMPENHAR AS FUNCOES INDICADAS NOS ITENS (A) A (C); (IX) ENTREGAR OS DIREITOS DE CREDITO AO CUSTODIANTE OU ADMINISTRADOR, CONFORME O CASO, NOS TERMOS DESTE ANEXO , POR MEIO DO ENVIO, PELO GESTOR AO CUSTODIANTE, DOS DOCUMENTOS COMPROBATORIOS DE CREDITO, DE FORMA ELETRONICA OU ENTREGA DAS VIAS FISICAS DOS REFERIDOS DOCUMENTOS; (X) NA HIPOTESE DE OCORRER SUBSTITUICAO DE DIREITOS DE CREDITO, POR QUALQUER MOTIVO, DILIGENCIAR PARA QUE A RELACAO ENTRE RISCO E RETORNO DA CARTEIRA DE DIREITOS DE CREDITO NAO SEJA ALTERADA, NOS TERMOS DA POLITICA DE INVESTIMENTOS; (XI) ATUAR PARA QUE OCORRA A CORRETA FORMALIZACAO DOS DOCUMENT</x:v>
+        <x:v>ARIA, NA QUALIDADE DE REPRESENTANTE DAS PARTES GARANTIDAS (CONFORME DEFINIDO NOS RESPECTIVOS INSTRUMENTOS DE GARANTIA, CONFORME APLICAVEL). DIFERENTEMENTE DO OCORRIDO EM RELACAO A ALIENACAO FIDUCIARIA DE VEICULOS, OS VEICULOS OBJETO DO PENHOR MERCANTIL DE ESTOQUE NAO SAO CONSIDERADOS DE FORMA INDIVIDUALIZADA, MAS SIM COMO PECA INTEGRANTE DO ESTOQUE, O QUE PODE DIFICULTAR A CAPACIDADE D A CLASSE DE APREENDER TAIS VEICULOS DADOS EM GARANTIA, EM CASO DE INADIMPLEMENTO PELO RESPECTIVO DEVEDOR VN PD. NAO OBSTANTE A PREVISAO DE VISTORIAS NO ESTOQUE PELAS A SER REALIZADA PELO AGENTE DE COBRANCA EXTRAORDINARIA, E POSSIVEL QUE, EM EVENTUAL EXECUCAO DE UM DEVEDOR VN PD INADIMPLENTE, OS VEICULOS, OBJETO DO PENHOR MERCANTIL DE ESTOQUE, NAO SEJAM E</x:v>
       </x:c>
       <x:c r="AI31" s="23" t="str">
-        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=21126275000146</x:v>
       </x:c>
       <x:c r="AJ31" s="23" t="str">
-        <x:v>IMG_8592</x:v>
+        <x:v>Regulamento id 1159092 e correlatos</x:v>
       </x:c>
       <x:c r="AK31" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL31" s="23" t="str">
-        <x:v>Linha do FIDC na imagem</x:v>
+        <x:v>p. 77 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM31" s="23" t="str">
         <x:v>N/D</x:v>
@@ -4236,22 +4253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D32" s="38" t="n">
-        <x:v>62393829000159</x:v>
+        <x:v>17250006000110</x:v>
       </x:c>
       <x:c r="E32" s="24" t="str">
-        <x:v>62.393.829/0001-59</x:v>
+        <x:v>17.250.006/0001-10</x:v>
       </x:c>
       <x:c r="F32" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS COMERCIAIS MEDICI I - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>RED FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS REAL LP DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G32" s="44" t="n">
-        <x:v>3091715187.97</x:v>
+        <x:v>3334605706.65</x:v>
       </x:c>
       <x:c r="H32" s="50" t="n">
-        <x:v>0.0037641342634337866</x:v>
+        <x:v>0.003949061598690066</x:v>
       </x:c>
       <x:c r="I32" s="50" t="n">
-        <x:v>0.0545912971158512</x:v>
+        <x:v>0.4811159979432757</x:v>
       </x:c>
       <x:c r="J32" s="50" t="str">
         <x:v>N/D</x:v>
@@ -4290,25 +4307,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V32" s="24" t="str">
-        <x:v>Multicedente</x:v>
+        <x:v>Múltiplos cedentes</x:v>
       </x:c>
       <x:c r="W32" s="24" t="str">
-        <x:v>BRF</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="X32" s="24" t="str">
-        <x:v>Risco Sacado BRF</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y32" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z32" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA32" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB32" s="24" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC32" s="24" t="str">
         <x:v>Crédito PJ</x:v>
@@ -4326,19 +4343,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH32" s="24" t="str">
-        <x:v>INVESTIMENTO, DIVERSIFICACAO E COMPOSICAO DA CARTEIRA PREVISTAS NESTE CAPITULO SERAO OBSERVADAS DIARIAMENTE, COM BASE NO PATRIMONIO LIQUIDO DO DIA UTIL IMEDIATAMENTE ANTERIOR. 9. DIREITOS CREDITORIOS CARACTERISTICAS DOS DIREITOS CREDITORIOS OS DIREITOS CREDITORIOS A SEREM ADQUIRIDOS PELA CLASSE SAO DIREITOS CREDITORIOS PERFORMADOS, DECORRENTES DE OPERACOES DE COMPRA E VENDA DE PRODUTOS E PRESTACAO DE SERVICOS PELOS CEDENTES AS DEVEDORAS, REALIZADAS NO SEGMENTO COMERCIAL, BEM COMO RECEBIVEIS DE CARTAO DE CREDITO 9.1.1. A CLASSE NAO PODERA ADQUIRIR DIREITOS CREDITORIOS NAO PADRONIZADOS E/OU NAO PERFORMADOS, CUJA EXIGIBILIDADE AINDA DEPENDA DA CONTRAPRESTACAO PELOS RESPECTIVOS CEDENTES. 9.1.2. OS TERMOS DE CESSAO A SER EM FIRMADOS NA CESSAO DOS RECEBIVEIS DE CARTOES DE CREDITO COM CADA UMA DAS CREDENCIADORAS DEVERAO SER APRESENTADOS AOS COTISTAS SENIORES DE CADA SERIE INDIVIDUALMENTE ANTES DA FORMALIZACAO COM CADA CREDENC</x:v>
+        <x:v>A FINALIDADE DE REALIZAR A GESTAO DE CAIXA E DE LIQUIDEZ DO FUNDO. ARTIGO 39. O FUNDO ADQUIRIRA OS DIREITOS CREDITORIOS, DEVIDAMENTE REPRESENTADOS PELOS DOCUMENTOS COMPROBATORIOS, DECORRENTES DOS SEGMENTOS COMERCIAL, INDUSTRIAL, FINANCEIR O E DE PRESTACAO DE SERVICOS, QUE ATENDAM AOS CRITERIOS DE ELEGIBILIDADE E AS CONDICOES DE CESSAO. PARAGRAFO PRIMEIRO. OS DIREITOS CREDITORIOS PODERAO SER ADQUIRIDOS (I) DE FORMA PRIMARIA ; OU (II) EM MERCADO SECUNDARIO. PARAGRAFO SEGUNDO. OS DIREITOS CREDITORIOS SERAO ADQUIRIDOS PELO FUNDO JUNTAMENTE COM TODOS OS DIREITOS, PRIVILEGIOS, PREFERENCIAS, PRERROGATIVAS E ACOES ASSEGURADOS AOS SEUS TITULARES, NOS TERMOS DOS CONTRATOS DE CESSAO. PARAGRAFO TERCEIRO. NOS TERMOS DOS ARTIGOS 42, CAPUT E §1O, E 30, §5O, DO ANEXO NORMATIVO II A RESOLUCAO CVM 175, OBSERVADAS AS NORMAS QU</x:v>
       </x:c>
       <x:c r="AI32" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62393829000159</x:v>
+        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
       </x:c>
       <x:c r="AJ32" s="24" t="str">
-        <x:v>Regulamento id 1231073 e correlatos</x:v>
+        <x:v>Regulamento arquivado no FundosNET</x:v>
       </x:c>
       <x:c r="AK32" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL32" s="24" t="str">
-        <x:v>p. 48 — política/definição do lastro</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM32" s="24" t="str">
         <x:v>N/D</x:v>
@@ -4361,22 +4378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D33" s="39" t="n">
-        <x:v>11468186000124</x:v>
+        <x:v>33254370000104</x:v>
       </x:c>
       <x:c r="E33" s="23" t="str">
-        <x:v>11.468.186/0001-24</x:v>
+        <x:v>33.254.370/0001-04</x:v>
       </x:c>
       <x:c r="F33" s="23" t="str">
-        <x:v>ATLANTA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>MERCADO CRÉDITO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G33" s="45" t="n">
-        <x:v>3090301588.05</x:v>
+        <x:v>3311135945.94</x:v>
       </x:c>
       <x:c r="H33" s="51" t="n">
-        <x:v>0.0037624132187805267</x:v>
+        <x:v>0.003921267148939838</x:v>
       </x:c>
       <x:c r="I33" s="51" t="n">
-        <x:v>0.797482279939063</x:v>
+        <x:v>0.7289331396097506</x:v>
       </x:c>
       <x:c r="J33" s="51" t="str">
         <x:v>N/D</x:v>
@@ -4415,31 +4432,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V33" s="23" t="str">
-        <x:v>Multicedentes e Multisacados</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W33" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X33" s="23" t="str">
-        <x:v>FIDC Multicedentes &amp; Multisacados</x:v>
+        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
       </x:c>
       <x:c r="Y33" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z33" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA33" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB33" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC33" s="23" t="str">
         <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD33" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
       </x:c>
       <x:c r="AE33" s="23" t="str">
         <x:v>N/D</x:v>
@@ -4451,19 +4468,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH33" s="23" t="str">
-        <x:v>O regulamento define cedentes genericamente e informa que os múltiplos cedentes não são conhecidos previamente.</x:v>
+        <x:v>O documento define cedentes como instituições financeiras parceiras e vendedores usuários da plataforma sem identificação nominal.</x:v>
       </x:c>
       <x:c r="AI33" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=11468186000124</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=33254370000104</x:v>
       </x:c>
       <x:c r="AJ33" s="23" t="str">
-        <x:v>1130308</x:v>
+        <x:v>1128340</x:v>
       </x:c>
       <x:c r="AK33" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL33" s="23" t="str">
-        <x:v>p. 49 — política/definição do lastro</x:v>
+        <x:v>p. 91 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM33" s="23" t="str">
         <x:v>N/D</x:v>
@@ -4472,7 +4489,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO33" s="23" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="36" customHeight="1">
@@ -4486,22 +4503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D34" s="38" t="n">
-        <x:v>62588266000154</x:v>
+        <x:v>60356171000180</x:v>
       </x:c>
       <x:c r="E34" s="24" t="str">
-        <x:v>62.588.266/0001-54</x:v>
+        <x:v>60.356.171/0001-80</x:v>
       </x:c>
       <x:c r="F34" s="24" t="str">
-        <x:v>VTK FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>CLOUDWALK PI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO</x:v>
       </x:c>
       <x:c r="G34" s="44" t="n">
-        <x:v>3085111034.31</x:v>
+        <x:v>3256435200.06</x:v>
       </x:c>
       <x:c r="H34" s="50" t="n">
-        <x:v>0.0037560937682519164</x:v>
+        <x:v>0.0038564868918486853</x:v>
       </x:c>
       <x:c r="I34" s="50" t="n">
-        <x:v>0.1851583225887235</x:v>
+        <x:v>0.1617789634703957</x:v>
       </x:c>
       <x:c r="J34" s="50" t="str">
         <x:v>N/D</x:v>
@@ -4540,55 +4557,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V34" s="24" t="str">
-        <x:v>Facta</x:v>
+        <x:v>Cloudwalk</x:v>
       </x:c>
       <x:c r="W34" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X34" s="24" t="str">
-        <x:v>Crédito INSS</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="Y34" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z34" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA34" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB34" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC34" s="24" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD34" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
-      </x:c>
-      <x:c r="AE34" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
+      </x:c>
+      <x:c r="AE34" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF34" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG34" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH34" s="24" t="str">
-        <x:v>A Facta origina digitalmente as CCBs concede os empréstimos e endossa ou transfere os direitos ao fundo.</x:v>
+        <x:v>A CloudWalk é definida como cedente dos recebíveis de transações de pagamento devidos pelos emissores.</x:v>
       </x:c>
       <x:c r="AI34" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62588266000154</x:v>
+        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
       </x:c>
       <x:c r="AJ34" s="24" t="str">
-        <x:v>1002580</x:v>
+        <x:v>chat_task_acquiring_2026_07_31</x:v>
       </x:c>
       <x:c r="AK34" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL34" s="24" t="str">
-        <x:v>p. 20 — política/definição do lastro</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM34" s="24" t="str">
         <x:v>N/D</x:v>
@@ -4611,22 +4628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D35" s="39" t="n">
-        <x:v>60010416000112</x:v>
+        <x:v>7727002000126</x:v>
       </x:c>
       <x:c r="E35" s="23" t="str">
-        <x:v>60.010.416/0001-12</x:v>
+        <x:v>07.727.002/0001-26</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
-        <x:v>MT CONSIGNADO PRIVADO I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FIDC PCG - BRASIL MULTICARTEIRA</x:v>
       </x:c>
       <x:c r="G35" s="45" t="n">
-        <x:v>3072067502.44</x:v>
+        <x:v>3196029095.69</x:v>
       </x:c>
       <x:c r="H35" s="51" t="n">
-        <x:v>0.0037402133904541495</x:v>
+        <x:v>0.0037849499702215465</x:v>
       </x:c>
       <x:c r="I35" s="51" t="n">
-        <x:v>0.0572199210343438</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J35" s="51" t="str">
         <x:v>N/D</x:v>
@@ -4665,55 +4682,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V35" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Múltiplos cedentes</x:v>
       </x:c>
       <x:c r="W35" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X35" s="23" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Não padronizado/NPL</x:v>
       </x:c>
       <x:c r="Y35" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z35" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA35" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB35" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC35" s="23" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD35" s="23" t="str">
-        <x:v>Consignado/INSS</x:v>
-      </x:c>
-      <x:c r="AE35" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Não padronizado/NPL</x:v>
+      </x:c>
+      <x:c r="AE35" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF35" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG35" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH35" s="23" t="str">
-        <x:v>A Parati concede os empréstimos consignados e endossa ao fundo as CCBs correspondentes.</x:v>
+        <x:v>RSIFICACAO; E (C) AVALIAR A ADERENCIA DO RISCO DE PERFORMANCE DOS DIREITOS DE CREDITO, SE HOUVER, A POLITICA DE INVESTIMENTO, OBSERVADO QUE O CUSTODIANTE PODERA SER SUBCONTRATADO PELO GESTOR PARA DESEMPENHAR AS FUNCOES INDICADAS NOS ITENS (A) A (C); (IX) ENTREGAR OS DIREITOS DE CREDITO AO CUSTODIANTE OU ADMINISTRADOR, CONFORME O CASO, NOS TERMOS DESTE ANEXO , POR MEIO DO ENVIO, PELO GESTOR AO CUSTODIANTE, DOS DOCUMENTOS COMPROBATORIOS DE CREDITO, DE FORMA ELETRONICA OU ENTREGA DAS VIAS FISICAS DOS REFERIDOS DOCUMENTOS; (X) NA HIPOTESE DE OCORRER SUBSTITUICAO DE DIREITOS DE CREDITO, POR QUALQUER MOTIVO, DILIGENCIAR PARA QUE A RELACAO ENTRE RISCO E RETORNO DA CARTEIRA DE DIREITOS DE CREDITO NAO SEJA ALTERADA, NOS TERMOS DA POLITICA DE INVESTIMENTOS; (XI) ATUAR PARA QUE OCORRA A CORRETA FORMALIZACAO DOS DOCUMENT</x:v>
       </x:c>
       <x:c r="AI35" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=60010416000112</x:v>
+        <x:v>Comentário manual do usuário — IMG_8592.jpg</x:v>
       </x:c>
       <x:c r="AJ35" s="23" t="str">
-        <x:v>1051393</x:v>
+        <x:v>IMG_8592</x:v>
       </x:c>
       <x:c r="AK35" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL35" s="23" t="str">
-        <x:v>p. 9 — política/definição do lastro</x:v>
+        <x:v>Linha do FIDC na imagem</x:v>
       </x:c>
       <x:c r="AM35" s="23" t="str">
         <x:v>N/D</x:v>
@@ -4722,7 +4739,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO35" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="36" customHeight="1">
@@ -4736,22 +4753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D36" s="38" t="n">
-        <x:v>51079269000146</x:v>
+        <x:v>54836930000109</x:v>
       </x:c>
       <x:c r="E36" s="24" t="str">
-        <x:v>51.079.269/0001-46</x:v>
+        <x:v>54.836.930/0001-09</x:v>
       </x:c>
       <x:c r="F36" s="24" t="str">
-        <x:v>CARNIVAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS METEORO - RESP LTDA</x:v>
       </x:c>
       <x:c r="G36" s="44" t="n">
-        <x:v>3058107297.6</x:v>
+        <x:v>3141061787.79</x:v>
       </x:c>
       <x:c r="H36" s="50" t="n">
-        <x:v>0.0037232169719071677</x:v>
+        <x:v>0.0037198540326783534</x:v>
       </x:c>
       <x:c r="I36" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J36" s="50" t="str">
         <x:v>N/D</x:v>
@@ -4799,16 +4816,16 @@
         <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y36" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z36" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA36" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB36" s="24" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AC36" s="24" t="str">
         <x:v>Multissetorial / Outros</x:v>
@@ -4826,19 +4843,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH36" s="24" t="str">
-        <x:v>O regulamento admite CCBs, duplicatas, cheques e contratos oriundos de setores financeiro, comercial, industrial e de serviços. O mandato é multicarteira.</x:v>
+        <x:v>TIVO; E (II) ATIVOS FINANCEIROS DE LIQUIDEZ. 6.1.1. PARA FINS DO ARTIGO 21 DO ANEXO NORMATIVO II, A POLITICA DE INVESTIMENTO DA CLASSE UNICA ABRANGE, ALEM DESTE CAPITULO 6, O DISPOSTO NOS CAPITULOS 7 E 8 E NO SUPLEMENTO A DO PRESENTE ANEXO DESCRITIVO. 6.2. ORIGEM DOS DIREITOS CREDITORIOS. OS DIREITOS CREDITORIOS SAO ORIUNDOS DE DIVIDAS CONTRAIDAS PELOS DEVEDORES (1) FRENTE A NU PAGAMENTOS, NO AMBITO DE CONTRATO DE CARTAO DE CREDITO, REPRESENTADAS POR CCB EMITIDAS EM FAVOR DA NU FINANCEIRA; (2) DECORRENTES DE OPERACOES DE EMPRESTIMO BANCAR IO CELEBRADAS ENTRE OS DEVEDORES E A NU FINANCEIRA; OU (3) DECORRENTES DE DIVIDAS PREVIAMENTE INCORRIDAS PELOS DEVEDORES E QUE FORAM RENEGOCIADAS ATRAVES DA EMISSAO DAS CCB EM BENEFICIO DO ENDOSSANTE OU DA CELEBRACAO DE CONTRATO DE EMPRESTIMO ENTRE O ENDOS SANTE E O DEVEDOR,</x:v>
       </x:c>
       <x:c r="AI36" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=51079269000146</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=54836930000109</x:v>
       </x:c>
       <x:c r="AJ36" s="24" t="str">
-        <x:v>Regulamento id 884671</x:v>
+        <x:v>1044203</x:v>
       </x:c>
       <x:c r="AK36" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL36" s="24" t="str">
-        <x:v>p. 27 — política/definição do lastro</x:v>
+        <x:v>p. 37</x:v>
       </x:c>
       <x:c r="AM36" s="24" t="str">
         <x:v>N/D</x:v>
@@ -4861,22 +4878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D37" s="39" t="n">
-        <x:v>24194675000187</x:v>
+        <x:v>62588266000154</x:v>
       </x:c>
       <x:c r="E37" s="23" t="str">
-        <x:v>24.194.675/0001-87</x:v>
+        <x:v>62.588.266/0001-54</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ALTERNATIVE ASSETS I RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>VTK FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G37" s="45" t="n">
-        <x:v>3030582055.52</x:v>
+        <x:v>3100556826.01</x:v>
       </x:c>
       <x:c r="H37" s="51" t="n">
-        <x:v>0.0036897052476623916</x:v>
+        <x:v>0.003671885366157207</x:v>
       </x:c>
       <x:c r="I37" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1896520557500736</x:v>
       </x:c>
       <x:c r="J37" s="51" t="str">
         <x:v>N/D</x:v>
@@ -4915,55 +4932,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V37" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Facta</x:v>
       </x:c>
       <x:c r="W37" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X37" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Crédito INSS</x:v>
       </x:c>
       <x:c r="Y37" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z37" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA37" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB37" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC37" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD37" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE37" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE37" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF37" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG37" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH37" s="23" t="str">
-        <x:v>E FORMA PRIVADA OU OFERTADOS PUBLICAMENTE, INDEPENDENTEMENTE DO REGIME DE DISTRIBUICAO, OBSERVADA A POLITICA DE INVESTIMENTOS E AS DEMAIS DISPOSICOES DESTE REGULAMENTO E DA LEGISLACAO E REGULAMENTACAO APLICAVEIS . 4.5 O GESTOR SERA RESPONSAVEL POR VERIFICAR O CUMPRIMENTO, PELOS CEDENTES DA OBRIGACAO, CONFORME APLICAVEL, DE NOTIFICAR OS RESPECTIVOS DEVEDORES ACERCA DA CESSAO DOS DIREITOS CREDITORIOS A CLASSE CASO O CEDENTE NAO O TENHA FEITO. CRITERIOS DE ELEGIBILIDADE DIREITOS CREDITORIOS (I) ORIUNDOS DE LITIGIOS, JA AJUIZADOS, CONTRA PESSOAS FISICAS OU JURIDICAS DE DIREITO PRIVADO OU PUBLICO, NESTE ULTIMO CASO, JA REPRESENTADOS EM PRE PRECATORIOS E/OU PRECATORIOS DE TITULARIDADE DO CEDENTE E O/OU (II) DIREITOS CREDITORIOS PERFORMADOS QUE SE ENCONTREM VENCIDOS E INADIMPLIDOS NA DATA DE SUA CESSAO A CLASSE 4.5.</x:v>
+        <x:v>A Facta origina digitalmente as CCBs concede os empréstimos e endossa ou transfere os direitos ao fundo.</x:v>
       </x:c>
       <x:c r="AI37" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=24194675000187</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62588266000154</x:v>
       </x:c>
       <x:c r="AJ37" s="23" t="str">
-        <x:v>830508</x:v>
+        <x:v>1002580</x:v>
       </x:c>
       <x:c r="AK37" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL37" s="23" t="str">
-        <x:v>p. 9</x:v>
+        <x:v>p. 20 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM37" s="23" t="str">
         <x:v>N/D</x:v>
@@ -4972,7 +4989,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO37" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="36" customHeight="1">
@@ -4986,22 +5003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D38" s="38" t="n">
-        <x:v>33254370000104</x:v>
+        <x:v>24194675000187</x:v>
       </x:c>
       <x:c r="E38" s="24" t="str">
-        <x:v>33.254.370/0001-04</x:v>
+        <x:v>24.194.675/0001-87</x:v>
       </x:c>
       <x:c r="F38" s="24" t="str">
-        <x:v>MERCADO CRÉDITO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ALTERNATIVE ASSETS I RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G38" s="44" t="n">
-        <x:v>3017886933.33</x:v>
+        <x:v>3091810070.76</x:v>
       </x:c>
       <x:c r="H38" s="50" t="n">
-        <x:v>0.0036742490553844627</x:v>
+        <x:v>0.0036615268775352892</x:v>
       </x:c>
       <x:c r="I38" s="50" t="n">
-        <x:v>0.6940802460808179</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J38" s="50" t="str">
         <x:v>N/D</x:v>
@@ -5046,49 +5063,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X38" s="24" t="str">
-        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y38" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z38" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA38" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB38" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC38" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD38" s="24" t="str">
-        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
-      </x:c>
-      <x:c r="AE38" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira outros</x:v>
+      </x:c>
+      <x:c r="AE38" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF38" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG38" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH38" s="24" t="str">
-        <x:v>O documento define cedentes como instituições financeiras parceiras e vendedores usuários da plataforma sem identificação nominal.</x:v>
+        <x:v>E FORMA PRIVADA OU OFERTADOS PUBLICAMENTE, INDEPENDENTEMENTE DO REGIME DE DISTRIBUICAO, OBSERVADA A POLITICA DE INVESTIMENTOS E AS DEMAIS DISPOSICOES DESTE REGULAMENTO E DA LEGISLACAO E REGULAMENTACAO APLICAVEIS . 4.5 O GESTOR SERA RESPONSAVEL POR VERIFICAR O CUMPRIMENTO, PELOS CEDENTES DA OBRIGACAO, CONFORME APLICAVEL, DE NOTIFICAR OS RESPECTIVOS DEVEDORES ACERCA DA CESSAO DOS DIREITOS CREDITORIOS A CLASSE CASO O CEDENTE NAO O TENHA FEITO. CRITERIOS DE ELEGIBILIDADE DIREITOS CREDITORIOS (I) ORIUNDOS DE LITIGIOS, JA AJUIZADOS, CONTRA PESSOAS FISICAS OU JURIDICAS DE DIREITO PRIVADO OU PUBLICO, NESTE ULTIMO CASO, JA REPRESENTADOS EM PRE PRECATORIOS E/OU PRECATORIOS DE TITULARIDADE DO CEDENTE E O/OU (II) DIREITOS CREDITORIOS PERFORMADOS QUE SE ENCONTREM VENCIDOS E INADIMPLIDOS NA DATA DE SUA CESSAO A CLASSE 4.5.</x:v>
       </x:c>
       <x:c r="AI38" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=33254370000104</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=24194675000187</x:v>
       </x:c>
       <x:c r="AJ38" s="24" t="str">
-        <x:v>1128340</x:v>
+        <x:v>830508</x:v>
       </x:c>
       <x:c r="AK38" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL38" s="24" t="str">
-        <x:v>p. 91 — política/definição do lastro</x:v>
+        <x:v>p. 9</x:v>
       </x:c>
       <x:c r="AM38" s="24" t="str">
         <x:v>N/D</x:v>
@@ -5111,19 +5128,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D39" s="39" t="n">
-        <x:v>11230727000181</x:v>
+        <x:v>51079269000146</x:v>
       </x:c>
       <x:c r="E39" s="23" t="str">
-        <x:v>11.230.727/0001-81</x:v>
+        <x:v>51.079.269/0001-46</x:v>
       </x:c>
       <x:c r="F39" s="23" t="str">
-        <x:v>FIDC GM - VENDA DE VEÍCULOS</x:v>
+        <x:v>CARNIVAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G39" s="45" t="n">
-        <x:v>2984648919.61</x:v>
+        <x:v>3058103926.17</x:v>
       </x:c>
       <x:c r="H39" s="51" t="n">
-        <x:v>0.003633782085212452</x:v>
+        <x:v>0.00362160982198212</x:v>
       </x:c>
       <x:c r="I39" s="51" t="n">
         <x:v>0</x:v>
@@ -5171,25 +5188,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X39" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y39" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z39" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA39" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB39" s="23" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC39" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD39" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE39" s="23" t="str">
         <x:v>N/D</x:v>
@@ -5201,19 +5218,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH39" s="23" t="str">
-        <x:v>DITORIO CEDIDO SIGNIFICA UM DIREITO CREDITORIO QUE ATENDA A TODOS OS CRITERIOS DE ELEGIBILIDADE E A POLITICA DE INVESTIMENTO E VENHA A SER ADQUIRIDO PELA CLASSE, NOS TERMOS DO CONTRATO DE CESSAO E RESPECTIVO TERMO DE CESSAO. DIREITOS CREDITORIOS SIGNIFICA, CONJUNTA OU SEPARADAMENTE, OS DIREITOS DE CREDITO E VALORES ORIUNDOS DE UMA VENDA DE VEICULOS A PRAZO DO CEDENTE A UMA CONCESSIONARIA, COM TUDO QUE OS REFERIDOS DIREITOS DE CREDITO REPRESENTAM, INCLUINDO AJUSTES MONETARIOS E TODOS OS DIREITOS ASSEGURADOS AO CEDENTE PELOS MESMOS. DIREITOS CREDITORIOS INADIMPLIDOS COM RELACAO A QUALQUER DIREITO CREDITORIO, SIGNIFICA O NAO PAGAMENTO A CLASSE POR PARTE DA CONCESSIONARIA DO VALOR DA VENDA DO VEICULO AO CONSUMIDOR FINAL OU DA ENTREGA FISICA DO VEICULO A TERCEIROS, A QUALQUER TITULO QUE SEJA, NO PRAZO</x:v>
+        <x:v>O regulamento admite CCBs, duplicatas, cheques e contratos oriundos de setores financeiro, comercial, industrial e de serviços. O mandato é multicarteira.</x:v>
       </x:c>
       <x:c r="AI39" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 700587</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=51079269000146</x:v>
       </x:c>
       <x:c r="AJ39" s="23" t="str">
-        <x:v>700587</x:v>
+        <x:v>Regulamento id 884671</x:v>
       </x:c>
       <x:c r="AK39" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL39" s="23" t="str">
-        <x:v>p. 18 — venda de veículos a prazo à concessionária</x:v>
+        <x:v>p. 27 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM39" s="23" t="str">
         <x:v>N/D</x:v>
@@ -5236,22 +5253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D40" s="38" t="n">
-        <x:v>65976848000104</x:v>
+        <x:v>11230727000181</x:v>
       </x:c>
       <x:c r="E40" s="24" t="str">
-        <x:v>65.976.848/0001-04</x:v>
+        <x:v>11.230.727/0001-81</x:v>
       </x:c>
       <x:c r="F40" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AGIBANK II RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FIDC GM - VENDA DE VEÍCULOS</x:v>
       </x:c>
       <x:c r="G40" s="44" t="n">
-        <x:v>2967229777.92</x:v>
+        <x:v>3000510455.02</x:v>
       </x:c>
       <x:c r="H40" s="50" t="n">
-        <x:v>0.0036125744434703975</x:v>
+        <x:v>0.003553403807459875</x:v>
       </x:c>
       <x:c r="I40" s="50" t="n">
-        <x:v>0.1521734277067646</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J40" s="50" t="str">
         <x:v>N/D</x:v>
@@ -5296,49 +5313,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X40" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y40" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z40" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA40" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB40" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Crédito Corporativo</x:v>
       </x:c>
       <x:c r="AC40" s="24" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD40" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
-      </x:c>
-      <x:c r="AE40" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE40" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF40" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG40" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH40" s="24" t="str">
-        <x:v>ITORIOS QUE ATENDAM A POLITICA DE INVESTIMENTO, COMPOSICAO E DIVERSIFICACAO DA CARTEIRA DO FUNDO, DESCRITA NESTE ANEXO DESCRITIVO. 1.3 CATEGORIA DO FUNDO. FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS, CONFORME ANEXO NORMATIVO II DA RESOLUCAO CVM 175. 1.4 CLASSIFICACAO ANBIMA. PARA FINS DO DISPOSTO NO CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS DA ANBIMA, O FUNDO E CLASSIFICADO COMO " FINANCEIRO – CREDITO CONSIGNADO", CONFORME ARTIGO 34 DO ANEXO COMPLEMENTAR V DAS REGRAS E PROCEDIMENTOS DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS DA ANBIMA. 1.5 FORMA DE CONSTITUICAO. A CLASSE A E CONSTITUIDA SOB A FORMA DE CONDOMINIO FECHADO, DE MODO QUE AS COTAS DE CADA SUBCLASSE OU SERIE SOMENTE SERAO RESGATADAS, ORDINARIAMENTE, NAS RESPECTIVAS DATAS DE RESGATE OU EM CASO DE LIQUIDACAO DO FUNDO E/OU DA CLASSE A. NAO OBSTANTE, AS COTAS SERAO OBJETO DE AMORTIZACOES DURANTE O PRAZO DE VIGENCIA DO FUNDO, NOS TERMOS DESTE REGULAMENTO E DO</x:v>
+        <x:v>DITORIO CEDIDO SIGNIFICA UM DIREITO CREDITORIO QUE ATENDA A TODOS OS CRITERIOS DE ELEGIBILIDADE E A POLITICA DE INVESTIMENTO E VENHA A SER ADQUIRIDO PELA CLASSE, NOS TERMOS DO CONTRATO DE CESSAO E RESPECTIVO TERMO DE CESSAO. DIREITOS CREDITORIOS SIGNIFICA, CONJUNTA OU SEPARADAMENTE, OS DIREITOS DE CREDITO E VALORES ORIUNDOS DE UMA VENDA DE VEICULOS A PRAZO DO CEDENTE A UMA CONCESSIONARIA, COM TUDO QUE OS REFERIDOS DIREITOS DE CREDITO REPRESENTAM, INCLUINDO AJUSTES MONETARIOS E TODOS OS DIREITOS ASSEGURADOS AO CEDENTE PELOS MESMOS. DIREITOS CREDITORIOS INADIMPLIDOS COM RELACAO A QUALQUER DIREITO CREDITORIO, SIGNIFICA O NAO PAGAMENTO A CLASSE POR PARTE DA CONCESSIONARIA DO VALOR DA VENDA DO VEICULO AO CONSUMIDOR FINAL OU DA ENTREGA FISICA DO VEICULO A TERCEIROS, A QUALQUER TITULO QUE SEJA, NO PRAZO</x:v>
       </x:c>
       <x:c r="AI40" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=65976848000104</x:v>
+        <x:v>FundosNet/B3 — regulamento 700587</x:v>
       </x:c>
       <x:c r="AJ40" s="24" t="str">
-        <x:v>1239452</x:v>
+        <x:v>700587</x:v>
       </x:c>
       <x:c r="AK40" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL40" s="24" t="str">
-        <x:v>p. 17 — política/definição do lastro</x:v>
+        <x:v>p. 18 — venda de veículos a prazo à concessionária</x:v>
       </x:c>
       <x:c r="AM40" s="24" t="str">
         <x:v>N/D</x:v>
@@ -5361,109 +5378,109 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D41" s="39" t="n">
-        <x:v>53029409000105</x:v>
+        <x:v>65976848000104</x:v>
       </x:c>
       <x:c r="E41" s="23" t="str">
-        <x:v>53.029.409/0001-05</x:v>
+        <x:v>65.976.848/0001-04</x:v>
       </x:c>
       <x:c r="F41" s="23" t="str">
-        <x:v>GSR FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AGIBANK II RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G41" s="45" t="n">
-        <x:v>2943415740.48</x:v>
+        <x:v>2966345679.42</x:v>
       </x:c>
       <x:c r="H41" s="51" t="n">
-        <x:v>0.0035835810760905724</x:v>
+        <x:v>0.003512943610597391</x:v>
       </x:c>
       <x:c r="I41" s="51" t="n">
+        <x:v>0.1524969562841521</x:v>
+      </x:c>
+      <x:c r="J41" s="51" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="K41" s="51" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="L41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="M41" s="45" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="N41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="O41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="P41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="Q41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="R41" s="45" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="S41" s="33" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="T41" s="33" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="U41" s="45" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="V41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="W41" s="23" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="X41" s="23" t="str">
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="Y41" s="23" t="str">
+        <x:v>Financeiro</x:v>
+      </x:c>
+      <x:c r="Z41" s="23" t="str">
+        <x:v>Crédito Consignado</x:v>
+      </x:c>
+      <x:c r="AA41" s="23" t="str">
+        <x:v>Financeiro</x:v>
+      </x:c>
+      <x:c r="AB41" s="23" t="str">
+        <x:v>Crédito Consignado</x:v>
+      </x:c>
+      <x:c r="AC41" s="23" t="str">
+        <x:v>Crédito PF</x:v>
+      </x:c>
+      <x:c r="AD41" s="23" t="str">
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE41" s="27" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J41" s="51" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="K41" s="51" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="L41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="M41" s="45" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="N41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="O41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="P41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="Q41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="R41" s="45" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="S41" s="33" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="T41" s="33" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="U41" s="45" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="V41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="W41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="X41" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="Y41" s="23" t="str">
-        <x:v>Outros</x:v>
-      </x:c>
-      <x:c r="Z41" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
-      </x:c>
-      <x:c r="AA41" s="23" t="str">
-        <x:v>Outros</x:v>
-      </x:c>
-      <x:c r="AB41" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
-      </x:c>
-      <x:c r="AC41" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
-      </x:c>
-      <x:c r="AD41" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE41" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
       <x:c r="AF41" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG41" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH41" s="23" t="str">
-        <x:v>O regulamento enumera duplicatas, cheques, debêntures, certificados, cédulas rurais, industriais, comerciais, imobiliárias e bancárias, contratos e agendas de cartão.</x:v>
+        <x:v>ITORIOS QUE ATENDAM A POLITICA DE INVESTIMENTO, COMPOSICAO E DIVERSIFICACAO DA CARTEIRA DO FUNDO, DESCRITA NESTE ANEXO DESCRITIVO. 1.3 CATEGORIA DO FUNDO. FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS, CONFORME ANEXO NORMATIVO II DA RESOLUCAO CVM 175. 1.4 CLASSIFICACAO ANBIMA. PARA FINS DO DISPOSTO NO CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS DA ANBIMA, O FUNDO E CLASSIFICADO COMO " FINANCEIRO – CREDITO CONSIGNADO", CONFORME ARTIGO 34 DO ANEXO COMPLEMENTAR V DAS REGRAS E PROCEDIMENTOS DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS DA ANBIMA. 1.5 FORMA DE CONSTITUICAO. A CLASSE A E CONSTITUIDA SOB A FORMA DE CONDOMINIO FECHADO, DE MODO QUE AS COTAS DE CADA SUBCLASSE OU SERIE SOMENTE SERAO RESGATADAS, ORDINARIAMENTE, NAS RESPECTIVAS DATAS DE RESGATE OU EM CASO DE LIQUIDACAO DO FUNDO E/OU DA CLASSE A. NAO OBSTANTE, AS COTAS SERAO OBJETO DE AMORTIZACOES DURANTE O PRAZO DE VIGENCIA DO FUNDO, NOS TERMOS DESTE REGULAMENTO E DO</x:v>
       </x:c>
       <x:c r="AI41" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53029409000105</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=65976848000104</x:v>
       </x:c>
       <x:c r="AJ41" s="23" t="str">
-        <x:v>565885</x:v>
+        <x:v>1239452</x:v>
       </x:c>
       <x:c r="AK41" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL41" s="23" t="str">
-        <x:v>p. 19 — política/definição do lastro</x:v>
+        <x:v>p. 17 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM41" s="23" t="str">
         <x:v>N/D</x:v>
@@ -5486,22 +5503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D42" s="38" t="n">
-        <x:v>55471753000177</x:v>
+        <x:v>53029409000105</x:v>
       </x:c>
       <x:c r="E42" s="24" t="str">
-        <x:v>55.471.753/0001-77</x:v>
+        <x:v>53.029.409/0001-05</x:v>
       </x:c>
       <x:c r="F42" s="24" t="str">
-        <x:v>SELLER II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO RESP LTDA</x:v>
+        <x:v>GSR FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS</x:v>
       </x:c>
       <x:c r="G42" s="44" t="n">
-        <x:v>2879663753.83</x:v>
+        <x:v>2940889060.03</x:v>
       </x:c>
       <x:c r="H42" s="50" t="n">
-        <x:v>0.003505963629876582</x:v>
+        <x:v>0.003482796190809487</x:v>
       </x:c>
       <x:c r="I42" s="50" t="n">
-        <x:v>0.650587163121943</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J42" s="50" t="str">
         <x:v>N/D</x:v>
@@ -5546,49 +5563,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X42" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y42" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z42" s="24" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA42" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB42" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC42" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD42" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
-      </x:c>
-      <x:c r="AE42" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Multicarteira outros</x:v>
+      </x:c>
+      <x:c r="AE42" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF42" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG42" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH42" s="24" t="str">
-        <x:v>OS ESTABELECIMENTO COMERCIAIS ORGANIZADOS E FORMALIZADOS ATRAVES DE U.R. E REGISTRADOS EM SISTEM AS DE REGISTRO, NOS TERMOS DA RESOLUCAO BCB 264/22. 3.18.1.AS CESSOES DAS U.RS DOS DIREITOS CREDITORIOS ESTABELECIMENTOS COMERCIAIS SAO REGISTRADAS EM BENEFICIO DA CLASSE UNICA NO SISTEMA DE REGISTRO , CONSIDERANDO-SE O SEGUINTE CONJUNTO DE INFORMACOES (I) NUMERO DE INSCRICAO NO CNPJ OU NO CPF DOS ESTABELECIMENTOS COMERCIAIS; (II) IDENTIFICACAO DO ARRANJO DE PAGAMENTO (BANDEIRAS); (III) IDENTIFICACAO DO CREDENCIADOR OU SUBCREDENCIADOR ; (IV) DATA DE LIQUIDACAO (VENCIMENTO); E (V) VALOR FIXO. 3.18.2.O REGISTRO DAS CESSOES DOS DIREITOS CREDITORIOS ESTABELECIMENTOS COMERCIAIS NO SISTEMA DE REGISTRO EM BENEFICIO DA CLASSE UNICA SERA OPERACIONALIZADO PELO AGENTE DE PAGAMENTO E REGISTRO, OBSERVADAS AS DISPOSICOES DO CONTRATO DE AGENTE DE PAGAMENTO E REGISTRO. 3.18.3.A CLASSE UNICA ADQUIRIRA OS DIREITOS CREDITORIOS ESTABELECIMENTOS COMERCIAIS DOS ESTABELECIMENTOS COMERCIAIS, POR MEIO</x:v>
+        <x:v>O regulamento enumera duplicatas, cheques, debêntures, certificados, cédulas rurais, industriais, comerciais, imobiliárias e bancárias, contratos e agendas de cartão.</x:v>
       </x:c>
       <x:c r="AI42" s="24" t="str">
-        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53029409000105</x:v>
       </x:c>
       <x:c r="AJ42" s="24" t="str">
-        <x:v>Regulamento arquivado no FundosNET</x:v>
+        <x:v>565885</x:v>
       </x:c>
       <x:c r="AK42" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL42" s="24" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>p. 19 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM42" s="24" t="str">
         <x:v>N/D</x:v>
@@ -5620,10 +5637,10 @@
         <x:v>CITY - 02 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS RESPONSABILIDADE ILIMITADA</x:v>
       </x:c>
       <x:c r="G43" s="45" t="n">
-        <x:v>2712460624.74</x:v>
+        <x:v>2758097886.13</x:v>
       </x:c>
       <x:c r="H43" s="51" t="n">
-        <x:v>0.0033023953873651314</x:v>
+        <x:v>0.0032663227396939865</x:v>
       </x:c>
       <x:c r="I43" s="51" t="n">
         <x:v>1</x:v>
@@ -5745,13 +5762,13 @@
         <x:v>CLOUDWALK A.I. FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO</x:v>
       </x:c>
       <x:c r="G44" s="44" t="n">
-        <x:v>2700487143.69</x:v>
+        <x:v>2703044510.17</x:v>
       </x:c>
       <x:c r="H44" s="50" t="n">
-        <x:v>0.0032878177864113798</x:v>
+        <x:v>0.003201124874636562</x:v>
       </x:c>
       <x:c r="I44" s="50" t="n">
-        <x:v>0.1618628982389708</x:v>
+        <x:v>0.1623408260106682</x:v>
       </x:c>
       <x:c r="J44" s="50" t="str">
         <x:v>N/D</x:v>
@@ -5861,22 +5878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D45" s="39" t="n">
-        <x:v>54836930000109</x:v>
+        <x:v>29492605000129</x:v>
       </x:c>
       <x:c r="E45" s="23" t="str">
-        <x:v>54.836.930/0001-09</x:v>
+        <x:v>29.492.605/0001-29</x:v>
       </x:c>
       <x:c r="F45" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS METEORO - RESP LTDA</x:v>
+        <x:v>GAZIN FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MULTISSEGMENTOS - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G45" s="45" t="n">
-        <x:v>2688587997.05</x:v>
+        <x:v>2661374071.86</x:v>
       </x:c>
       <x:c r="H45" s="51" t="n">
-        <x:v>0.0032733306869050845</x:v>
+        <x:v>0.003151775973384929</x:v>
       </x:c>
       <x:c r="I45" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0.6957359372662582</x:v>
       </x:c>
       <x:c r="J45" s="51" t="str">
         <x:v>N/D</x:v>
@@ -5921,25 +5938,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X45" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y45" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z45" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AA45" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB45" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AC45" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD45" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="AE45" s="23" t="str">
         <x:v>N/D</x:v>
@@ -5951,19 +5968,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH45" s="23" t="str">
-        <x:v>TIVO; E (II) ATIVOS FINANCEIROS DE LIQUIDEZ. 6.1.1. PARA FINS DO ARTIGO 21 DO ANEXO NORMATIVO II, A POLITICA DE INVESTIMENTO DA CLASSE UNICA ABRANGE, ALEM DESTE CAPITULO 6, O DISPOSTO NOS CAPITULOS 7 E 8 E NO SUPLEMENTO A DO PRESENTE ANEXO DESCRITIVO. 6.2. ORIGEM DOS DIREITOS CREDITORIOS. OS DIREITOS CREDITORIOS SAO ORIUNDOS DE DIVIDAS CONTRAIDAS PELOS DEVEDORES (1) FRENTE A NU PAGAMENTOS, NO AMBITO DE CONTRATO DE CARTAO DE CREDITO, REPRESENTADAS POR CCB EMITIDAS EM FAVOR DA NU FINANCEIRA; (2) DECORRENTES DE OPERACOES DE EMPRESTIMO BANCAR IO CELEBRADAS ENTRE OS DEVEDORES E A NU FINANCEIRA; OU (3) DECORRENTES DE DIVIDAS PREVIAMENTE INCORRIDAS PELOS DEVEDORES E QUE FORAM RENEGOCIADAS ATRAVES DA EMISSAO DAS CCB EM BENEFICIO DO ENDOSSANTE OU DA CELEBRACAO DE CONTRATO DE EMPRESTIMO ENTRE O ENDOS SANTE E O DEVEDOR,</x:v>
+        <x:v>A política admite recebíveis documentados por NF-e e NFC-e e créditos representados por CCBs em múltiplos segmentos econômicos. O enquadramento oficial multicarteira é aderente.</x:v>
       </x:c>
       <x:c r="AI45" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=54836930000109</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=29492605000129</x:v>
       </x:c>
       <x:c r="AJ45" s="23" t="str">
-        <x:v>1044203</x:v>
+        <x:v>1117213</x:v>
       </x:c>
       <x:c r="AK45" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL45" s="23" t="str">
-        <x:v>p. 37</x:v>
+        <x:v>p. 30 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM45" s="23" t="str">
         <x:v>N/D</x:v>
@@ -5986,22 +6003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D46" s="38" t="n">
-        <x:v>52256912000122</x:v>
+        <x:v>50473039000102</x:v>
       </x:c>
       <x:c r="E46" s="24" t="str">
-        <x:v>52.256.912/0001-22</x:v>
+        <x:v>50.473.039/0001-02</x:v>
       </x:c>
       <x:c r="F46" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ACR I BANCOS EMISSORES DE CARTÃO DE CRÉDITO RESP LIMI</x:v>
+        <x:v>SELLER FIDC SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G46" s="44" t="n">
-        <x:v>2661592324.9</x:v>
+        <x:v>2641955191.86</x:v>
       </x:c>
       <x:c r="H46" s="50" t="n">
-        <x:v>0.0032404637090865484</x:v>
+        <x:v>0.003128778845675155</x:v>
       </x:c>
       <x:c r="I46" s="50" t="n">
-        <x:v>0.0830337384588593</x:v>
+        <x:v>0.3493155766177357</x:v>
       </x:c>
       <x:c r="J46" s="50" t="str">
         <x:v>N/D</x:v>
@@ -6040,19 +6057,19 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V46" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Mercado Pago (originador) | Mercado Livre (cedente)</x:v>
       </x:c>
       <x:c r="W46" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X46" s="24" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>recebíveis com risco Grupo Mercado Livre</x:v>
       </x:c>
       <x:c r="Y46" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z46" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA46" s="24" t="str">
         <x:v>Financeiro</x:v>
@@ -6064,7 +6081,7 @@
         <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD46" s="24" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="AE46" s="26" t="b">
         <x:v>0</x:v>
@@ -6076,7 +6093,7 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH46" s="24" t="str">
-        <x:v>Financeiro → Adquirência; risco banco emissor</x:v>
+        <x:v>Há recebíveis cedidos por lojistas e recebíveis de pagamento originados ou cedidos pelo Mercado Crédito.</x:v>
       </x:c>
       <x:c r="AI46" s="24" t="str">
         <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
@@ -6097,7 +6114,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO46" s="24" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="36" customHeight="1">
@@ -6111,22 +6128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D47" s="39" t="n">
-        <x:v>26405883000103</x:v>
+        <x:v>40801446000130</x:v>
       </x:c>
       <x:c r="E47" s="23" t="str">
-        <x:v>26.405.883/0001-03</x:v>
+        <x:v>40.801.446/0001-30</x:v>
       </x:c>
       <x:c r="F47" s="23" t="str">
-        <x:v>FIDC MULTISEGMENTOS NPL IPANEMA VI RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>EB VESTA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G47" s="45" t="n">
-        <x:v>2633629374.15</x:v>
+        <x:v>2579461850.15</x:v>
       </x:c>
       <x:c r="H47" s="51" t="n">
-        <x:v>0.0032064190786385877</x:v>
+        <x:v>0.0030547700789329223</x:v>
       </x:c>
       <x:c r="I47" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.4829575505614513</x:v>
       </x:c>
       <x:c r="J47" s="51" t="str">
         <x:v>N/D</x:v>
@@ -6171,7 +6188,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X47" s="23" t="str">
-        <x:v>Não padronizado/NPL</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y47" s="23" t="str">
         <x:v>Outros</x:v>
@@ -6180,40 +6197,40 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA47" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB47" s="23" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC47" s="23" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD47" s="23" t="str">
-        <x:v>Não padronizado/NPL</x:v>
-      </x:c>
-      <x:c r="AE47" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE47" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF47" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG47" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH47" s="23" t="str">
-        <x:v>IVO DO FUNDO. O OBJETIVO DO FUNDO E PROPORCIONAR AOS SEUS COTISTAS A VALORIZACAO DE SUAS COTAS, NO LONGO PRAZO, POR MEIO DA APLICACAO DOS RECURSOS DO FUNDO, PREPONDERANTEMENTE, NA AQUISICAO DE CARTEIRAS DE DIREITOS CREDITORIOS NAO-PADRONIZADOS, VENCIDOS E NAO PAGOS QUANDO DE SUA CESSAO PARA O FUNDO, CONFORME A POLITICA DE INVESTIMENTO DESTE REGULAMENTO. 7.2 CRITERIOS MINIMOS . OS DIREITOS CREDITORIOS DEVERAO OBEDECER PELO MENOS UM DOS CRITERIOS ABAIXO: (I) SER ORIGINADOS DE OPERACOES FINANCEIRAS, COMERCIAIS, IMOBILIARIAS, DE PRESTACOES DE SERVICOS, DE ARRENDAMENTO MERCANTIL E/OU INDUSTRIAIS REALIZADAS POR INSTITUICOES FINANCEIRAS E OUTRAS SOCIEDADES ATUANTES NO MERCADO BRASILEIRO NOS SEGMENTOS ANTERIORMENTE REFERIDOS; (II) SER DECORRENTES DE RECEITAS PUBLICAS ORI</x:v>
+        <x:v>O documento está em nome de CTG FIDC para o mesmo CNPJ e admite direitos e títulos de crédito, valores mobiliários de crédito, certificados de recebíveis ou securitização e cotas de FIDC; a descrição específica remete a Anexo Descritivo ausente.</x:v>
       </x:c>
       <x:c r="AI47" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26405883000103</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=40801446000130</x:v>
       </x:c>
       <x:c r="AJ47" s="23" t="str">
-        <x:v>Regulamento id 787165</x:v>
+        <x:v>1220023</x:v>
       </x:c>
       <x:c r="AK47" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL47" s="23" t="str">
-        <x:v>p. 9 — política/definição do lastro</x:v>
+        <x:v>regulamento 1220023 p. 43</x:v>
       </x:c>
       <x:c r="AM47" s="23" t="str">
         <x:v>N/D</x:v>
@@ -6236,22 +6253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D48" s="38" t="n">
-        <x:v>29492605000129</x:v>
+        <x:v>52256912000122</x:v>
       </x:c>
       <x:c r="E48" s="24" t="str">
-        <x:v>29.492.605/0001-29</x:v>
+        <x:v>52.256.912/0001-22</x:v>
       </x:c>
       <x:c r="F48" s="24" t="str">
-        <x:v>GAZIN FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MULTISSEGMENTOS - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS ACR I BANCOS EMISSORES DE CARTÃO DE CRÉDITO RESP LIMI</x:v>
       </x:c>
       <x:c r="G48" s="44" t="n">
-        <x:v>2494236413.23</x:v>
+        <x:v>2575168330.09</x:v>
       </x:c>
       <x:c r="H48" s="50" t="n">
-        <x:v>0.0030367094552159433</x:v>
+        <x:v>0.003049685407255447</x:v>
       </x:c>
       <x:c r="I48" s="50" t="n">
-        <x:v>0.6759511157308264</x:v>
+        <x:v>0.0876860137103579</x:v>
       </x:c>
       <x:c r="J48" s="50" t="str">
         <x:v>N/D</x:v>
@@ -6296,49 +6313,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X48" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="Y48" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z48" s="24" t="str">
-        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA48" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB48" s="24" t="str">
-        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC48" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD48" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE48" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
+      </x:c>
+      <x:c r="AE48" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF48" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG48" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH48" s="24" t="str">
-        <x:v>A política admite recebíveis documentados por NF-e e NFC-e e créditos representados por CCBs em múltiplos segmentos econômicos. O enquadramento oficial multicarteira é aderente.</x:v>
+        <x:v>Os direitos creditórios são detidos pela credenciadora/cedente contra bancos emissores de cartões, no fluxo financeiro dos arranjos de pagamento.</x:v>
       </x:c>
       <x:c r="AI48" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=29492605000129</x:v>
+        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
       </x:c>
       <x:c r="AJ48" s="24" t="str">
-        <x:v>1117213</x:v>
+        <x:v>chat_task_acquiring_2026_07_31</x:v>
       </x:c>
       <x:c r="AK48" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL48" s="24" t="str">
-        <x:v>p. 30 — política/definição do lastro</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM48" s="24" t="str">
         <x:v>N/D</x:v>
@@ -6361,22 +6378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D49" s="39" t="n">
-        <x:v>50095909000149</x:v>
+        <x:v>38314763000180</x:v>
       </x:c>
       <x:c r="E49" s="23" t="str">
-        <x:v>50.095.909/0001-49</x:v>
+        <x:v>38.314.763/0001-80</x:v>
       </x:c>
       <x:c r="F49" s="23" t="str">
-        <x:v>VITA AUTO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>SOMA III FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G49" s="45" t="n">
-        <x:v>2489750068.19</x:v>
+        <x:v>2567223636.65</x:v>
       </x:c>
       <x:c r="H49" s="51" t="n">
-        <x:v>0.0030312473721792006</x:v>
+        <x:v>0.0030402767735106234</x:v>
       </x:c>
       <x:c r="I49" s="51" t="n">
-        <x:v>0.0723606913022373</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J49" s="51" t="str">
         <x:v>N/D</x:v>
@@ -6424,16 +6441,16 @@
         <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y49" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z49" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA49" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB49" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AC49" s="23" t="str">
         <x:v>Multissetorial / Outros</x:v>
@@ -6441,29 +6458,29 @@
       <x:c r="AD49" s="23" t="str">
         <x:v>Multicarteira outros</x:v>
       </x:c>
-      <x:c r="AE49" s="23" t="str">
-        <x:v>N/D</x:v>
+      <x:c r="AE49" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF49" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG49" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH49" s="23" t="str">
-        <x:v>E PELAS CONCESSIONARIAS NA CONTA CORRENTE DE TITULARIDADE DA CLASSE, POR MEIO DE BOLETO BANCARIO. 9 POLITICA DE INVESTIMENTO 9.1 OS INVESTIMENTOS D A CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”). 9.2 A CLASSE E VOLTAD A, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS, ORIUNDOS DA VENDA DE VEICULOS A PRAZO DO CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 9.2.1 A CLASSE E CLASSIFICADA COMO UMA CLASSE DE FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS DO TIPO ANBIMA "AGRO, INDUSTRIA E COMERCIO", COM FOCO DE ATUACAO EM "RECEBIVEIS COMERCIAIS", NOS TERMOS DO “CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS” EDITADO PELA ANBIMA E EM VIGOR NESTA DATA. 9.2.2 A CLASSE DEVERA MANTER, EM ATE 180 (CENTO E OITENTA ) DIAS, A PARTIR DO INICIO DE SUAS ATIVI</x:v>
+        <x:v>ENCIA DOS DIREITOS CREDITORIOS E ATENDIMENTO AOS CRITERIOS DE ELEGIBILIDADE DO ANEXO I-A; E (III) A POLITICA DE INVESTIMENTO PREVISTA NESTE CAPITULO 2 DESTE ANEXO I-A. 2.6.3. CADA CEDENTE OU ENDOSSANTE, CONFORME O CASO, E RESPONSAVEL PELA EXISTENCIA, VERACIDADE E CORRETA FORMALIZACAO DOS RESPECTIVOS DIREITOS CREDITORIOS ADQUIRIDOS, NOS TERMOS DA LEGISLACAO APLICAVEL, DESTE REGULAMENTO E DOS RESPECTIVOS DOCUMENTOS COMPROBATORIOS. 2.6.4. OS TERMOS DE TRANSFERENCIA DOS DIREITOS CREDITORIOS ADQUIRIDOS NAO SERAO REGISTRADOS NOS CARTORIOS DE REGISTROS DE TITULOS E DOCUMENTOS. 2.7. O PROCESSO DE ORIGINACAO DOS DIREITOS CREDITORIOS E A POLITICA DE CREDITO ENCONTRAM-SE DESCRITOS NO ANEXO I-B A ESTE REGULAMENTO. 2.8. UMA VEZ REALIZADO A CESSAO OU O ENDOSSO , CONFORME O CASO, DOS DIREITOS CREDITORIOS ADQUIRIDOS, A AMORT</x:v>
       </x:c>
       <x:c r="AI49" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=50095909000149</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=38314763000180</x:v>
       </x:c>
       <x:c r="AJ49" s="23" t="str">
-        <x:v>1074512</x:v>
+        <x:v>1238855</x:v>
       </x:c>
       <x:c r="AK49" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL49" s="23" t="str">
-        <x:v>p. 40</x:v>
+        <x:v>p. 19</x:v>
       </x:c>
       <x:c r="AM49" s="23" t="str">
         <x:v>N/D</x:v>
@@ -6486,22 +6503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D50" s="38" t="n">
-        <x:v>26142862000142</x:v>
+        <x:v>50095909000149</x:v>
       </x:c>
       <x:c r="E50" s="24" t="str">
-        <x:v>26.142.862/0001-42</x:v>
+        <x:v>50.095.909/0001-49</x:v>
       </x:c>
       <x:c r="F50" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CLUBCARD VAREJO - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>VITA AUTO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G50" s="44" t="n">
-        <x:v>2470380152.66</x:v>
+        <x:v>2543457792.98</x:v>
       </x:c>
       <x:c r="H50" s="50" t="n">
-        <x:v>0.0030076646815710905</x:v>
+        <x:v>0.0030121316826501043</x:v>
       </x:c>
       <x:c r="I50" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0760103608607955</x:v>
       </x:c>
       <x:c r="J50" s="50" t="str">
         <x:v>N/D</x:v>
@@ -6549,16 +6566,16 @@
         <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y50" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z50" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA50" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB50" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC50" s="24" t="str">
         <x:v>Multissetorial / Outros</x:v>
@@ -6566,29 +6583,29 @@
       <x:c r="AD50" s="24" t="str">
         <x:v>Multicarteira outros</x:v>
       </x:c>
-      <x:c r="AE50" s="26" t="b">
-        <x:v>0</x:v>
+      <x:c r="AE50" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF50" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG50" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH50" s="24" t="str">
-        <x:v>A política admite direitos creditórios e títulos de naturezas diversas, operações de securitização e cotas de FIDC. O mandato sustenta Multicarteira Financeiro.</x:v>
+        <x:v>E PELAS CONCESSIONARIAS NA CONTA CORRENTE DE TITULARIDADE DA CLASSE, POR MEIO DE BOLETO BANCARIO. 9 POLITICA DE INVESTIMENTO 9.1 OS INVESTIMENTOS D A CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”). 9.2 A CLASSE E VOLTAD A, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS, ORIUNDOS DA VENDA DE VEICULOS A PRAZO DO CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 9.2.1 A CLASSE E CLASSIFICADA COMO UMA CLASSE DE FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS DO TIPO ANBIMA "AGRO, INDUSTRIA E COMERCIO", COM FOCO DE ATUACAO EM "RECEBIVEIS COMERCIAIS", NOS TERMOS DO “CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS” EDITADO PELA ANBIMA E EM VIGOR NESTA DATA. 9.2.2 A CLASSE DEVERA MANTER, EM ATE 180 (CENTO E OITENTA ) DIAS, A PARTIR DO INICIO DE SUAS ATIVI</x:v>
       </x:c>
       <x:c r="AI50" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26142862000142</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=50095909000149</x:v>
       </x:c>
       <x:c r="AJ50" s="24" t="str">
-        <x:v>1166301</x:v>
+        <x:v>1074512</x:v>
       </x:c>
       <x:c r="AK50" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL50" s="24" t="str">
-        <x:v>p. 36 — política/definição do lastro</x:v>
+        <x:v>p. 40</x:v>
       </x:c>
       <x:c r="AM50" s="24" t="str">
         <x:v>N/D</x:v>
@@ -6611,22 +6628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D51" s="39" t="n">
-        <x:v>38314763000180</x:v>
+        <x:v>59356753000187</x:v>
       </x:c>
       <x:c r="E51" s="23" t="str">
-        <x:v>38.314.763/0001-80</x:v>
+        <x:v>59.356.753/0001-87</x:v>
       </x:c>
       <x:c r="F51" s="23" t="str">
-        <x:v>SOMA III FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>ER - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G51" s="45" t="n">
-        <x:v>2464460565.77</x:v>
+        <x:v>2539517617.4</x:v>
       </x:c>
       <x:c r="H51" s="51" t="n">
-        <x:v>0.003000457640015412</x:v>
+        <x:v>0.003007465464978839</x:v>
       </x:c>
       <x:c r="I51" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J51" s="51" t="str">
         <x:v>N/D</x:v>
@@ -6671,25 +6688,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X51" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Energia/infra</x:v>
       </x:c>
       <x:c r="Y51" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z51" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Infraestrutura</x:v>
       </x:c>
       <x:c r="AA51" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB51" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Infraestrutura</x:v>
       </x:c>
       <x:c r="AC51" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Infra/Energia</x:v>
       </x:c>
       <x:c r="AD51" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Energia/infra</x:v>
       </x:c>
       <x:c r="AE51" s="27" t="b">
         <x:v>0</x:v>
@@ -6701,19 +6718,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH51" s="23" t="str">
-        <x:v>ENCIA DOS DIREITOS CREDITORIOS E ATENDIMENTO AOS CRITERIOS DE ELEGIBILIDADE DO ANEXO I-A; E (III) A POLITICA DE INVESTIMENTO PREVISTA NESTE CAPITULO 2 DESTE ANEXO I-A. 2.6.3. CADA CEDENTE OU ENDOSSANTE, CONFORME O CASO, E RESPONSAVEL PELA EXISTENCIA, VERACIDADE E CORRETA FORMALIZACAO DOS RESPECTIVOS DIREITOS CREDITORIOS ADQUIRIDOS, NOS TERMOS DA LEGISLACAO APLICAVEL, DESTE REGULAMENTO E DOS RESPECTIVOS DOCUMENTOS COMPROBATORIOS. 2.6.4. OS TERMOS DE TRANSFERENCIA DOS DIREITOS CREDITORIOS ADQUIRIDOS NAO SERAO REGISTRADOS NOS CARTORIOS DE REGISTROS DE TITULOS E DOCUMENTOS. 2.7. O PROCESSO DE ORIGINACAO DOS DIREITOS CREDITORIOS E A POLITICA DE CREDITO ENCONTRAM-SE DESCRITOS NO ANEXO I-B A ESTE REGULAMENTO. 2.8. UMA VEZ REALIZADO A CESSAO OU O ENDOSSO , CONFORME O CASO, DOS DIREITOS CREDITORIOS ADQUIRIDOS, A AMORT</x:v>
+        <x:v>A Âmbar é credora original e cedente dos recebíveis CER devidos pela CCEE.</x:v>
       </x:c>
       <x:c r="AI51" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=38314763000180</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=59356753000187</x:v>
       </x:c>
       <x:c r="AJ51" s="23" t="str">
-        <x:v>1238855</x:v>
+        <x:v>1001065</x:v>
       </x:c>
       <x:c r="AK51" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL51" s="23" t="str">
-        <x:v>p. 19</x:v>
+        <x:v>p. 68 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM51" s="23" t="str">
         <x:v>N/D</x:v>
@@ -6736,19 +6753,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D52" s="38" t="n">
-        <x:v>59356753000187</x:v>
+        <x:v>26142862000142</x:v>
       </x:c>
       <x:c r="E52" s="24" t="str">
-        <x:v>59.356.753/0001-87</x:v>
+        <x:v>26.142.862/0001-42</x:v>
       </x:c>
       <x:c r="F52" s="24" t="str">
-        <x:v>ER - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CLUBCARD VAREJO - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G52" s="44" t="n">
-        <x:v>2463356625.53</x:v>
+        <x:v>2531012852.93</x:v>
       </x:c>
       <x:c r="H52" s="50" t="n">
-        <x:v>0.0029991136031201847</x:v>
+        <x:v>0.002997393557914263</x:v>
       </x:c>
       <x:c r="I52" s="50" t="n">
         <x:v>0</x:v>
@@ -6796,25 +6813,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X52" s="24" t="str">
-        <x:v>Energia/infra</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y52" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z52" s="24" t="str">
-        <x:v>Infraestrutura</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA52" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB52" s="24" t="str">
-        <x:v>Infraestrutura</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC52" s="24" t="str">
-        <x:v>Infra/Energia</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD52" s="24" t="str">
-        <x:v>Energia/infra</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE52" s="26" t="b">
         <x:v>0</x:v>
@@ -6826,19 +6843,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH52" s="24" t="str">
-        <x:v>A Âmbar é credora original e cedente dos recebíveis CER devidos pela CCEE.</x:v>
+        <x:v>A política admite direitos creditórios e títulos de naturezas diversas, operações de securitização e cotas de FIDC. O mandato sustenta Multicarteira Financeiro.</x:v>
       </x:c>
       <x:c r="AI52" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=59356753000187</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26142862000142</x:v>
       </x:c>
       <x:c r="AJ52" s="24" t="str">
-        <x:v>1001065</x:v>
+        <x:v>1166301</x:v>
       </x:c>
       <x:c r="AK52" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL52" s="24" t="str">
-        <x:v>p. 68 — política/definição do lastro</x:v>
+        <x:v>p. 36 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM52" s="24" t="str">
         <x:v>N/D</x:v>
@@ -6861,22 +6878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D53" s="39" t="n">
-        <x:v>63662224000189</x:v>
+        <x:v>59929098000109</x:v>
       </x:c>
       <x:c r="E53" s="23" t="str">
-        <x:v>63.662.224/0001-89</x:v>
+        <x:v>59.929.098/0001-09</x:v>
       </x:c>
       <x:c r="F53" s="23" t="str">
-        <x:v>FIDC SANTANDER AUTO LOANS I SEGMENTO FINANCEIRO - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CREDITAS AUTO XII</x:v>
       </x:c>
       <x:c r="G53" s="45" t="n">
-        <x:v>2430490971.94</x:v>
+        <x:v>2498979874.47</x:v>
       </x:c>
       <x:c r="H53" s="51" t="n">
-        <x:v>0.0029590999779164047</x:v>
+        <x:v>0.00295945797684218</x:v>
       </x:c>
       <x:c r="I53" s="51" t="n">
-        <x:v>0.1332185833742618</x:v>
+        <x:v>0.2593848573902249</x:v>
       </x:c>
       <x:c r="J53" s="51" t="str">
         <x:v>N/D</x:v>
@@ -6924,10 +6941,10 @@
         <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="Y53" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z53" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA53" s="23" t="str">
         <x:v>Financeiro</x:v>
@@ -6941,29 +6958,29 @@
       <x:c r="AD53" s="23" t="str">
         <x:v>Auto/Veículos</x:v>
       </x:c>
-      <x:c r="AE53" s="23" t="str">
-        <x:v>N/D</x:v>
+      <x:c r="AE53" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF53" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG53" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH53" s="23" t="str">
-        <x:v>MEIO DA B3, HIPOTESE EM QUE SERAO CONSIDERADOS DIAS UTEIS TODOS OS DIAS EXCETO FERIADO NACIONAL, SABADO OU DOMINGO OU DATA EM QUE, POR QUALQUER MOTIVO, NAO HAJA EXPEDIENTE NA B3. “DIREITOS CREDITORIOS”: SIGNIFICAM OS DIREITOS CREDITORIOS VINCULADOS AOS CCCBS ELEGIVEIS ADQUIRIDOS PELA CLASSE A QUE, POR SUA VEZ, ESTAO RELACIONADOS AS CCBS VINCULADAS, QUE REPRESENTAM CREDITOS DECORRENTES DE OPERACOES DE FINANCIAMENTO DE VEICULOS AUTOMOTORES A DEVEDORES, INCLUINDO AQUELES DECORRENTES DOS DEMAIS DIREITOS, DOCUSIGN ENVELOPE ID: 21CD02BF-005B-8612-80FE-9AE34DBAC3E9</x:v>
+        <x:v>regulamento 1251746 p. 20 [classificação ANBIMA declarada no regulamento]: OS DE TERCEIROS, DA ANBIMA, A CLASSE CLASSIFICA -SE COMO TIPO “FINANCEIRO”, COM FOCO DE ATUACAO “FINANCIAMENTO DE VEICULOS”. CAPITULO II - DO OBJETIVO DA CLASSE E DA POLITICA DE INVESTIMENTO || regulamento 1251746 p. 20 [financiamento de veículos]: ANEXO COMPLEMENTAR V DAS REGRAS E PROCEDIMENTOS DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS, DA ANBIMA, A CLASSE CLASSIFICA -SE COMO TIPO “FINANCEIRO”, COM FOCO DE ATUACAO “FINANCIAMENTO DE VEICULOS”. CAPITULO II - DO OBJETIVO DA CLASSE E DA POLITICA DE INVESTIMENTO | regulamento 1251746 p. 68 [créditos inadimplidos / NPL]: NDO ESTE, INCLUSIVE, INCORRER EM CUSTOS COM O FIM DE RECUPERAR OS SEUS CREDITOS. O NAO -PAGAMENTO DAS OPERA COES INTEGRANTES DA CARTEIRA DA CLASSE E OS CUSTOS ADMINISTRATIVOS E DE RECUPERACAO DE CREDITOS DA CLASSE PODERAO FAZER COM QUE A CLASSE SOFRA UMA PERDA PATRIMONIAL SIGNIFICATIVA, O QUE AFETARIA NEGATIVAMENTE A RENTABILIDADE DAS COTAS. 17.1.10. FATORES MACROECONOMICOS . COMO A CLASSE APLICARA SEUS RECURSOS PREPONDERANTEMENTE EM DIREITOS CREDITORIOS, O PAGAMENTO DAS AMORTIZACOES E RENTABILIDADE AOS COTISTAS DEPEN | regulamento 1251746 p. 103 [banco emissor / cartão de crédito]: DIMENTO ORDINARIO DE PAGAMENTO DOS DIREITOS OS DIREITOS CREDITORIOS SAO PAGOS NORMALMENTE POR MEIO DE BOLETOS BANCARIOS, ENVIADOS AOS DEVEDORES, EM FAVOR DA CLASSE, OU POR MEIO DE CARTAO DE CREDITO E/OU CARTAO DE DEBITO, OU POR MEIO DE PIX, TRANSFERENCIA ELETRONICA DISPONIVEL – TED OU QUALQUER OUTRO MEIO DE TRANSFERENCIA OU PAGAMENTO DIRETAMENTE PARA UMA CONTA DE COBRANCA PARA A CONTA DA CLASSE, OU PARA UMA CONTA VINCULADA MANTIDA E GERENCIADA POR AGENTE DE RECEBIMENTO COM A FINALIDADE ESPECIFICA DE RECEBER PAGA</x:v>
       </x:c>
       <x:c r="AI53" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=63662224000189</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=59929098000109</x:v>
       </x:c>
       <x:c r="AJ53" s="23" t="str">
-        <x:v>1240697</x:v>
+        <x:v>1251746</x:v>
       </x:c>
       <x:c r="AK53" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL53" s="23" t="str">
-        <x:v>p. 20 — política/definição do lastro</x:v>
+        <x:v>regulamento 1251746 p. 20; regulamento 1251746 p. 20, regulamento 1251746 p. 68, regulamento 1251746 p. 103</x:v>
       </x:c>
       <x:c r="AM53" s="23" t="str">
         <x:v>N/D</x:v>
@@ -6986,22 +7003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D54" s="38" t="n">
-        <x:v>60528786000146</x:v>
+        <x:v>61652768000134</x:v>
       </x:c>
       <x:c r="E54" s="24" t="str">
-        <x:v>60.528.786/0001-46</x:v>
+        <x:v>61.652.768/0001-34</x:v>
       </x:c>
       <x:c r="F54" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AGIBANK I RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DRIVER MASTER BRASIL I - RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G54" s="44" t="n">
-        <x:v>2374382918.49</x:v>
+        <x:v>2464338064.69</x:v>
       </x:c>
       <x:c r="H54" s="50" t="n">
-        <x:v>0.002890788948728625</x:v>
+        <x:v>0.0029184328444139276</x:v>
       </x:c>
       <x:c r="I54" s="50" t="n">
-        <x:v>0.1522959202306858</x:v>
+        <x:v>0.180905841005734</x:v>
       </x:c>
       <x:c r="J54" s="50" t="str">
         <x:v>N/D</x:v>
@@ -7046,25 +7063,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X54" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="Y54" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z54" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AA54" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB54" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AC54" s="24" t="str">
         <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD54" s="24" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="AE54" s="26" t="b">
         <x:v>0</x:v>
@@ -7076,19 +7093,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH54" s="24" t="str">
-        <x:v>E ORIGINACAO DE DIREITOS CREDITORIOS PODERA AFETAR NEGATIVAMENTE A CAPACIDADE DO FUNDO DE PAGAMENTO DA META DE RENTABILIDADE. O FUNDO ADQUIRIRA DIREITOS CREDITORIOS DECORRENTES DE EMPRESTIMOS CONSIGNADOS ORIGINADOS E/OU ADQUIRIDOS PELO ENDOSSANTE, CONFORME TERMOS E CONDICOES PREVISTOS NO CONTRATO DE ENDOSSO. DESSA FORMA, AS ATIVIDADES DO FUNDO ESTARAO ASSIM CONDICIONADAS A CONT INUIDADE DAS OPERACOES DO ENDOSSANTE E, NOTADAMENTE, A SUA CAPACIDADE DE ORIGINACAO E/OU AQUISICAO E TRANSFERENC IA DOS DIREITOS CREDITORIOS. O FUNDO NAO TEM QUALQUER CONTROLE OU INGERENCIA SOBRE A ORIGINACAO DOS DIREITOS CREDITORIOS, A QUAL E CONDUZIDA PELO ENDOSSANTE, DE ACORDO COM CRITERIOS E POLITICAS PROPRIAS DO ENDOSSANTE. O ENDOSSANT</x:v>
+        <x:v>IFICADO E VALIDADO PELO CUSTODIANTE NO DIA UTIL IMEDIATAMENTE ANTERIOR A DATA DE AQUISICAO, DE ACORDO COM OS SEGUINTES CRITERIOS DE ELEGIBILIDADE: (I) O VALOR NOMINAL AGREGADO DOS DIREITOS CREDITORIOS ADQUIRIDOS DECORRENTES DE CEDULAS DE CREDITO BANCARIO DE UM UNICO DEVEDOR NAO PODERA EXCEDER R$ 250.000,00 (DUZENTOS E CINQUENTA MIL REAIS); (II) OS DIREITOS CREDITORIOS SOMENTE SERAO REFERENTES AS CEDULAS DE CREDITO BANCARIO RELATIVAS AO FINANCIAMENTO DE VEICULOS NA MODALIDADE DE CREDITO DIRETO AO CONSUMIDOR (CDC – VEICULOS), DESDE QUE AS CEDULAS DE CREDITO BANCARIO RELATIVAS AO FINANCIAMENTO DE VEICULOS SEMINOVOS CORRESPONDAM A, NO MAXIMO, 15,0% (QUINZE POR CENTO) DE TODOS OS DIREITOS CREDITORIOS ADQUIRIDOS PELA CLASSE; (III) OS DIREITOS CREDITORIOS DEVEM SER DE DEVEDORES QUE NAO APRESENTEM, NO MOMENTO DA COMPRA PELO FUNDO, OUTROS DIREITOS CREDITORIOS ADQUIRIDOS ACUMULADOS E NAO PAGOS AO FUNDO; (IV) CONSIDERANDO A CESSAO PROPOSTA PRO FORMA, OS DIREITOS CREDITORIOS ADQUIRIDOS QUE COMPOEM A CARTEIRA DO FUNDO TERAO APENAS PARCELAS MENS</x:v>
       </x:c>
       <x:c r="AI54" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=60528786000146</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=61652768000134</x:v>
       </x:c>
       <x:c r="AJ54" s="24" t="str">
-        <x:v>1239450</x:v>
+        <x:v>1044627</x:v>
       </x:c>
       <x:c r="AK54" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL54" s="24" t="str">
-        <x:v>p. 76 — política/definição do lastro</x:v>
+        <x:v>p. 35 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM54" s="24" t="str">
         <x:v>N/D</x:v>
@@ -7120,10 +7137,10 @@
         <x:v>AGRO FLEX FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G55" s="45" t="n">
-        <x:v>2352850421.12</x:v>
+        <x:v>2420168048.15</x:v>
       </x:c>
       <x:c r="H55" s="51" t="n">
-        <x:v>0.0028645733349996864</x:v>
+        <x:v>0.002866123776573084</x:v>
       </x:c>
       <x:c r="I55" s="51" t="n">
         <x:v>0</x:v>
@@ -7236,22 +7253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D56" s="38" t="n">
-        <x:v>42358004000196</x:v>
+        <x:v>60010416000112</x:v>
       </x:c>
       <x:c r="E56" s="24" t="str">
-        <x:v>42.358.004/0001-96</x:v>
+        <x:v>60.010.416/0001-12</x:v>
       </x:c>
       <x:c r="F56" s="24" t="str">
-        <x:v>ACONCÁGUA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>MT CONSIGNADO PRIVADO I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G56" s="44" t="n">
-        <x:v>2341582512.2</x:v>
+        <x:v>2402205778.31</x:v>
       </x:c>
       <x:c r="H56" s="50" t="n">
-        <x:v>0.002850854761501048</x:v>
+        <x:v>0.0028448516633787133</x:v>
       </x:c>
       <x:c r="I56" s="50" t="n">
-        <x:v>1</x:v>
+        <x:v>0.0864587494545391</x:v>
       </x:c>
       <x:c r="J56" s="50" t="str">
         <x:v>N/D</x:v>
@@ -7296,49 +7313,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X56" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="Y56" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z56" s="24" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA56" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB56" s="24" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC56" s="24" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD56" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE56" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE56" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF56" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG56" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH56" s="24" t="str">
-        <x:v>E/OU DA GESTORA, OU DE QUALQUER MECANISMO DE SEGURO OU, AINDA NO FUNDO GARANTIDOR DE CREDITOS - FGC POLITICA DE INVESTIMENTO OS DIREITOS CREDITORIOS QUE INTEGRARAO A CARTEIRA D A CLASSE CONSISTEM NAQUELES ORIGINADOS DE ACOES JUDICIAIS MOVIDAS POR COMPANHIA USINA CAMBAHYBA, COMPANHIA USINA DO OUTEIRO, USINA SAO JOAO B LYZANDRO S.A E COMPANHIA ACUCAREIRA PARAISO – EM RECUPERACAO JUDICIAL CONTRA A UNIAO FEDERAL DO BRASIL, NA POSICAO DE SUCESSORA DO ANTIGO INSTITUTO DO ACUCAR E DO ALCOOL, POR MEIO DAS QUAIS CADA CEDENTE PLEITEIA INDENIZACAO PELOS PREJUIZOS PATRIMONIAIS DECORRENTES DA FIXACAO DE PRECOS DOS PRODUTOS DO SETOR SUCROALCOOLEIRO ABAIXO DOS RESPECTIVOS CUSTOS MEDIOS DE PRODUCAO, EM DESACORDO COM A LEI FEDERAL NO 4.870/1965 (“ACOES JUDICIAIS”). OS DIREITOS CREDITORIOS TEM ORIGEM NAS RESPECTIVAS ACOES JUDI</x:v>
+        <x:v>S DIREITOS CREDITORIOS SERAO ADQUIRIDOS PELA CLASSE SEMPRE DE ACORDO COM A PRESENTE POLITICA DE INVESTIMENTOS. 4.2 OS DIREITOS CREDITORIOS SAO ORIGINADOS NO AMBITO DE OPERACOES DE EMPRESTIMO CONSIGNADO CONCEDIDO PELO ENDOSSANTE A UM DEVEDOR POR MEIO DA PLATAFORMA MT E REPRESENTADO POR CCB, DEVIDAMENTE FORMALIZADA POR VIA ELETRONICA, DE ACORDO COM A LEGISLACAO APLICAVEL, OBSERVADA A POLITICA DE CREDITO CONSTANTE DO CONTRATO DE ENDOSSO. O ENDOSSANTE CELEBROU O CONVENIO CONSIGNADO PRIVADO PREVIAMENTE AO ENDOSSO DE DIREITOS CREDITORIOS ELEGIVEIS A CLASSE, PARA QUE, APOS A AVERBACAO DOS DIREITOS CREDITORIOS NA DATAPREV, O PAGAMENTO REGULAR DOS DIREITOS CREDITORIOS DECORRENTES DAS CCB SEJA FEITO POR CONSIGNACAO E/OU D</x:v>
       </x:c>
       <x:c r="AI56" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=42358004000196</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=60010416000112</x:v>
       </x:c>
       <x:c r="AJ56" s="24" t="str">
-        <x:v>777021</x:v>
+        <x:v>1051393</x:v>
       </x:c>
       <x:c r="AK56" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL56" s="24" t="str">
-        <x:v>p. 37</x:v>
+        <x:v>p. 9 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM56" s="24" t="str">
         <x:v>N/D</x:v>
@@ -7361,22 +7378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D57" s="39" t="n">
-        <x:v>55720253000121</x:v>
+        <x:v>60528786000146</x:v>
       </x:c>
       <x:c r="E57" s="23" t="str">
-        <x:v>55.720.253/0001-21</x:v>
+        <x:v>60.528.786/0001-46</x:v>
       </x:c>
       <x:c r="F57" s="23" t="str">
-        <x:v>ITAL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS RESPONSABILIDADE ILIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AGIBANK I RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G57" s="45" t="n">
-        <x:v>2302518318.66</x:v>
+        <x:v>2373894609.18</x:v>
       </x:c>
       <x:c r="H57" s="51" t="n">
-        <x:v>0.0028032944720056013</x:v>
+        <x:v>0.0028113236961583785</x:v>
       </x:c>
       <x:c r="I57" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0.1527059368171675</x:v>
       </x:c>
       <x:c r="J57" s="51" t="str">
         <x:v>N/D</x:v>
@@ -7421,25 +7438,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X57" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="Y57" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z57" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA57" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB57" s="23" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC57" s="23" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD57" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="AE57" s="27" t="b">
         <x:v>0</x:v>
@@ -7451,19 +7468,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH57" s="23" t="str">
-        <x:v>regulamento 1198083 p. 27 [precatórios e requisitórios contra entes públicos]: ACAO DO RESPECTIVO CEDENTE. 5.2.2. OBSERVADO O DISPOSTO NO PRESENTE ANEXO, A CLASSE PODERA ADQUIRIR DO(S) CEDENTE(S) DIREITOS CREDITORIOS, TOTAL OU PARCIALMENTE: I –ORIGINARIOS DE PRECATORIOS OU AINDA CREDITOS DECORRENTES DE RECEITAS OU DIVIDAS PUBLICAS ORIGINARIAS OU DERIVADAS DA UNIAO, ESTADOS, DISTRITO FEDERAL E MUNICIPIOS, AUTARQUIAS E FUNDACOES. || CEDENTE/ORIGINADOR: regulamento 1198083 p. 25: CEDENTES: PESSOA JURIDICA E/OU FISICA, IDENTIFICADA PELO SEU NUMERO DE INSCRICAO NO CNPJ/MF OU CPF/MF OU FUNDOS DE</x:v>
+        <x:v>E ORIGINACAO DE DIREITOS CREDITORIOS PODERA AFETAR NEGATIVAMENTE A CAPACIDADE DO FUNDO DE PAGAMENTO DA META DE RENTABILIDADE. O FUNDO ADQUIRIRA DIREITOS CREDITORIOS DECORRENTES DE EMPRESTIMOS CONSIGNADOS ORIGINADOS E/OU ADQUIRIDOS PELO ENDOSSANTE, CONFORME TERMOS E CONDICOES PREVISTOS NO CONTRATO DE ENDOSSO. DESSA FORMA, AS ATIVIDADES DO FUNDO ESTARAO ASSIM CONDICIONADAS A CONT INUIDADE DAS OPERACOES DO ENDOSSANTE E, NOTADAMENTE, A SUA CAPACIDADE DE ORIGINACAO E/OU AQUISICAO E TRANSFERENC IA DOS DIREITOS CREDITORIOS. O FUNDO NAO TEM QUALQUER CONTROLE OU INGERENCIA SOBRE A ORIGINACAO DOS DIREITOS CREDITORIOS, A QUAL E CONDUZIDA PELO ENDOSSANTE, DE ACORDO COM CRITERIOS E POLITICAS PROPRIAS DO ENDOSSANTE. O ENDOSSANT</x:v>
       </x:c>
       <x:c r="AI57" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=55720253000121</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=60528786000146</x:v>
       </x:c>
       <x:c r="AJ57" s="23" t="str">
-        <x:v>1198083</x:v>
+        <x:v>1239450</x:v>
       </x:c>
       <x:c r="AK57" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL57" s="23" t="str">
-        <x:v>regulamento 1198083 p. 27</x:v>
+        <x:v>p. 76 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM57" s="23" t="str">
         <x:v>N/D</x:v>
@@ -7486,22 +7503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D58" s="38" t="n">
-        <x:v>59929098000109</x:v>
+        <x:v>42358004000196</x:v>
       </x:c>
       <x:c r="E58" s="24" t="str">
-        <x:v>59.929.098/0001-09</x:v>
+        <x:v>42.358.004/0001-96</x:v>
       </x:c>
       <x:c r="F58" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CREDITAS AUTO XII</x:v>
+        <x:v>ACONCÁGUA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO PADRONIZADOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G58" s="44" t="n">
-        <x:v>2207591119.67</x:v>
+        <x:v>2373588339.88</x:v>
       </x:c>
       <x:c r="H58" s="50" t="n">
-        <x:v>0.002687721496965598</x:v>
+        <x:v>0.002810960991707572</x:v>
       </x:c>
       <x:c r="I58" s="50" t="n">
-        <x:v>0.2480810505995611</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J58" s="50" t="str">
         <x:v>N/D</x:v>
@@ -7546,25 +7563,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X58" s="24" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y58" s="24" t="str">
         <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z58" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Poder Público</x:v>
       </x:c>
       <x:c r="AA58" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB58" s="24" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Poder Público</x:v>
       </x:c>
       <x:c r="AC58" s="24" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD58" s="24" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE58" s="26" t="b">
         <x:v>0</x:v>
@@ -7576,19 +7593,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH58" s="24" t="str">
-        <x:v>regulamento 1251746 p. 20 [classificação ANBIMA declarada no regulamento]: OS DE TERCEIROS, DA ANBIMA, A CLASSE CLASSIFICA -SE COMO TIPO “FINANCEIRO”, COM FOCO DE ATUACAO “FINANCIAMENTO DE VEICULOS”. CAPITULO II - DO OBJETIVO DA CLASSE E DA POLITICA DE INVESTIMENTO || regulamento 1251746 p. 20 [financiamento de veículos]: ANEXO COMPLEMENTAR V DAS REGRAS E PROCEDIMENTOS DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS, DA ANBIMA, A CLASSE CLASSIFICA -SE COMO TIPO “FINANCEIRO”, COM FOCO DE ATUACAO “FINANCIAMENTO DE VEICULOS”. CAPITULO II - DO OBJETIVO DA CLASSE E DA POLITICA DE INVESTIMENTO | regulamento 1251746 p. 68 [créditos inadimplidos / NPL]: NDO ESTE, INCLUSIVE, INCORRER EM CUSTOS COM O FIM DE RECUPERAR OS SEUS CREDITOS. O NAO -PAGAMENTO DAS OPERA COES INTEGRANTES DA CARTEIRA DA CLASSE E OS CUSTOS ADMINISTRATIVOS E DE RECUPERACAO DE CREDITOS DA CLASSE PODERAO FAZER COM QUE A CLASSE SOFRA UMA PERDA PATRIMONIAL SIGNIFICATIVA, O QUE AFETARIA NEGATIVAMENTE A RENTABILIDADE DAS COTAS. 17.1.10. FATORES MACROECONOMICOS . COMO A CLASSE APLICARA SEUS RECURSOS PREPONDERANTEMENTE EM DIREITOS CREDITORIOS, O PAGAMENTO DAS AMORTIZACOES E RENTABILIDADE AOS COTISTAS DEPEN | regulamento 1251746 p. 103 [banco emissor / cartão de crédito]: DIMENTO ORDINARIO DE PAGAMENTO DOS DIREITOS OS DIREITOS CREDITORIOS SAO PAGOS NORMALMENTE POR MEIO DE BOLETOS BANCARIOS, ENVIADOS AOS DEVEDORES, EM FAVOR DA CLASSE, OU POR MEIO DE CARTAO DE CREDITO E/OU CARTAO DE DEBITO, OU POR MEIO DE PIX, TRANSFERENCIA ELETRONICA DISPONIVEL – TED OU QUALQUER OUTRO MEIO DE TRANSFERENCIA OU PAGAMENTO DIRETAMENTE PARA UMA CONTA DE COBRANCA PARA A CONTA DA CLASSE, OU PARA UMA CONTA VINCULADA MANTIDA E GERENCIADA POR AGENTE DE RECEBIMENTO COM A FINALIDADE ESPECIFICA DE RECEBER PAGA</x:v>
+        <x:v>E/OU DA GESTORA, OU DE QUALQUER MECANISMO DE SEGURO OU, AINDA NO FUNDO GARANTIDOR DE CREDITOS - FGC POLITICA DE INVESTIMENTO OS DIREITOS CREDITORIOS QUE INTEGRARAO A CARTEIRA D A CLASSE CONSISTEM NAQUELES ORIGINADOS DE ACOES JUDICIAIS MOVIDAS POR COMPANHIA USINA CAMBAHYBA, COMPANHIA USINA DO OUTEIRO, USINA SAO JOAO B LYZANDRO S.A E COMPANHIA ACUCAREIRA PARAISO – EM RECUPERACAO JUDICIAL CONTRA A UNIAO FEDERAL DO BRASIL, NA POSICAO DE SUCESSORA DO ANTIGO INSTITUTO DO ACUCAR E DO ALCOOL, POR MEIO DAS QUAIS CADA CEDENTE PLEITEIA INDENIZACAO PELOS PREJUIZOS PATRIMONIAIS DECORRENTES DA FIXACAO DE PRECOS DOS PRODUTOS DO SETOR SUCROALCOOLEIRO ABAIXO DOS RESPECTIVOS CUSTOS MEDIOS DE PRODUCAO, EM DESACORDO COM A LEI FEDERAL NO 4.870/1965 (“ACOES JUDICIAIS”). OS DIREITOS CREDITORIOS TEM ORIGEM NAS RESPECTIVAS ACOES JUDI</x:v>
       </x:c>
       <x:c r="AI58" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=59929098000109</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=42358004000196</x:v>
       </x:c>
       <x:c r="AJ58" s="24" t="str">
-        <x:v>1251746</x:v>
+        <x:v>777021</x:v>
       </x:c>
       <x:c r="AK58" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL58" s="24" t="str">
-        <x:v>regulamento 1251746 p. 20; regulamento 1251746 p. 20, regulamento 1251746 p. 68, regulamento 1251746 p. 103</x:v>
+        <x:v>p. 37</x:v>
       </x:c>
       <x:c r="AM58" s="24" t="str">
         <x:v>N/D</x:v>
@@ -7611,22 +7628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D59" s="39" t="n">
-        <x:v>40801446000130</x:v>
+        <x:v>63662224000189</x:v>
       </x:c>
       <x:c r="E59" s="23" t="str">
-        <x:v>40.801.446/0001-30</x:v>
+        <x:v>63.662.224/0001-89</x:v>
       </x:c>
       <x:c r="F59" s="23" t="str">
-        <x:v>EB VESTA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FIDC SANTANDER AUTO LOANS I SEGMENTO FINANCEIRO - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G59" s="45" t="n">
-        <x:v>2202074010.33</x:v>
+        <x:v>2234066329.65</x:v>
       </x:c>
       <x:c r="H59" s="51" t="n">
-        <x:v>0.002681004468054717</x:v>
+        <x:v>0.0026457297586197893</x:v>
       </x:c>
       <x:c r="I59" s="51" t="n">
-        <x:v>0.5079249203375443</x:v>
+        <x:v>0.1327136681119272</x:v>
       </x:c>
       <x:c r="J59" s="51" t="str">
         <x:v>N/D</x:v>
@@ -7671,25 +7688,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X59" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="Y59" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z59" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA59" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB59" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AC59" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD59" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="AE59" s="23" t="str">
         <x:v>N/D</x:v>
@@ -7701,19 +7718,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH59" s="23" t="str">
-        <x:v>O documento está em nome de CTG FIDC para o mesmo CNPJ e admite direitos e títulos de crédito, valores mobiliários de crédito, certificados de recebíveis ou securitização e cotas de FIDC; a descrição específica remete a Anexo Descritivo ausente.</x:v>
+        <x:v>MEIO DA B3, HIPOTESE EM QUE SERAO CONSIDERADOS DIAS UTEIS TODOS OS DIAS EXCETO FERIADO NACIONAL, SABADO OU DOMINGO OU DATA EM QUE, POR QUALQUER MOTIVO, NAO HAJA EXPEDIENTE NA B3. “DIREITOS CREDITORIOS”: SIGNIFICAM OS DIREITOS CREDITORIOS VINCULADOS AOS CCCBS ELEGIVEIS ADQUIRIDOS PELA CLASSE A QUE, POR SUA VEZ, ESTAO RELACIONADOS AS CCBS VINCULADAS, QUE REPRESENTAM CREDITOS DECORRENTES DE OPERACOES DE FINANCIAMENTO DE VEICULOS AUTOMOTORES A DEVEDORES, INCLUINDO AQUELES DECORRENTES DOS DEMAIS DIREITOS, DOCUSIGN ENVELOPE ID: 21CD02BF-005B-8612-80FE-9AE34DBAC3E9</x:v>
       </x:c>
       <x:c r="AI59" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=40801446000130</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=63662224000189</x:v>
       </x:c>
       <x:c r="AJ59" s="23" t="str">
-        <x:v>1220023</x:v>
+        <x:v>1240697</x:v>
       </x:c>
       <x:c r="AK59" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL59" s="23" t="str">
-        <x:v>regulamento 1220023 p. 43</x:v>
+        <x:v>p. 20 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM59" s="23" t="str">
         <x:v>N/D</x:v>
@@ -7736,19 +7753,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D60" s="38" t="n">
-        <x:v>52651831000127</x:v>
+        <x:v>44229197000100</x:v>
       </x:c>
       <x:c r="E60" s="24" t="str">
-        <x:v>52.651.831/0001-27</x:v>
+        <x:v>44.229.197/0001-00</x:v>
       </x:c>
       <x:c r="F60" s="24" t="str">
-        <x:v>HYUNDAI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>EUV SP1 FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS</x:v>
       </x:c>
       <x:c r="G60" s="44" t="n">
-        <x:v>2187326043.42</x:v>
+        <x:v>2220692700.39</x:v>
       </x:c>
       <x:c r="H60" s="50" t="n">
-        <x:v>0.0026630489565710193</x:v>
+        <x:v>0.0026298918184278013</x:v>
       </x:c>
       <x:c r="I60" s="50" t="n">
         <x:v>0</x:v>
@@ -7799,16 +7816,16 @@
         <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y60" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z60" s="24" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA60" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB60" s="24" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC60" s="24" t="str">
         <x:v>Crédito PJ</x:v>
@@ -7826,19 +7843,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH60" s="24" t="str">
-        <x:v>E ASSUNTO, CEDER OU ORIGINAR, DIRETA OU INDIRETAMENTE, DIREITOS CREDITORIOS AO FUNDO E A CLASSE. 4. POLITICA DE INVESTIMENTO 4.1. OS INVESTIMENTOS DA CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”), SENDO QUE, NOS TERMOS DO ARTIGO 45, PARAGRAFO 7O, INCISO II, DO ANEXO NORMATIVO II DA RESOLUCAO CVM 175, A CLASSE ESTA DISPENSADA DE LIMITAR-SE AOS 20% (VINTE POR CENTO) DE APLICACAO DE RECURSOS EM DIREITOS CREDITORIOS E OUTROS ATIVOS DE RESPONSABILIDADE OU COOBRIGACAO DE UM MESMO DEVEDOR COM RELACAO AO PATRIMONIO LIQUIDO DA CLASSE. 4.2. A CLASSE E VOLTADA, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS, ORIUNDOS DA VENDA DE VEICULOS A PRAZO DA CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 4.3. DE ACORDO COM AS REGRAS E PROCEDIMENTOS ANBIMA PARA CLASSIFICAC</x:v>
+        <x:v>ECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS ELEGIVEIS E/OU ATIVOS FINANCEIROS , OBSERVADOS OS LIMITES E AS RESTRICOES PREVISTAS NA LEGISLACAO VIGENTE E NESTE REGULAMENTO. 4.3. OS DIREITOS CREDITORIOS CONSISTIRAO EM DIREITOS CREDITORIOS PERFORMADOS E/OU NAO PERFORMADOS, ORIUNDOS DE OPERACOES REALIZADAS PELOS CEDENTES NOS SEGMENTOS FINANCEIRO, INDUSTRIAL, COMERCIAL, IMOBILIARIO E/OU DE PRESTACAO DE SERVICOS DE ACORDO COM OS CRITERIOS DE</x:v>
       </x:c>
       <x:c r="AI60" s="24" t="str">
-        <x:v>FundosNet/B3 — regulamento 690896</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=44229197000100</x:v>
       </x:c>
       <x:c r="AJ60" s="24" t="str">
-        <x:v>690896</x:v>
+        <x:v>800235</x:v>
       </x:c>
       <x:c r="AK60" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL60" s="24" t="str">
-        <x:v>p. 47 — venda de veículos a prazo à concessionária</x:v>
+        <x:v>p. 22 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM60" s="24" t="str">
         <x:v>N/D</x:v>
@@ -7861,19 +7878,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D61" s="39" t="n">
-        <x:v>44229197000100</x:v>
+        <x:v>26405883000103</x:v>
       </x:c>
       <x:c r="E61" s="23" t="str">
-        <x:v>44.229.197/0001-00</x:v>
+        <x:v>26.405.883/0001-03</x:v>
       </x:c>
       <x:c r="F61" s="23" t="str">
-        <x:v>EUV SP1 FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS</x:v>
+        <x:v>FIDC MULTISEGMENTOS NPL IPANEMA VI RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G61" s="45" t="n">
-        <x:v>2178946912.58</x:v>
+        <x:v>2207595143.13</x:v>
       </x:c>
       <x:c r="H61" s="51" t="n">
-        <x:v>0.002652847443308943</x:v>
+        <x:v>0.002614380821037927</x:v>
       </x:c>
       <x:c r="I61" s="51" t="n">
         <x:v>0</x:v>
@@ -7921,49 +7938,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X61" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Não padronizado/NPL</x:v>
       </x:c>
       <x:c r="Y61" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z61" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA61" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB61" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC61" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD61" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE61" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Não padronizado/NPL</x:v>
+      </x:c>
+      <x:c r="AE61" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF61" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG61" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH61" s="23" t="str">
-        <x:v>ECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS ELEGIVEIS E/OU ATIVOS FINANCEIROS , OBSERVADOS OS LIMITES E AS RESTRICOES PREVISTAS NA LEGISLACAO VIGENTE E NESTE REGULAMENTO. 4.3. OS DIREITOS CREDITORIOS CONSISTIRAO EM DIREITOS CREDITORIOS PERFORMADOS E/OU NAO PERFORMADOS, ORIUNDOS DE OPERACOES REALIZADAS PELOS CEDENTES NOS SEGMENTOS FINANCEIRO, INDUSTRIAL, COMERCIAL, IMOBILIARIO E/OU DE PRESTACAO DE SERVICOS DE ACORDO COM OS CRITERIOS DE</x:v>
+        <x:v>IVO DO FUNDO. O OBJETIVO DO FUNDO E PROPORCIONAR AOS SEUS COTISTAS A VALORIZACAO DE SUAS COTAS, NO LONGO PRAZO, POR MEIO DA APLICACAO DOS RECURSOS DO FUNDO, PREPONDERANTEMENTE, NA AQUISICAO DE CARTEIRAS DE DIREITOS CREDITORIOS NAO-PADRONIZADOS, VENCIDOS E NAO PAGOS QUANDO DE SUA CESSAO PARA O FUNDO, CONFORME A POLITICA DE INVESTIMENTO DESTE REGULAMENTO. 7.2 CRITERIOS MINIMOS . OS DIREITOS CREDITORIOS DEVERAO OBEDECER PELO MENOS UM DOS CRITERIOS ABAIXO: (I) SER ORIGINADOS DE OPERACOES FINANCEIRAS, COMERCIAIS, IMOBILIARIAS, DE PRESTACOES DE SERVICOS, DE ARRENDAMENTO MERCANTIL E/OU INDUSTRIAIS REALIZADAS POR INSTITUICOES FINANCEIRAS E OUTRAS SOCIEDADES ATUANTES NO MERCADO BRASILEIRO NOS SEGMENTOS ANTERIORMENTE REFERIDOS; (II) SER DECORRENTES DE RECEITAS PUBLICAS ORI</x:v>
       </x:c>
       <x:c r="AI61" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=44229197000100</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=26405883000103</x:v>
       </x:c>
       <x:c r="AJ61" s="23" t="str">
-        <x:v>800235</x:v>
+        <x:v>Regulamento id 787165</x:v>
       </x:c>
       <x:c r="AK61" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL61" s="23" t="str">
-        <x:v>p. 22 — política/definição do lastro</x:v>
+        <x:v>p. 9 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM61" s="23" t="str">
         <x:v>N/D</x:v>
@@ -7986,22 +8003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D62" s="38" t="n">
-        <x:v>57719370000109</x:v>
+        <x:v>42154687000160</x:v>
       </x:c>
       <x:c r="E62" s="24" t="str">
-        <x:v>57.719.370/0001-09</x:v>
+        <x:v>42.154.687/0001-60</x:v>
       </x:c>
       <x:c r="F62" s="24" t="str">
-        <x:v>RSG FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>MULTIPLIKE PLUS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G62" s="44" t="n">
-        <x:v>2140596574.92</x:v>
+        <x:v>2162550453.27</x:v>
       </x:c>
       <x:c r="H62" s="50" t="n">
-        <x:v>0.0026061562666565927</x:v>
+        <x:v>0.002561035906946199</x:v>
       </x:c>
       <x:c r="I62" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.4168932745358105</x:v>
       </x:c>
       <x:c r="J62" s="50" t="str">
         <x:v>N/D</x:v>
@@ -8040,55 +8057,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V62" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicedentes &amp; Multisacados</x:v>
       </x:c>
       <x:c r="W62" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X62" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>FIDC MultiCedente / Multisacado</x:v>
       </x:c>
       <x:c r="Y62" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z62" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA62" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB62" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC62" s="24" t="str">
         <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD62" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE62" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira financeiro</x:v>
+      </x:c>
+      <x:c r="AE62" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF62" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG62" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH62" s="24" t="str">
-        <x:v>regulamento 1098228 p. 18 [crédito corporativo / mercado de capitais]: DO FUNDO. PARAGRAFO UNICO OS DIREITOS CREDITORIOS SERAO INDIVIDUALMENTE REPRESENTADOS POR TITULOS DE CREDITO, COMO DUPLICATAS FISICAS OU ESCRITURAIS, CHEQUES, NOTAS PROMISSORIAS, DEBENTURES, CERTIFICADOS DE RECEBIVEIS, CEDULAS OU NOTAS DE CREDITO (HIPOTECARIA, RURAL, INDUSTRIAL, A EXPORTACAO, COMERCIAL, IMOBILIARIO OU BANCARIO), NOTAS COMERCIAIS, POR CONTRATOS DE COMPRA E VENDA, CONTRATOS DE PRESTACAO DE SERVICOS, CONTRATOS DE LOCACAO, POR FATURA OU NOTA FISCAL, POR AGENDA DE CARTAO DE CREDITO OU NSU (NU | regulamento 1098228 p. 16 [receitas e dívidas do poder público]: ATIVOS; (O) NO CASO DE CLASSE FECHADA, SE FOR O CASO, AS DESPESAS INERENTES A: I) DISTRIBUICAO PRIMARIA DE COTAS; E II) ADMISSAO DAS COTAS A NEGOCIACAO EM MERCADO ORGANIZADO; (P) ROYALTIES DEVIDOS PELO LICENCIAMENTO DE INDICES DE REFERENCIA, DESDE QUE COBRADOS DE ACORDO COM CONTRATO ESTABELECIDO ENTRE O ADMINISTRADOR E A INSTITUICAO QUE DETEM OS DIREITOS SOBRE O INDICE; (Q) TAXAS DE ADMINISTRACAO E DE GESTAO; (R) MONTANTES DEVIDOS A FUNDOS INVESTIDORES NA HIPOTESE DE ACORDO DE REMUNERACAO COM BASE NA TA | regulamento 1098228 p. 18 [recebíveis comerciais / multissetorial]: NTATIVOS DOS DIREITOS CREDITORIOS PELA CONSULTORIA ESPECIALIZADA DO FUNDO. PARAGRAFO UNICO OS DIREITOS CREDITORIOS SERAO INDIVIDUALMENTE REPRESENTADOS POR TITULOS DE CREDITO, COMO DUPLICATAS FISICAS OU ESCRITURAIS, CHEQUES, NOTAS PROMISSORIAS, DEBENTURES, CERTIFICADOS DE RECEBIVEIS, CEDULAS OU NOTAS DE CREDITO (HIPOTECARIA, RURAL, INDUSTRIAL, A EXPORTACAO, COMERCIAL, IMOBILIARIO OU BANCARIO), NOTAS COMERCIAIS, POR CONTRATOS DE COMPRA E VENDA, CONTRATOS DE PRESTACAO DE SERVICOS, CONTRATOS DE LOCACAO, POR F || CEDENTE/ORIGINADOR: regulamento 1098228 p. 20: CEDENTE E SEUS COLATERAIS, POR TODOS OS MEIOS DISPONIVEIS NA LEGISLACAO BRASILEIRA</x:v>
+        <x:v>Direção aprovada: Financeiro / Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AI62" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=57719370000109</x:v>
+        <x:v>FundosNet/B3 — regulamento 1223029</x:v>
       </x:c>
       <x:c r="AJ62" s="24" t="str">
-        <x:v>1098228</x:v>
+        <x:v>1223029</x:v>
       </x:c>
       <x:c r="AK62" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL62" s="24" t="str">
-        <x:v>regulamento 1098228 p. 18, regulamento 1098228 p. 16, regulamento 1098228 p. 18</x:v>
+        <x:v>pp. 23 e 26–29 — ativos elegíveis e garantias</x:v>
       </x:c>
       <x:c r="AM62" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8097,7 +8114,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO62" s="24" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="36" customHeight="1">
@@ -8111,22 +8128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D63" s="39" t="n">
-        <x:v>42154687000160</x:v>
+        <x:v>66929956000180</x:v>
       </x:c>
       <x:c r="E63" s="23" t="str">
-        <x:v>42.154.687/0001-60</x:v>
+        <x:v>66.929.956/0001-80</x:v>
       </x:c>
       <x:c r="F63" s="23" t="str">
-        <x:v>MULTIPLIKE PLUS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>BV AUTO III SEGMENTO FINANCEIRO FIDC RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G63" s="45" t="n">
-        <x:v>2118132225.34</x:v>
+        <x:v>2125721812.65</x:v>
       </x:c>
       <x:c r="H63" s="51" t="n">
-        <x:v>0.0025788061315960105</x:v>
+        <x:v>0.002517420984164066</x:v>
       </x:c>
       <x:c r="I63" s="51" t="n">
-        <x:v>0.4225649486265656</x:v>
+        <x:v>0.1507558774200163</x:v>
       </x:c>
       <x:c r="J63" s="51" t="str">
         <x:v>N/D</x:v>
@@ -8165,55 +8182,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V63" s="23" t="str">
-        <x:v>Multicedentes &amp; Multisacados</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W63" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X63" s="23" t="str">
-        <x:v>FIDC MultiCedente / Multisacado</x:v>
+        <x:v>Auto/Veículos</x:v>
       </x:c>
       <x:c r="Y63" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z63" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA63" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB63" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AC63" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD63" s="23" t="str">
-        <x:v>Multicarteira financeiro</x:v>
-      </x:c>
-      <x:c r="AE63" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Auto/Veículos</x:v>
+      </x:c>
+      <x:c r="AE63" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF63" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG63" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH63" s="23" t="str">
-        <x:v>Direção aprovada: Financeiro / Multicarteira Financeiro</x:v>
+        <x:v>Def. "Devedores": pessoas físicas que adquiriram um Veículo Automotor mediante financiamento concedido pelo Emitente por meio de emissão de CCBs. É financiamento ao consumidor, o oposto do floor plan de montadora.</x:v>
       </x:c>
       <x:c r="AI63" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 1223029</x:v>
+        <x:v>Industria_FIDC_202606_auditada.xlsx#Auditoria classificação Top200</x:v>
       </x:c>
       <x:c r="AJ63" s="23" t="str">
-        <x:v>1223029</x:v>
+        <x:v>Regulamento arquivado no FundosNET</x:v>
       </x:c>
       <x:c r="AK63" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL63" s="23" t="str">
-        <x:v>pp. 23 e 26–29 — ativos elegíveis e garantias</x:v>
+        <x:v>Regulamento arquivado no FundosNET</x:v>
       </x:c>
       <x:c r="AM63" s="23" t="str">
         <x:v>N/D</x:v>
@@ -8222,7 +8239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO63" s="23" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="36" customHeight="1">
@@ -8236,22 +8253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D64" s="38" t="n">
-        <x:v>13321819000100</x:v>
+        <x:v>23216398000101</x:v>
       </x:c>
       <x:c r="E64" s="24" t="str">
-        <x:v>13.321.819/0001-00</x:v>
+        <x:v>23.216.398/0001-01</x:v>
       </x:c>
       <x:c r="F64" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS VALE</x:v>
+        <x:v>MULTIPLICA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G64" s="44" t="n">
-        <x:v>2110355080.85</x:v>
+        <x:v>2090403784.62</x:v>
       </x:c>
       <x:c r="H64" s="50" t="n">
-        <x:v>0.0025693375310727826</x:v>
+        <x:v>0.0024755950291623727</x:v>
       </x:c>
       <x:c r="I64" s="50" t="n">
-        <x:v>0.0370380606480036</x:v>
+        <x:v>0.4527500152326454</x:v>
       </x:c>
       <x:c r="J64" s="50" t="str">
         <x:v>N/D</x:v>
@@ -8296,25 +8313,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X64" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y64" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z64" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA64" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB64" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC64" s="24" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD64" s="24" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="AE64" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8326,19 +8343,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH64" s="24" t="str">
-        <x:v>Os documentos admitem cupons e notas fiscais, CCBs, recebíveis de cartão e renegociações. A diversidade contratual sustenta Multicarteira Outros.</x:v>
+        <x:v>ZACAO DE SUAS COTAS ATRAVES DA APLICACAO PREPONDERANTE DOS RECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS CONFORME POLITICA DE INVESTIMENTO ESTABELECIDA NESTE REGULAMENTO. 11.2. OS DIREITOS CREDITORIOS QUE SERAO ADQUIRIDOS PELO FUNDO PODERAO SER ORIGINADOS EM DIVERSOS SEGMENTOS, SENDO ORIUNDOS DE OPERACOES DE NATUREZA INDUSTRIAL, COMERCIAL, FINANCEIRA, AGRICOLA, HIPOTECARIA E IMOBILIARIA, BEM COMO DE OPERACOES DE ARRENDAMENTO MERCANTIL OU DO SEGMENTO DE PRESTACAO DE SERVICOS. OS:</x:v>
       </x:c>
       <x:c r="AI64" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=13321819000100</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=23216398000101</x:v>
       </x:c>
       <x:c r="AJ64" s="24" t="str">
-        <x:v>975461</x:v>
+        <x:v>930881</x:v>
       </x:c>
       <x:c r="AK64" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL64" s="24" t="str">
-        <x:v>p. 13 — política/definição do lastro</x:v>
+        <x:v>p. 56 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM64" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8361,19 +8378,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D65" s="39" t="n">
-        <x:v>49306883000151</x:v>
+        <x:v>54871427000194</x:v>
       </x:c>
       <x:c r="E65" s="23" t="str">
-        <x:v>49.306.883/0001-51</x:v>
+        <x:v>54.871.427/0001-94</x:v>
       </x:c>
       <x:c r="F65" s="23" t="str">
-        <x:v>TM FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>CONSIGNADO DELTA RECEIVABLES I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G65" s="45" t="n">
-        <x:v>2100498673.09</x:v>
+        <x:v>2082486408.15</x:v>
       </x:c>
       <x:c r="H65" s="51" t="n">
-        <x:v>0.0025573374470067756</x:v>
+        <x:v>0.0024662187459881142</x:v>
       </x:c>
       <x:c r="I65" s="51" t="n">
         <x:v>0</x:v>
@@ -8421,25 +8438,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X65" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>FGTS</x:v>
       </x:c>
       <x:c r="Y65" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z65" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA65" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB65" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC65" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD65" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>FGTS</x:v>
       </x:c>
       <x:c r="AE65" s="23" t="str">
         <x:v>N/D</x:v>
@@ -8451,19 +8468,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH65" s="23" t="str">
-        <x:v>O regulamento declara que a origem não pode ser especificada e admite debêntures, notas, CCBs, precatórios e direitos judiciais. O mandato sustenta Multicarteira Outros.</x:v>
+        <x:v>Def. "Endossante": cada instituição financeira que ceda Direitos Creditórios à Classe. Def. "Devedores": cada trabalhador beneficiário do FGTS que emita CCB com cessão fiduciária do Saque-aniversário. A Tabela II aloca 100% em C1 "Comercial", campo incompatível com CCB de pessoa física garantida por FGTS.</x:v>
       </x:c>
       <x:c r="AI65" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=49306883000151</x:v>
+        <x:v>Industria_FIDC_202606_auditada.xlsx#Auditoria classificação Top200</x:v>
       </x:c>
       <x:c r="AJ65" s="23" t="str">
-        <x:v>771170</x:v>
+        <x:v>Regulamento ids 670689 e 670690</x:v>
       </x:c>
       <x:c r="AK65" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL65" s="23" t="str">
-        <x:v>p. 9 — política/definição do lastro</x:v>
+        <x:v>Regulamento ids 670689 e 670690</x:v>
       </x:c>
       <x:c r="AM65" s="23" t="str">
         <x:v>N/D</x:v>
@@ -8486,22 +8503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D66" s="38" t="n">
-        <x:v>54871427000194</x:v>
+        <x:v>13321819000100</x:v>
       </x:c>
       <x:c r="E66" s="24" t="str">
-        <x:v>54.871.427/0001-94</x:v>
+        <x:v>13.321.819/0001-00</x:v>
       </x:c>
       <x:c r="F66" s="24" t="str">
-        <x:v>CONSIGNADO DELTA RECEIVABLES I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS VALE</x:v>
       </x:c>
       <x:c r="G66" s="44" t="n">
-        <x:v>2008347381.44</x:v>
+        <x:v>2045856427.66</x:v>
       </x:c>
       <x:c r="H66" s="50" t="n">
-        <x:v>0.0024451441131352956</x:v>
+        <x:v>0.0024228390897290996</x:v>
       </x:c>
       <x:c r="I66" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0393499895555923</x:v>
       </x:c>
       <x:c r="J66" s="50" t="str">
         <x:v>N/D</x:v>
@@ -8546,25 +8563,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X66" s="24" t="str">
-        <x:v>FGTS</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y66" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z66" s="24" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA66" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB66" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC66" s="24" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD66" s="24" t="str">
-        <x:v>FGTS</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE66" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8576,19 +8593,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH66" s="24" t="str">
-        <x:v>Def. "Endossante": cada instituição financeira que ceda Direitos Creditórios à Classe. Def. "Devedores": cada trabalhador beneficiário do FGTS que emita CCB com cessão fiduciária do Saque-aniversário. A Tabela II aloca 100% em C1 "Comercial", campo incompatível com CCB de pessoa física garantida por FGTS.</x:v>
+        <x:v>Os documentos admitem cupons e notas fiscais, CCBs, recebíveis de cartão e renegociações. A diversidade contratual sustenta Multicarteira Outros.</x:v>
       </x:c>
       <x:c r="AI66" s="24" t="str">
-        <x:v>Industria_FIDC_202606_auditada.xlsx#Auditoria classificação Top200</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=13321819000100</x:v>
       </x:c>
       <x:c r="AJ66" s="24" t="str">
-        <x:v>Regulamento ids 670689 e 670690</x:v>
+        <x:v>975461</x:v>
       </x:c>
       <x:c r="AK66" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL66" s="24" t="str">
-        <x:v>Regulamento ids 670689 e 670690</x:v>
+        <x:v>p. 13 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM66" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8611,22 +8628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D67" s="39" t="n">
-        <x:v>62838025000116</x:v>
+        <x:v>52651831000127</x:v>
       </x:c>
       <x:c r="E67" s="23" t="str">
-        <x:v>62.838.025/0001-16</x:v>
+        <x:v>52.651.831/0001-27</x:v>
       </x:c>
       <x:c r="F67" s="23" t="str">
-        <x:v>ENDURANCE FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>HYUNDAI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G67" s="45" t="n">
-        <x:v>2004513902.3</x:v>
+        <x:v>2040649598.42</x:v>
       </x:c>
       <x:c r="H67" s="51" t="n">
-        <x:v>0.002440476888212644</x:v>
+        <x:v>0.0024166728166487125</x:v>
       </x:c>
       <x:c r="I67" s="51" t="n">
-        <x:v>0.0945332125270876</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J67" s="51" t="str">
         <x:v>N/D</x:v>
@@ -8665,13 +8682,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V67" s="23" t="str">
-        <x:v>Pague Veloz / Serasa</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W67" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X67" s="23" t="str">
-        <x:v>recebíveis de Rede, GetNet, Cielo e Pag</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y67" s="23" t="str">
         <x:v>Agro, Indústria e Comércio</x:v>
@@ -8680,40 +8697,40 @@
         <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA67" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB67" s="23" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Crédito Corporativo</x:v>
       </x:c>
       <x:c r="AC67" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD67" s="23" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
-      </x:c>
-      <x:c r="AE67" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE67" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF67" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG67" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH67" s="23" t="str">
-        <x:v>Direção aprovada: Financeiro / Adquirência</x:v>
+        <x:v>E ASSUNTO, CEDER OU ORIGINAR, DIRETA OU INDIRETAMENTE, DIREITOS CREDITORIOS AO FUNDO E A CLASSE. 4. POLITICA DE INVESTIMENTO 4.1. OS INVESTIMENTOS DA CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”), SENDO QUE, NOS TERMOS DO ARTIGO 45, PARAGRAFO 7O, INCISO II, DO ANEXO NORMATIVO II DA RESOLUCAO CVM 175, A CLASSE ESTA DISPENSADA DE LIMITAR-SE AOS 20% (VINTE POR CENTO) DE APLICACAO DE RECURSOS EM DIREITOS CREDITORIOS E OUTROS ATIVOS DE RESPONSABILIDADE OU COOBRIGACAO DE UM MESMO DEVEDOR COM RELACAO AO PATRIMONIO LIQUIDO DA CLASSE. 4.2. A CLASSE E VOLTADA, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS, ORIUNDOS DA VENDA DE VEICULOS A PRAZO DA CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 4.3. DE ACORDO COM AS REGRAS E PROCEDIMENTOS ANBIMA PARA CLASSIFICAC</x:v>
       </x:c>
       <x:c r="AI67" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 1058234</x:v>
+        <x:v>FundosNet/B3 — regulamento 690896</x:v>
       </x:c>
       <x:c r="AJ67" s="23" t="str">
-        <x:v>1058234</x:v>
+        <x:v>690896</x:v>
       </x:c>
       <x:c r="AK67" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL67" s="23" t="str">
-        <x:v>p. 25 — unidades de recebíveis e subcredenciadoras</x:v>
+        <x:v>p. 47 — venda de veículos a prazo à concessionária</x:v>
       </x:c>
       <x:c r="AM67" s="23" t="str">
         <x:v>N/D</x:v>
@@ -8722,7 +8739,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO67" s="23" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="36" customHeight="1">
@@ -8736,22 +8753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D68" s="38" t="n">
-        <x:v>23216398000101</x:v>
+        <x:v>49306883000151</x:v>
       </x:c>
       <x:c r="E68" s="24" t="str">
-        <x:v>23.216.398/0001-01</x:v>
+        <x:v>49.306.883/0001-51</x:v>
       </x:c>
       <x:c r="F68" s="24" t="str">
-        <x:v>MULTIPLICA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>TM FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G68" s="44" t="n">
-        <x:v>1993263958.67</x:v>
+        <x:v>2040580910.81</x:v>
       </x:c>
       <x:c r="H68" s="50" t="n">
-        <x:v>0.0024267801872861964</x:v>
+        <x:v>0.0024165914722179705</x:v>
       </x:c>
       <x:c r="I68" s="50" t="n">
-        <x:v>0.4477404397036854</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J68" s="50" t="str">
         <x:v>N/D</x:v>
@@ -8796,25 +8813,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X68" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y68" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z68" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA68" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB68" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC68" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD68" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE68" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8826,19 +8843,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH68" s="24" t="str">
-        <x:v>ZACAO DE SUAS COTAS ATRAVES DA APLICACAO PREPONDERANTE DOS RECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS CONFORME POLITICA DE INVESTIMENTO ESTABELECIDA NESTE REGULAMENTO. 11.2. OS DIREITOS CREDITORIOS QUE SERAO ADQUIRIDOS PELO FUNDO PODERAO SER ORIGINADOS EM DIVERSOS SEGMENTOS, SENDO ORIUNDOS DE OPERACOES DE NATUREZA INDUSTRIAL, COMERCIAL, FINANCEIRA, AGRICOLA, HIPOTECARIA E IMOBILIARIA, BEM COMO DE OPERACOES DE ARRENDAMENTO MERCANTIL OU DO SEGMENTO DE PRESTACAO DE SERVICOS. OS:</x:v>
+        <x:v>O regulamento declara que a origem não pode ser especificada e admite debêntures, notas, CCBs, precatórios e direitos judiciais. O mandato sustenta Multicarteira Outros.</x:v>
       </x:c>
       <x:c r="AI68" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=23216398000101</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=49306883000151</x:v>
       </x:c>
       <x:c r="AJ68" s="24" t="str">
-        <x:v>930881</x:v>
+        <x:v>771170</x:v>
       </x:c>
       <x:c r="AK68" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL68" s="24" t="str">
-        <x:v>p. 56 — política/definição do lastro</x:v>
+        <x:v>p. 9 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM68" s="24" t="str">
         <x:v>N/D</x:v>
@@ -8861,22 +8878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D69" s="39" t="n">
-        <x:v>61652768000134</x:v>
+        <x:v>62838025000116</x:v>
       </x:c>
       <x:c r="E69" s="23" t="str">
-        <x:v>61.652.768/0001-34</x:v>
+        <x:v>62.838.025/0001-16</x:v>
       </x:c>
       <x:c r="F69" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DRIVER MASTER BRASIL I - RESP LIMITADA</x:v>
+        <x:v>ENDURANCE FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G69" s="45" t="n">
-        <x:v>1972712266.59</x:v>
+        <x:v>1999981369.56</x:v>
       </x:c>
       <x:c r="H69" s="51" t="n">
-        <x:v>0.002401758694804975</x:v>
+        <x:v>0.0023685107984054497</x:v>
       </x:c>
       <x:c r="I69" s="51" t="n">
-        <x:v>0.2309097529943922</x:v>
+        <x:v>0.0930889101736938</x:v>
       </x:c>
       <x:c r="J69" s="51" t="str">
         <x:v>N/D</x:v>
@@ -8915,31 +8932,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V69" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Pague Veloz / Serasa</x:v>
       </x:c>
       <x:c r="W69" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X69" s="23" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>recebíveis de Rede, GetNet, Cielo e Pag</x:v>
       </x:c>
       <x:c r="Y69" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z69" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA69" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB69" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC69" s="23" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD69" s="23" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="AE69" s="27" t="b">
         <x:v>0</x:v>
@@ -8951,19 +8968,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH69" s="23" t="str">
-        <x:v>IFICADO E VALIDADO PELO CUSTODIANTE NO DIA UTIL IMEDIATAMENTE ANTERIOR A DATA DE AQUISICAO, DE ACORDO COM OS SEGUINTES CRITERIOS DE ELEGIBILIDADE: (I) O VALOR NOMINAL AGREGADO DOS DIREITOS CREDITORIOS ADQUIRIDOS DECORRENTES DE CEDULAS DE CREDITO BANCARIO DE UM UNICO DEVEDOR NAO PODERA EXCEDER R$ 250.000,00 (DUZENTOS E CINQUENTA MIL REAIS); (II) OS DIREITOS CREDITORIOS SOMENTE SERAO REFERENTES AS CEDULAS DE CREDITO BANCARIO RELATIVAS AO FINANCIAMENTO DE VEICULOS NA MODALIDADE DE CREDITO DIRETO AO CONSUMIDOR (CDC – VEICULOS), DESDE QUE AS CEDULAS DE CREDITO BANCARIO RELATIVAS AO FINANCIAMENTO DE VEICULOS SEMINOVOS CORRESPONDAM A, NO MAXIMO, 15,0% (QUINZE POR CENTO) DE TODOS OS DIREITOS CREDITORIOS ADQUIRIDOS PELA CLASSE; (III) OS DIREITOS CREDITORIOS DEVEM SER DE DEVEDORES QUE NAO APRESENTEM, NO MOMENTO DA COMPRA PELO FUNDO, OUTROS DIREITOS CREDITORIOS ADQUIRIDOS ACUMULADOS E NAO PAGOS AO FUNDO; (IV) CONSIDERANDO A CESSAO PROPOSTA PRO FORMA, OS DIREITOS CREDITORIOS ADQUIRIDOS QUE COMPOEM A CARTEIRA DO FUNDO TERAO APENAS PARCELAS MENS</x:v>
+        <x:v>Direção aprovada: Financeiro / Adquirência</x:v>
       </x:c>
       <x:c r="AI69" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=61652768000134</x:v>
+        <x:v>FundosNet/B3 — regulamento 1058234</x:v>
       </x:c>
       <x:c r="AJ69" s="23" t="str">
-        <x:v>1044627</x:v>
+        <x:v>1058234</x:v>
       </x:c>
       <x:c r="AK69" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL69" s="23" t="str">
-        <x:v>p. 35 — política/definição do lastro</x:v>
+        <x:v>p. 25 — unidades de recebíveis e subcredenciadoras</x:v>
       </x:c>
       <x:c r="AM69" s="23" t="str">
         <x:v>N/D</x:v>
@@ -8972,7 +8989,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO69" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="36" customHeight="1">
@@ -8995,10 +9012,10 @@
         <x:v>MONTENEGRO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G70" s="44" t="n">
-        <x:v>1967671103.82</x:v>
+        <x:v>1960417320.47</x:v>
       </x:c>
       <x:c r="H70" s="50" t="n">
-        <x:v>0.0023956211263821336</x:v>
+        <x:v>0.0023216564231974828</x:v>
       </x:c>
       <x:c r="I70" s="50" t="n">
         <x:v>0</x:v>
@@ -9111,22 +9128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D71" s="39" t="n">
-        <x:v>50114948000146</x:v>
+        <x:v>58893662000118</x:v>
       </x:c>
       <x:c r="E71" s="23" t="str">
-        <x:v>50.114.948/0001-46</x:v>
+        <x:v>58.893.662/0001-18</x:v>
       </x:c>
       <x:c r="F71" s="23" t="str">
-        <x:v>DRIVER BRASIL SIX BANCO VOLKSWAGEN FIDC FINANCIAMENTO DE VEÍCULOS - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>JIVE BOSSANOVA90 - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G71" s="45" t="n">
-        <x:v>1934784988.69</x:v>
+        <x:v>1944596528.21</x:v>
       </x:c>
       <x:c r="H71" s="51" t="n">
-        <x:v>0.0023555825894451855</x:v>
+        <x:v>0.002302920390013642</x:v>
       </x:c>
       <x:c r="I71" s="51" t="n">
-        <x:v>0.1340459460934414</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J71" s="51" t="str">
         <x:v>N/D</x:v>
@@ -9171,49 +9188,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="Y71" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z71" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA71" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB71" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Poder Público</x:v>
       </x:c>
       <x:c r="AC71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD71" s="23" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="AE71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
+      </x:c>
+      <x:c r="AE71" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF71" s="23" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG71" s="23" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>regulamento 1044435 p. 11 [precatórios e requisitórios contra entes públicos]: O JUDICIAL DA CLASSE E O MONITORAMENTO DOS DIREITOS CREDITORIOS; E (2) PREVIAMENTE A AQUISICAO DE CADA DIREITO CREDITORIO, POSSUIR O OFICIO REQUISITORIO E A CERTIDAO DE REMESSA DO PRECATORIO AO TRIBUNAL REGIONAL FE DERAL COMPETENTE, OU O || CEDENTE/ORIGINADOR: regulamento 1044435 p. 39: CEDENTE SERA RESPONSAVEL PELA EXISTENCIA DOS DIREITOS CREDITORIOS CEDIDOS, NOS TERMOS DO ARTIGO 295 DO CODIGO CIVIL BRASILEIRO</x:v>
       </x:c>
       <x:c r="AI71" s="23" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=58893662000118</x:v>
       </x:c>
       <x:c r="AJ71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>1044435</x:v>
       </x:c>
       <x:c r="AK71" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>regulamento 1044435 p. 11</x:v>
       </x:c>
       <x:c r="AM71" s="23" t="str">
         <x:v>N/D</x:v>
@@ -9222,7 +9239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO71" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="36" customHeight="1">
@@ -9236,22 +9253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D72" s="38" t="n">
-        <x:v>53841740000117</x:v>
+        <x:v>43489824000180</x:v>
       </x:c>
       <x:c r="E72" s="24" t="str">
-        <x:v>53.841.740/0001-17</x:v>
+        <x:v>43.489.824/0001-80</x:v>
       </x:c>
       <x:c r="F72" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CRÉDITO CONSIGNADO PRIVADO PAKETÁ DE RESPONSABILID</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS COMPLEMENTAR AUTO-FORD</x:v>
       </x:c>
       <x:c r="G72" s="44" t="n">
-        <x:v>1918531934.02</x:v>
+        <x:v>1927443335.68</x:v>
       </x:c>
       <x:c r="H72" s="50" t="n">
-        <x:v>0.0023357946477205213</x:v>
+        <x:v>0.0022826064399175117</x:v>
       </x:c>
       <x:c r="I72" s="50" t="n">
-        <x:v>0.3199140206034778</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J72" s="50" t="str">
         <x:v>N/D</x:v>
@@ -9302,13 +9319,13 @@
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z72" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AA72" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB72" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AC72" s="24" t="str">
         <x:v>N/D</x:v>
@@ -9361,22 +9378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D73" s="39" t="n">
-        <x:v>53300525000109</x:v>
+        <x:v>66146197000180</x:v>
       </x:c>
       <x:c r="E73" s="23" t="str">
-        <x:v>53.300.525/0001-09</x:v>
+        <x:v>66.146.197/0001-80</x:v>
       </x:c>
       <x:c r="F73" s="23" t="str">
-        <x:v>IBCB-AF01 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS STELLANTIS MOBILITY III - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G73" s="45" t="n">
-        <x:v>1909790565.67</x:v>
+        <x:v>1925682597.46</x:v>
       </x:c>
       <x:c r="H73" s="51" t="n">
-        <x:v>0.0023251521136851867</x:v>
+        <x:v>0.002280521256749954</x:v>
       </x:c>
       <x:c r="I73" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0.1027449904369085</x:v>
       </x:c>
       <x:c r="J73" s="51" t="str">
         <x:v>N/D</x:v>
@@ -9421,7 +9438,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X73" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y73" s="23" t="str">
         <x:v>Agro, Indústria e Comércio</x:v>
@@ -9436,34 +9453,34 @@
         <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC73" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD73" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AE73" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF73" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG73" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH73" s="23" t="str">
-        <x:v>O documento define cedentes e endossantes como partes que transferem recebíveis sem individualizar entidades.</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI73" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53300525000109</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=66146197000180</x:v>
       </x:c>
       <x:c r="AJ73" s="23" t="str">
-        <x:v>1246711</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK73" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL73" s="23" t="str">
-        <x:v>p. 44 — política/definição do lastro</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM73" s="23" t="str">
         <x:v>N/D</x:v>
@@ -9472,7 +9489,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO73" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="36" customHeight="1">
@@ -9486,22 +9503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D74" s="38" t="n">
-        <x:v>24504464000101</x:v>
+        <x:v>28279473000199</x:v>
       </x:c>
       <x:c r="E74" s="24" t="str">
-        <x:v>24.504.464/0001-01</x:v>
+        <x:v>28.279.473/0001-99</x:v>
       </x:c>
       <x:c r="F74" s="24" t="str">
-        <x:v>IOX II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AUTO-HONDA</x:v>
       </x:c>
       <x:c r="G74" s="44" t="n">
-        <x:v>1893430371.86</x:v>
+        <x:v>1925498329.61</x:v>
       </x:c>
       <x:c r="H74" s="50" t="n">
-        <x:v>0.0023052337310617626</x:v>
+        <x:v>0.0022803030345209035</x:v>
       </x:c>
       <x:c r="I74" s="50" t="n">
-        <x:v>0.3808755174811066</x:v>
+        <x:v>0.1153248886507287</x:v>
       </x:c>
       <x:c r="J74" s="50" t="str">
         <x:v>N/D</x:v>
@@ -9549,16 +9566,16 @@
         <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y74" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z74" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA74" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB74" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Crédito Corporativo</x:v>
       </x:c>
       <x:c r="AC74" s="24" t="str">
         <x:v>Crédito PJ</x:v>
@@ -9576,19 +9593,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH74" s="24" t="str">
-        <x:v>NTRATAR PRESTADORES DE SERVICOS HABILITADOS PARA A VERIFICACAO E A GUARDA FISICA DOS DOCUMENTOS COMPROBATORIOS. 12. CRITERIOS DE ELEGIBILIDADE 12.1 O FUNDO SOMENTE PODERA ADQUIRIR DIREITOS CREDITORIOS QUE ATENDAM, EXCLUSIVA E CUMULATIVAMENTE, AOS SEGUINTES CRITERIOS DE ELEGIBILIDADE: A) SER REPRESENTADOS POR NOTAS COMERCIAIS, NOTAS PROMISSORIAS, DUPLICATAS, CHEQUES, CEDULAS DE CREDITO BANCARIO, CEDULAS DE PRODUTOR RURAL FINANCEIRA; B) TER VALOR MINIMO DE R$ 0,01 (UM CENTAVO);</x:v>
+        <x:v>A CLASSE, O AGENTE DE COBRANCA FARA JUS A TAXA DE COBRANCA, NOS TERMOS DO CONTRATO DE COBRANCA. 9. POLITICA DE INVESTIMENTO 9.1. OS INVESTIMENTOS DA CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”). 9.2. A CLASSE E VOLTAD A, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS , ORIUNDOS DA VENDA DE VEICULOS A PRAZO DO CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 9.2.1. A CLASSE E CLASSIFICADA COMO UMA CLASSE DE FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS DO TIPO ANBIMA " AGRO, INDUSTRIA E COMERCIO ", COM FOCO DE ATUACAO EM "RECEBIVEIS COMERCIAIS", NOS TERMOS DO “CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS” EDITADO PELA ANBIMA E EM VIGOR NESTA DATA. 9.2.2. A CLASSE DEVERA MANTER, EM ATE 180 (CENTO E OITENTA) DIAS A PARTIR DO INICIO DE SUAS A</x:v>
       </x:c>
       <x:c r="AI74" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=24504464000101</x:v>
+        <x:v>FundosNet/B3 — regulamento 659783</x:v>
       </x:c>
       <x:c r="AJ74" s="24" t="str">
-        <x:v>1266015</x:v>
+        <x:v>659783</x:v>
       </x:c>
       <x:c r="AK74" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL74" s="24" t="str">
-        <x:v>p. 15 — política/definição do lastro</x:v>
+        <x:v>p. 38 — venda de veículos a prazo à concessionária</x:v>
       </x:c>
       <x:c r="AM74" s="24" t="str">
         <x:v>N/D</x:v>
@@ -9611,22 +9628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D75" s="39" t="n">
-        <x:v>43489824000180</x:v>
+        <x:v>24504464000101</x:v>
       </x:c>
       <x:c r="E75" s="23" t="str">
-        <x:v>43.489.824/0001-80</x:v>
+        <x:v>24.504.464/0001-01</x:v>
       </x:c>
       <x:c r="F75" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS COMPLEMENTAR AUTO-FORD</x:v>
+        <x:v>IOX II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G75" s="45" t="n">
-        <x:v>1883891566.03</x:v>
+        <x:v>1924331624.55</x:v>
       </x:c>
       <x:c r="H75" s="51" t="n">
-        <x:v>0.0022936203243687225</x:v>
+        <x:v>0.0022789213448835785</x:v>
       </x:c>
       <x:c r="I75" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.3851477559871331</x:v>
       </x:c>
       <x:c r="J75" s="51" t="str">
         <x:v>N/D</x:v>
@@ -9671,49 +9688,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y75" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z75" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA75" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB75" s="23" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="AE75" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF75" s="23" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG75" s="23" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>NTRATAR PRESTADORES DE SERVICOS HABILITADOS PARA A VERIFICACAO E A GUARDA FISICA DOS DOCUMENTOS COMPROBATORIOS. 12. CRITERIOS DE ELEGIBILIDADE 12.1 O FUNDO SOMENTE PODERA ADQUIRIR DIREITOS CREDITORIOS QUE ATENDAM, EXCLUSIVA E CUMULATIVAMENTE, AOS SEGUINTES CRITERIOS DE ELEGIBILIDADE: A) SER REPRESENTADOS POR NOTAS COMERCIAIS, NOTAS PROMISSORIAS, DUPLICATAS, CHEQUES, CEDULAS DE CREDITO BANCARIO, CEDULAS DE PRODUTOR RURAL FINANCEIRA; B) TER VALOR MINIMO DE R$ 0,01 (UM CENTAVO);</x:v>
       </x:c>
       <x:c r="AI75" s="23" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=24504464000101</x:v>
       </x:c>
       <x:c r="AJ75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>1266015</x:v>
       </x:c>
       <x:c r="AK75" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>p. 15 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM75" s="23" t="str">
         <x:v>N/D</x:v>
@@ -9722,7 +9739,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO75" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="36" customHeight="1">
@@ -9736,22 +9753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D76" s="38" t="n">
-        <x:v>63572282000111</x:v>
+        <x:v>53300525000109</x:v>
       </x:c>
       <x:c r="E76" s="24" t="str">
-        <x:v>63.572.282/0001-11</x:v>
+        <x:v>53.300.525/0001-09</x:v>
       </x:c>
       <x:c r="F76" s="24" t="str">
-        <x:v>SELLER 3 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO DE RESP LIMITADA</x:v>
+        <x:v>IBCB-AF01 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G76" s="44" t="n">
-        <x:v>1876075238.87</x:v>
+        <x:v>1919387163.23</x:v>
       </x:c>
       <x:c r="H76" s="50" t="n">
-        <x:v>0.0022841040193120193</x:v>
+        <x:v>0.0022730657853233943</x:v>
       </x:c>
       <x:c r="I76" s="50" t="n">
-        <x:v>0.1553066180466027</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J76" s="50" t="str">
         <x:v>N/D</x:v>
@@ -9796,7 +9813,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X76" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y76" s="24" t="str">
         <x:v>Agro, Indústria e Comércio</x:v>
@@ -9805,40 +9822,40 @@
         <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA76" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB76" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC76" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD76" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
-      </x:c>
-      <x:c r="AE76" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE76" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF76" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG76" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH76" s="24" t="str">
-        <x:v>Financeiro → Adquirência; risco adquirente corporativo</x:v>
+        <x:v>O documento define cedentes e endossantes como partes que transferem recebíveis sem individualizar entidades.</x:v>
       </x:c>
       <x:c r="AI76" s="24" t="str">
-        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=53300525000109</x:v>
       </x:c>
       <x:c r="AJ76" s="24" t="str">
-        <x:v>Regulamento id 1091930 e correlatos</x:v>
+        <x:v>1246711</x:v>
       </x:c>
       <x:c r="AK76" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL76" s="24" t="str">
-        <x:v>Lista de fundos da tarefa</x:v>
+        <x:v>p. 44 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM76" s="24" t="str">
         <x:v>N/D</x:v>
@@ -9861,22 +9878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D77" s="39" t="n">
-        <x:v>28279473000199</x:v>
+        <x:v>53841740000117</x:v>
       </x:c>
       <x:c r="E77" s="23" t="str">
-        <x:v>28.279.473/0001-99</x:v>
+        <x:v>53.841.740/0001-17</x:v>
       </x:c>
       <x:c r="F77" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AUTO-HONDA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CRÉDITO CONSIGNADO PRIVADO PAKETÁ DE RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G77" s="45" t="n">
-        <x:v>1844741719.62</x:v>
+        <x:v>1911439961.8</x:v>
       </x:c>
       <x:c r="H77" s="51" t="n">
-        <x:v>0.002245955753306855</x:v>
+        <x:v>0.002263654181450204</x:v>
       </x:c>
       <x:c r="I77" s="51" t="n">
-        <x:v>0.1167435114360664</x:v>
+        <x:v>0.3289671657228036</x:v>
       </x:c>
       <x:c r="J77" s="51" t="str">
         <x:v>N/D</x:v>
@@ -9921,49 +9938,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X77" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y77" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z77" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA77" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB77" s="23" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC77" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD77" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AE77" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF77" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG77" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH77" s="23" t="str">
-        <x:v>A CLASSE, O AGENTE DE COBRANCA FARA JUS A TAXA DE COBRANCA, NOS TERMOS DO CONTRATO DE COBRANCA. 9. POLITICA DE INVESTIMENTO 9.1. OS INVESTIMENTOS DA CLASSE CONSISTIRAO EM DIREITOS CREDITORIOS E INVESTIMENTOS PERMITIDOS (“POLITICA DE INVESTIMENTO”). 9.2. A CLASSE E VOLTAD A, PRIMORDIALMENTE, A APLICACAO EM DIREITOS CREDITORIOS , ORIUNDOS DA VENDA DE VEICULOS A PRAZO DO CEDENTE EM FAVOR DA RESPECTIVA CONCESSIONARIA. 9.2.1. A CLASSE E CLASSIFICADA COMO UMA CLASSE DE FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS DO TIPO ANBIMA " AGRO, INDUSTRIA E COMERCIO ", COM FOCO DE ATUACAO EM "RECEBIVEIS COMERCIAIS", NOS TERMOS DO “CODIGO DE ADMINISTRACAO E GESTAO DE RECURSOS DE TERCEIROS” EDITADO PELA ANBIMA E EM VIGOR NESTA DATA. 9.2.2. A CLASSE DEVERA MANTER, EM ATE 180 (CENTO E OITENTA) DIAS A PARTIR DO INICIO DE SUAS A</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI77" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 659783</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ77" s="23" t="str">
-        <x:v>659783</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK77" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL77" s="23" t="str">
-        <x:v>p. 38 — venda de veículos a prazo à concessionária</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM77" s="23" t="str">
         <x:v>N/D</x:v>
@@ -9972,7 +9989,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO77" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="36" customHeight="1">
@@ -9986,22 +10003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D78" s="38" t="n">
-        <x:v>41970012000126</x:v>
+        <x:v>55471753000177</x:v>
       </x:c>
       <x:c r="E78" s="24" t="str">
-        <x:v>41.970.012/0001-26</x:v>
+        <x:v>55.471.753/0001-77</x:v>
       </x:c>
       <x:c r="F78" s="24" t="str">
-        <x:v>MERCADO CRÉDITO II BRASIL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>SELLER II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO RESP LTDA</x:v>
       </x:c>
       <x:c r="G78" s="44" t="n">
-        <x:v>1761615997.81</x:v>
+        <x:v>1911426358.03</x:v>
       </x:c>
       <x:c r="H78" s="50" t="n">
-        <x:v>0.00214475096612103</x:v>
+        <x:v>0.0022636380709620597</x:v>
       </x:c>
       <x:c r="I78" s="50" t="n">
-        <x:v>0.3143179016233531</x:v>
+        <x:v>0.4739448173839156</x:v>
       </x:c>
       <x:c r="J78" s="50" t="str">
         <x:v>N/D</x:v>
@@ -10046,49 +10063,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X78" s="24" t="str">
-        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="Y78" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z78" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA78" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB78" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC78" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD78" s="24" t="str">
-        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
-      </x:c>
-      <x:c r="AE78" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
+      </x:c>
+      <x:c r="AE78" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF78" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG78" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH78" s="24" t="str">
-        <x:v>NAO EXCEDERA O VALOR MAXIMO DE INVESTIMENTO SENIOR E DEVERA RESPEITAR AS REGRAS PREVISTAS NESTE REGULAMENTO. "CARTEIRA" SIGNIFICA A CARTEIRA DE INVESTIMENTOS DO FUNDO, FORMADA POR DIREITOS CREDITORIOS E ATIVOS FINANCEIROS DE TITULARIDADE DO FUNDO. "CCB" OU "CCBS" SIGNIFICAM AS CEDULAS DE CREDITO BANCARIO EMITIDAS A PARTIR DOS CARACTERES CRIADOS EM COMPUTADOR PELOS DEVEDORES CCB EM FAVOR DAS INSTITUICOES FINANCEIRAS PARCEIRAS OU DA INSTITUICAO FINANCEIRA MELI, CONFORME O CASO, NOS TERMOS DA LEI NO 10.931, DE 02 DE A GOSTO DE 2004, CONFORME ALTERADA, COM O OBJETIVO DE REALIZAR UMA OPERACAO DE CREDITO PARCELADO OU EMPRESTIMO PESSOAL, CONFORME APLICAVEL, QUE OBSERVEM OS MODELOS PREVISTOS NOS CONTRATOS DE ENDOSSO. "CEDENTE" OU "CEDENTES" SIGNIFICAM OS CEDENTES CCB E OS CEDENTES PPV, QUANDO REFERIDOS EM CONJUNTO. "CEDEN</x:v>
+        <x:v>Financeiro → Adquirência; risco adquirente corporativo</x:v>
       </x:c>
       <x:c r="AI78" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=41970012000126</x:v>
+        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
       </x:c>
       <x:c r="AJ78" s="24" t="str">
-        <x:v>1077334</x:v>
+        <x:v>Regulamento arquivado no FundosNET</x:v>
       </x:c>
       <x:c r="AK78" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL78" s="24" t="str">
-        <x:v>p. 11 — política/definição do lastro</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM78" s="24" t="str">
         <x:v>N/D</x:v>
@@ -10111,22 +10128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D79" s="39" t="n">
-        <x:v>32526025000110</x:v>
+        <x:v>11468186000124</x:v>
       </x:c>
       <x:c r="E79" s="23" t="str">
-        <x:v>32.526.025/0001-10</x:v>
+        <x:v>11.468.186/0001-24</x:v>
       </x:c>
       <x:c r="F79" s="23" t="str">
-        <x:v>COBUCCIO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE CLASSE ÚNICA FECHADA DE RESPONS LIMITADA</x:v>
+        <x:v>ATLANTA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G79" s="45" t="n">
-        <x:v>1759550198.61</x:v>
+        <x:v>1897667543.94</x:v>
       </x:c>
       <x:c r="H79" s="51" t="n">
-        <x:v>0.0021422358749572804</x:v>
+        <x:v>0.0022473439693062093</x:v>
       </x:c>
       <x:c r="I79" s="51" t="n">
-        <x:v>0.7555299286267351</x:v>
+        <x:v>0.8815886150370092</x:v>
       </x:c>
       <x:c r="J79" s="51" t="str">
         <x:v>N/D</x:v>
@@ -10165,55 +10182,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V79" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicedentes e Multisacados</x:v>
       </x:c>
       <x:c r="W79" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X79" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>FIDC Multicedentes &amp; Multisacados</x:v>
       </x:c>
       <x:c r="Y79" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z79" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA79" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB79" s="23" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC79" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD79" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
-      </x:c>
-      <x:c r="AE79" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE79" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF79" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG79" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH79" s="23" t="str">
-        <x:v>Direção aprovada: Financeiro / Cartão de crédito</x:v>
+        <x:v>O regulamento define cedentes genericamente e informa que os múltiplos cedentes não são conhecidos previamente.</x:v>
       </x:c>
       <x:c r="AI79" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 1186789</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=11468186000124</x:v>
       </x:c>
       <x:c r="AJ79" s="23" t="str">
-        <x:v>Regulamento id 1186789</x:v>
+        <x:v>1130308</x:v>
       </x:c>
       <x:c r="AK79" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL79" s="23" t="str">
-        <x:v>pp. 5–10 — cartões Brasil Card, faturas, carnês e CCBs</x:v>
+        <x:v>p. 49 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM79" s="23" t="str">
         <x:v>N/D</x:v>
@@ -10222,7 +10239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO79" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="36" customHeight="1">
@@ -10236,22 +10253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D80" s="38" t="n">
-        <x:v>38376526000143</x:v>
+        <x:v>34081900000122</x:v>
       </x:c>
       <x:c r="E80" s="24" t="str">
-        <x:v>38.376.526/0001-43</x:v>
+        <x:v>34.081.900/0001-22</x:v>
       </x:c>
       <x:c r="F80" s="24" t="str">
-        <x:v>HOTFUND FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDAD</x:v>
+        <x:v>GOLD STYLE FUNDO DE INVESTIMENTO EM PARTICIPAÇÕES MULTIESTRATÉGIA</x:v>
       </x:c>
       <x:c r="G80" s="44" t="n">
-        <x:v>1702368453.87</x:v>
+        <x:v>1866969812.56</x:v>
       </x:c>
       <x:c r="H80" s="50" t="n">
-        <x:v>0.0020726176366873818</x:v>
+        <x:v>0.002210989676527934</x:v>
       </x:c>
       <x:c r="I80" s="50" t="n">
-        <x:v>0.7641689143038269</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J80" s="50" t="str">
         <x:v>N/D</x:v>
@@ -10290,31 +10307,31 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V80" s="24" t="str">
-        <x:v>Hotmart</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W80" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X80" s="24" t="str">
-        <x:v>antecipação de parcelas de criadores de conteúdo</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y80" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z80" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA80" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB80" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AC80" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD80" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="AE80" s="26" t="b">
         <x:v>0</x:v>
@@ -10326,19 +10343,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH80" s="24" t="str">
-        <x:v>Nota 6 (a): «…DECORRENTES DE TRANSAÇÕES DE PAGAMENTO REALIZADAS POR USUÁRIOS COMPRADORES COM CARTÃO, À VISTA OU PARCELADAS, OPERACIONALIZADA PELO SISTEMA HOTPAY NO ÂMBITO DO RESPECTIVO ARRANJO DE PAGAMENTO»; «A MAIS RELEVANTE PARA FINS DA OPERAÇÃO DA CLASSE É O CRÉDITO DO PRODUTOR EM FACE DA SUBCREDENCIADORA (I.E., HOTMART)». A liquidação descrita na mesma nota passa por bandeiras, CIP/SILOC e credenciadoras.</x:v>
+        <x:v>EDITO E COBRANCA _______________________________________________________ 3 CAPITULO IV – OBJETIVO E POLITICA DE INVESTIMENTO, COMPOSICAO DA CARTEIRA E CONDICAO DE CESSAO _______________________________________________________ 4 CAPITULO V – CRITERIOS DE ELEGIBILIDADE ____________________________________ 7 CAPITULO VI – FATORES DE RISCO _____________________________________________ 8 CAPITULO VII – ADMINISTRADORA _____________________________________________ 18 CAPITULO VIII – SUBSTITUICAO E RENUNCIA DA ADMINISTRADORA _________________ 22 CAPITULO IX – CONTRATACAO DE TERCEIROS ___________________________________ 22 CAPITULO X– DAS CARACTERISTICAS, DIREITOS, CONDICOES DE EMISSAO, SUBSCRICAO E INTEGRALIZACAO E VALOR DAS COTAS _________________________________________ 25 CAPITULO XI – DAS CONDICOES DE RESGATE DAS</x:v>
       </x:c>
       <x:c r="AI80" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=38376526000143</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=34081900000122</x:v>
       </x:c>
       <x:c r="AJ80" s="24" t="str">
-        <x:v>1072072</x:v>
+        <x:v>516067</x:v>
       </x:c>
       <x:c r="AK80" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL80" s="24" t="str">
-        <x:v>Demonstrações financeiras, nota explicativa 6 (a) e 6 (e)</x:v>
+        <x:v>p. 2</x:v>
       </x:c>
       <x:c r="AM80" s="24" t="str">
         <x:v>N/D</x:v>
@@ -10347,7 +10364,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO80" s="24" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="36" customHeight="1">
@@ -10361,22 +10378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D81" s="39" t="n">
-        <x:v>40750266000176</x:v>
+        <x:v>63572282000111</x:v>
       </x:c>
       <x:c r="E81" s="23" t="str">
-        <x:v>40.750.266/0001-76</x:v>
+        <x:v>63.572.282/0001-11</x:v>
       </x:c>
       <x:c r="F81" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MT I RECEIVABLES RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>SELLER 3 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO DE RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G81" s="45" t="n">
-        <x:v>1701914787.69</x:v>
+        <x:v>1855894253.21</x:v>
       </x:c>
       <x:c r="H81" s="51" t="n">
-        <x:v>0.0020720653023653386</x:v>
+        <x:v>0.002197873263386232</x:v>
       </x:c>
       <x:c r="I81" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1873702924545502</x:v>
       </x:c>
       <x:c r="J81" s="51" t="str">
         <x:v>N/D</x:v>
@@ -10421,25 +10438,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X81" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="Y81" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z81" s="23" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA81" s="23" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB81" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC81" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD81" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="AE81" s="27" t="b">
         <x:v>0</x:v>
@@ -10451,19 +10468,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH81" s="23" t="str">
-        <x:v>AVEIS AS MANIFESTACOES DE VONTADE DOS COTISTAS; (VI) REMUNERACAO DOS PRESTADORES DE SERVICOS; (VII) POLITICA DE INVESTIMENTO E COMPOSICAO E DIVERSIFICACAO DA CARTEIRA; (VIII) EVENTOS DE AVALIACAO, EVENTOS DE LIQUIDACAO E LIQUIDACAO ANTECIPADA DA CLASSE; (IX) ORIGEM DOS DIREITOS CREDITORIOS; (X) CRITERIOS DE ELEGIBILIDADE; (XI) CUSTOS REFERENTES A DEFESA DOS INTERESSES DE CADA CLASSE DE COTAS; E (XII) FATORES DE RISCO. CAPITULO 2 – RESPONSABILIDADE DOS PRESTADORES DE SERVICOS ESSENCIAIS E DEMAIS PRESTADORES DE SERVICOS DO FUNDO 2.1 OS PRESTADORES DE SERVICOS ESSENCIAIS E DEMAIS PRESTADORES DE SERVICOS DO FUNDO RESPONDEM PERANTE A CVM, NAS SUAS RESPECTIVAS ESFERAS DE ATUACAO, POR SEUS PROPRIOS ATOS E OMISSOES CONTRARIOS A LEI, AO REGULAMENTO OU A REGULAMENTACAO VIGENTE, SEM PREJUIZO DO EXERCICIO DO DEVER DE FIS</x:v>
+        <x:v>Financeiro → Adquirência; risco adquirente corporativo</x:v>
       </x:c>
       <x:c r="AI81" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=40750266000176</x:v>
+        <x:v>Comentário explícito do usuário — tarefa Adquirência</x:v>
       </x:c>
       <x:c r="AJ81" s="23" t="str">
-        <x:v>1045050</x:v>
+        <x:v>Regulamento id 1091930 e correlatos</x:v>
       </x:c>
       <x:c r="AK81" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL81" s="23" t="str">
-        <x:v>p. 3</x:v>
+        <x:v>Lista de fundos da tarefa</x:v>
       </x:c>
       <x:c r="AM81" s="23" t="str">
         <x:v>N/D</x:v>
@@ -10486,22 +10503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D82" s="38" t="n">
-        <x:v>22358482000199</x:v>
+        <x:v>41970012000126</x:v>
       </x:c>
       <x:c r="E82" s="24" t="str">
-        <x:v>22.358.482/0001-99</x:v>
+        <x:v>41.970.012/0001-26</x:v>
       </x:c>
       <x:c r="F82" s="24" t="str">
-        <x:v>AFINITTY MF FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS FINANCEIROS - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>MERCADO CRÉDITO II BRASIL FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G82" s="44" t="n">
-        <x:v>1668953204.88</x:v>
+        <x:v>1847170248.89</x:v>
       </x:c>
       <x:c r="H82" s="50" t="n">
-        <x:v>0.0020319348842353312</x:v>
+        <x:v>0.0021875417179269855</x:v>
       </x:c>
       <x:c r="I82" s="50" t="n">
-        <x:v>1</x:v>
+        <x:v>0.3460699773697318</x:v>
       </x:c>
       <x:c r="J82" s="50" t="str">
         <x:v>N/D</x:v>
@@ -10546,7 +10563,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
       </x:c>
       <x:c r="Y82" s="24" t="str">
         <x:v>Financeiro</x:v>
@@ -10561,34 +10578,34 @@
         <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>CCB/Notas comerciais/Capital de giro</x:v>
       </x:c>
       <x:c r="AE82" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF82" s="24" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG82" s="24" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>NAO EXCEDERA O VALOR MAXIMO DE INVESTIMENTO SENIOR E DEVERA RESPEITAR AS REGRAS PREVISTAS NESTE REGULAMENTO. "CARTEIRA" SIGNIFICA A CARTEIRA DE INVESTIMENTOS DO FUNDO, FORMADA POR DIREITOS CREDITORIOS E ATIVOS FINANCEIROS DE TITULARIDADE DO FUNDO. "CCB" OU "CCBS" SIGNIFICAM AS CEDULAS DE CREDITO BANCARIO EMITIDAS A PARTIR DOS CARACTERES CRIADOS EM COMPUTADOR PELOS DEVEDORES CCB EM FAVOR DAS INSTITUICOES FINANCEIRAS PARCEIRAS OU DA INSTITUICAO FINANCEIRA MELI, CONFORME O CASO, NOS TERMOS DA LEI NO 10.931, DE 02 DE A GOSTO DE 2004, CONFORME ALTERADA, COM O OBJETIVO DE REALIZAR UMA OPERACAO DE CREDITO PARCELADO OU EMPRESTIMO PESSOAL, CONFORME APLICAVEL, QUE OBSERVEM OS MODELOS PREVISTOS NOS CONTRATOS DE ENDOSSO. "CEDENTE" OU "CEDENTES" SIGNIFICAM OS CEDENTES CCB E OS CEDENTES PPV, QUANDO REFERIDOS EM CONJUNTO. "CEDEN</x:v>
       </x:c>
       <x:c r="AI82" s="24" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=41970012000126</x:v>
       </x:c>
       <x:c r="AJ82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>1077334</x:v>
       </x:c>
       <x:c r="AK82" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>p. 11 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM82" s="24" t="str">
         <x:v>N/D</x:v>
@@ -10597,7 +10614,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO82" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="36" customHeight="1">
@@ -10611,19 +10628,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D83" s="39" t="n">
-        <x:v>5754060000113</x:v>
+        <x:v>52594798000140</x:v>
       </x:c>
       <x:c r="E83" s="23" t="str">
-        <x:v>05.754.060/0001-13</x:v>
+        <x:v>52.594.798/0001-40</x:v>
       </x:c>
       <x:c r="F83" s="23" t="str">
-        <x:v>CATERPILLAR FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DO SEGMENTO INDUSTRIAL II - RESP LIMITADA</x:v>
+        <x:v>MAKTUB FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G83" s="45" t="n">
-        <x:v>1666972490.26</x:v>
+        <x:v>1800909934.43</x:v>
       </x:c>
       <x:c r="H83" s="51" t="n">
-        <x:v>0.0020295233827502535</x:v>
+        <x:v>0.0021327571804288952</x:v>
       </x:c>
       <x:c r="I83" s="51" t="n">
         <x:v>0</x:v>
@@ -10671,49 +10688,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X83" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="Y83" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z83" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA83" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB83" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC83" s="23" t="str">
-        <x:v>Multissetorial / Outros</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD83" s="23" t="str">
-        <x:v>Multicarteira outros</x:v>
-      </x:c>
-      <x:c r="AE83" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE83" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF83" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG83" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH83" s="23" t="str">
-        <x:v>A SEXTA-FEIRA, EXCETO FERIADOS, NO HORARIO DAS 8H AS 18H (HORARIO DE BRASILIA). 4 CAPITULO III – DA POLITICA DE INVESTIMENTO E DOS FATORES DE RISCOS COMUNS AS CLASSES ARTIGO 6O - CADA CLASSE CONTA COM PATRIMONIO SEGREGADO E PODERA SEGUIR UMA POLITICA DE INVESTIMENTOS ESPECIFICA. A POLITICA DE INVESTIMENTOS A SER OBSERVADA PELA GESTORA, COM RELACAO A CADA CLASSE, ESTA INDICADA NO RESPECTIVO ANEXO. TODOS OS LIMITES DE INVESTIMENTO SERAO INDICADOS E DEVERAO SER INTERPRETADOS COM RELACAO AO PATRIMONIO LIQUIDO DA CLASSE CORRESPONDENTE. PARAGRAFO UNICO – O INVESTIMENTO EM CADA CLASSE E/OU SUBCLASSE NAO E GARANTIDO, DE FORMA ALGUMA, PELO FGC – FUNDO GARANTIDOR DE CREDITOS, PELA ADMINISTRADORA, PELA GESTORA, OU POR QUALQUER OUTRO PRESTADOR DE SERVICOS DO FUNDO. O INVESTIMENTO EM UMA CLASSE E/OU SUBCLASSE DESTE FUNDO</x:v>
+        <x:v>RECEBER OU ORIENTAR O RECEBIMENTO DE DEPOSITO EM CONTA QUE NAO SEJA DE TITULARIDADE DA CLASSE DE COTAS OU SEJA CONTA VINCULADA. VIII – DA NATUREZA, DOS PROCESSOS DE ORIGINACAO DOS DIREITOS CREDITORIOS E DA POLITICA DE CONCESSAO DE CREDITO 8.1. OS DIREITOS CREDITORIOS PASSIVEIS DE SEREM ADQUIRIDOS PELA CLASSE DECORREM DE CEDULAS DE CREDITO BANCARIO REPRESENTATIVAS DE EMPRESTIMOS OU SAQUE, NO AMBITO DE CARTAO DE CREDITO CONSIGNADO ("CCB"). 8.2. A ORIGINACAO DOS DIREITOS CREDITORIOS SE DA POR MEIO DE OPERACOES REALIZADAS PELOS CEDENTES NOS SEGMENTOS INDICADOS NO ITEM 8.1 ACIMA. 8.3. A POLITICA DE CONCESSAO DE CREDITO E DESENVOLVIDA E MONITORADA PELO GESTOR E PELA CONSULTORA, QUE SAO TECNICAMENTE CAPACITADAS PARA REALIZAR A AVALIACAO DA CAPACIDADE ECONOMICA DAS CEDENTES, BEM COMO DOS RESPECTIVOS DEVEDORES DOS DIREITOS CREDITORIOS.</x:v>
       </x:c>
       <x:c r="AI83" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=05754060000113</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=52594798000140</x:v>
       </x:c>
       <x:c r="AJ83" s="23" t="str">
-        <x:v>1097864</x:v>
+        <x:v>1168723</x:v>
       </x:c>
       <x:c r="AK83" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL83" s="23" t="str">
-        <x:v>p. 4</x:v>
+        <x:v>p. 32 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM83" s="23" t="str">
         <x:v>N/D</x:v>
@@ -10736,22 +10753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D84" s="38" t="n">
-        <x:v>12428086000137</x:v>
+        <x:v>40750266000176</x:v>
       </x:c>
       <x:c r="E84" s="24" t="str">
-        <x:v>12.428.086/0001-37</x:v>
+        <x:v>40.750.266/0001-76</x:v>
       </x:c>
       <x:c r="F84" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS MULTISSETORIAL BS NP</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MT I RECEIVABLES RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G84" s="44" t="n">
-        <x:v>1629151199.24</x:v>
+        <x:v>1755240553.43</x:v>
       </x:c>
       <x:c r="H84" s="50" t="n">
-        <x:v>0.0019834763154234734</x:v>
+        <x:v>0.0020786724655903815</x:v>
       </x:c>
       <x:c r="I84" s="50" t="n">
-        <x:v>0.2583621140487779</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J84" s="50" t="str">
         <x:v>N/D</x:v>
@@ -10796,49 +10813,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X84" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y84" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z84" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA84" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB84" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC84" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD84" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE84" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira outros</x:v>
+      </x:c>
+      <x:c r="AE84" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF84" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG84" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH84" s="24" t="str">
-        <x:v>O PAGAMENTO PELO ACEITANTE, NO CASO DA DUPL ICATA DIGITAL, SAO FEITOS POR BOLETO BANCARIO. DESSA FORMA, O FUNDO PODERA ENCONTRAR DIFICULDADES PARA REALIZAR A EXECUCAO JUDICIAL DOS DIREITOS CREDITORIOS REPRESENTADOS POR DUPLICATAS DIGITAIS. 4CB475AF-2E14-457E-B966-D5E3A2BC507A</x:v>
+        <x:v>AVEIS AS MANIFESTACOES DE VONTADE DOS COTISTAS; (VI) REMUNERACAO DOS PRESTADORES DE SERVICOS; (VII) POLITICA DE INVESTIMENTO E COMPOSICAO E DIVERSIFICACAO DA CARTEIRA; (VIII) EVENTOS DE AVALIACAO, EVENTOS DE LIQUIDACAO E LIQUIDACAO ANTECIPADA DA CLASSE; (IX) ORIGEM DOS DIREITOS CREDITORIOS; (X) CRITERIOS DE ELEGIBILIDADE; (XI) CUSTOS REFERENTES A DEFESA DOS INTERESSES DE CADA CLASSE DE COTAS; E (XII) FATORES DE RISCO. CAPITULO 2 – RESPONSABILIDADE DOS PRESTADORES DE SERVICOS ESSENCIAIS E DEMAIS PRESTADORES DE SERVICOS DO FUNDO 2.1 OS PRESTADORES DE SERVICOS ESSENCIAIS E DEMAIS PRESTADORES DE SERVICOS DO FUNDO RESPONDEM PERANTE A CVM, NAS SUAS RESPECTIVAS ESFERAS DE ATUACAO, POR SEUS PROPRIOS ATOS E OMISSOES CONTRARIOS A LEI, AO REGULAMENTO OU A REGULAMENTACAO VIGENTE, SEM PREJUIZO DO EXERCICIO DO DEVER DE FIS</x:v>
       </x:c>
       <x:c r="AI84" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=12428086000137</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=40750266000176</x:v>
       </x:c>
       <x:c r="AJ84" s="24" t="str">
-        <x:v>1138775</x:v>
+        <x:v>1045050</x:v>
       </x:c>
       <x:c r="AK84" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL84" s="24" t="str">
-        <x:v>p. 70 — política/definição do lastro</x:v>
+        <x:v>p. 3</x:v>
       </x:c>
       <x:c r="AM84" s="24" t="str">
         <x:v>N/D</x:v>
@@ -10861,22 +10878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D85" s="39" t="n">
-        <x:v>26722650000134</x:v>
+        <x:v>22358482000199</x:v>
       </x:c>
       <x:c r="E85" s="23" t="str">
-        <x:v>26.722.650/0001-34</x:v>
+        <x:v>22.358.482/0001-99</x:v>
       </x:c>
       <x:c r="F85" s="23" t="str">
-        <x:v>VERDECARD FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>AFINITTY MF FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS FINANCEIROS - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G85" s="45" t="n">
-        <x:v>1610706096.38</x:v>
+        <x:v>1737053741.97</x:v>
       </x:c>
       <x:c r="H85" s="51" t="n">
-        <x:v>0.0019610195755730368</x:v>
+        <x:v>0.002057134435293104</x:v>
       </x:c>
       <x:c r="I85" s="51" t="n">
-        <x:v>0.2141487023527794</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J85" s="51" t="str">
         <x:v>N/D</x:v>
@@ -10921,13 +10938,13 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X85" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y85" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z85" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA85" s="23" t="str">
         <x:v>Financeiro</x:v>
@@ -10936,34 +10953,34 @@
         <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC85" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD85" s="23" t="str">
-        <x:v>Banco emissor/cartão de crédito</x:v>
-      </x:c>
-      <x:c r="AE85" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE85" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF85" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG85" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH85" s="23" t="str">
-        <x:v>Direção aprovada: Financeiro / Cartão de crédito</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI85" s="23" t="str">
-        <x:v>FundosNet/B3 — regulamento 899881</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ85" s="23" t="str">
-        <x:v>899881</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK85" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL85" s="23" t="str">
-        <x:v>pp. 47–48 — transações no arranjo Verdecard</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM85" s="23" t="str">
         <x:v>N/D</x:v>
@@ -10972,7 +10989,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO85" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="36" customHeight="1">
@@ -10986,22 +11003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D86" s="38" t="n">
-        <x:v>8632394000102</x:v>
+        <x:v>5754060000113</x:v>
       </x:c>
       <x:c r="E86" s="24" t="str">
-        <x:v>08.632.394/0001-02</x:v>
+        <x:v>05.754.060/0001-13</x:v>
       </x:c>
       <x:c r="F86" s="24" t="str">
-        <x:v>RED - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MULTISETORIAL LP - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>CATERPILLAR FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DO SEGMENTO INDUSTRIAL II - RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G86" s="44" t="n">
-        <x:v>1569551198.23</x:v>
+        <x:v>1717939470.45</x:v>
       </x:c>
       <x:c r="H86" s="50" t="n">
-        <x:v>0.0019109138728105979</x:v>
+        <x:v>0.0020344980451807632</x:v>
       </x:c>
       <x:c r="I86" s="50" t="n">
-        <x:v>0.4131668988153203</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J86" s="50" t="str">
         <x:v>N/D</x:v>
@@ -11046,49 +11063,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X86" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>Multicarteira outros</x:v>
       </x:c>
       <x:c r="Y86" s="24" t="str">
         <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z86" s="24" t="str">
-        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA86" s="24" t="str">
         <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB86" s="24" t="str">
-        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AC86" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Multissetorial / Outros</x:v>
       </x:c>
       <x:c r="AD86" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE86" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Multicarteira outros</x:v>
+      </x:c>
+      <x:c r="AE86" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF86" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG86" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH86" s="24" t="str">
-        <x:v>A política contempla direitos dos setores comercial, industrial, financeiro e de serviços. O foco oficial Multicarteira Agro, Indústria e Comércio é aderente.</x:v>
+        <x:v>A SEXTA-FEIRA, EXCETO FERIADOS, NO HORARIO DAS 8H AS 18H (HORARIO DE BRASILIA). 4 CAPITULO III – DA POLITICA DE INVESTIMENTO E DOS FATORES DE RISCOS COMUNS AS CLASSES ARTIGO 6O - CADA CLASSE CONTA COM PATRIMONIO SEGREGADO E PODERA SEGUIR UMA POLITICA DE INVESTIMENTOS ESPECIFICA. A POLITICA DE INVESTIMENTOS A SER OBSERVADA PELA GESTORA, COM RELACAO A CADA CLASSE, ESTA INDICADA NO RESPECTIVO ANEXO. TODOS OS LIMITES DE INVESTIMENTO SERAO INDICADOS E DEVERAO SER INTERPRETADOS COM RELACAO AO PATRIMONIO LIQUIDO DA CLASSE CORRESPONDENTE. PARAGRAFO UNICO – O INVESTIMENTO EM CADA CLASSE E/OU SUBCLASSE NAO E GARANTIDO, DE FORMA ALGUMA, PELO FGC – FUNDO GARANTIDOR DE CREDITOS, PELA ADMINISTRADORA, PELA GESTORA, OU POR QUALQUER OUTRO PRESTADOR DE SERVICOS DO FUNDO. O INVESTIMENTO EM UMA CLASSE E/OU SUBCLASSE DESTE FUNDO</x:v>
       </x:c>
       <x:c r="AI86" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=08632394000102</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=05754060000113</x:v>
       </x:c>
       <x:c r="AJ86" s="24" t="str">
-        <x:v>1265950</x:v>
+        <x:v>1097864</x:v>
       </x:c>
       <x:c r="AK86" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL86" s="24" t="str">
-        <x:v>p. 24 — política/definição do lastro</x:v>
+        <x:v>p. 4</x:v>
       </x:c>
       <x:c r="AM86" s="24" t="str">
         <x:v>N/D</x:v>
@@ -11111,22 +11128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D87" s="39" t="n">
-        <x:v>58893662000118</x:v>
+        <x:v>50114948000146</x:v>
       </x:c>
       <x:c r="E87" s="23" t="str">
-        <x:v>58.893.662/0001-18</x:v>
+        <x:v>50.114.948/0001-46</x:v>
       </x:c>
       <x:c r="F87" s="23" t="str">
-        <x:v>JIVE BOSSANOVA90 - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>DRIVER BRASIL SIX BANCO VOLKSWAGEN FIDC FINANCIAMENTO DE VEÍCULOS - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G87" s="45" t="n">
-        <x:v>1554710409.76</x:v>
+        <x:v>1717932634.87</x:v>
       </x:c>
       <x:c r="H87" s="51" t="n">
-        <x:v>0.0018928453519475945</x:v>
+        <x:v>0.0020344899500328332</x:v>
       </x:c>
       <x:c r="I87" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0.1505283858312573</x:v>
       </x:c>
       <x:c r="J87" s="51" t="str">
         <x:v>N/D</x:v>
@@ -11171,49 +11188,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X87" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y87" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z87" s="23" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AA87" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB87" s="23" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Financiamento de Veículos</x:v>
       </x:c>
       <x:c r="AC87" s="23" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD87" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
-      </x:c>
-      <x:c r="AE87" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE87" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF87" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG87" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH87" s="23" t="str">
-        <x:v>regulamento 1044435 p. 11 [precatórios e requisitórios contra entes públicos]: O JUDICIAL DA CLASSE E O MONITORAMENTO DOS DIREITOS CREDITORIOS; E (2) PREVIAMENTE A AQUISICAO DE CADA DIREITO CREDITORIO, POSSUIR O OFICIO REQUISITORIO E A CERTIDAO DE REMESSA DO PRECATORIO AO TRIBUNAL REGIONAL FE DERAL COMPETENTE, OU O || CEDENTE/ORIGINADOR: regulamento 1044435 p. 39: CEDENTE SERA RESPONSAVEL PELA EXISTENCIA DOS DIREITOS CREDITORIOS CEDIDOS, NOS TERMOS DO ARTIGO 295 DO CODIGO CIVIL BRASILEIRO</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI87" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=58893662000118</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ87" s="23" t="str">
-        <x:v>1044435</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK87" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL87" s="23" t="str">
-        <x:v>regulamento 1044435 p. 11</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM87" s="23" t="str">
         <x:v>N/D</x:v>
@@ -11222,7 +11239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO87" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="36" customHeight="1">
@@ -11236,22 +11253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D88" s="38" t="n">
-        <x:v>53036495000175</x:v>
+        <x:v>32526025000110</x:v>
       </x:c>
       <x:c r="E88" s="24" t="str">
-        <x:v>53.036.495/0001-75</x:v>
+        <x:v>32.526.025/0001-10</x:v>
       </x:c>
       <x:c r="F88" s="24" t="str">
-        <x:v>XP RETURN I CONSIGNADO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESP LIMITADA</x:v>
+        <x:v>COBUCCIO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE CLASSE ÚNICA FECHADA DE RESPONS LIMITADA</x:v>
       </x:c>
       <x:c r="G88" s="44" t="n">
-        <x:v>1546482100.39</x:v>
+        <x:v>1695951362.31</x:v>
       </x:c>
       <x:c r="H88" s="50" t="n">
-        <x:v>0.0018828274624116293</x:v>
+        <x:v>0.0020084582668314505</x:v>
       </x:c>
       <x:c r="I88" s="50" t="n">
-        <x:v>0.2072981702268535</x:v>
+        <x:v>0.7583035475960594</x:v>
       </x:c>
       <x:c r="J88" s="50" t="str">
         <x:v>N/D</x:v>
@@ -11296,49 +11313,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="Y88" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z88" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA88" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB88" s="24" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD88" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="AE88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
+      </x:c>
+      <x:c r="AE88" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF88" s="24" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG88" s="24" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Direção aprovada: Financeiro / Cartão de crédito</x:v>
       </x:c>
       <x:c r="AI88" s="24" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>FundosNet/B3 — regulamento 1186789</x:v>
       </x:c>
       <x:c r="AJ88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Regulamento id 1186789</x:v>
       </x:c>
       <x:c r="AK88" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>pp. 5–10 — cartões Brasil Card, faturas, carnês e CCBs</x:v>
       </x:c>
       <x:c r="AM88" s="24" t="str">
         <x:v>N/D</x:v>
@@ -11347,7 +11364,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO88" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="36" customHeight="1">
@@ -11361,22 +11378,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D89" s="39" t="n">
-        <x:v>62310468000130</x:v>
+        <x:v>8632394000102</x:v>
       </x:c>
       <x:c r="E89" s="23" t="str">
-        <x:v>62.310.468/0001-30</x:v>
+        <x:v>08.632.394/0001-02</x:v>
       </x:c>
       <x:c r="F89" s="23" t="str">
-        <x:v>MT INSS RECEIVABLES VI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>RED - FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS MULTISETORIAL LP - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G89" s="45" t="n">
-        <x:v>1535189477.94</x:v>
+        <x:v>1626299680.36</x:v>
       </x:c>
       <x:c r="H89" s="51" t="n">
-        <x:v>0.0018690788004218498</x:v>
+        <x:v>0.0019259721180419891</x:v>
       </x:c>
       <x:c r="I89" s="51" t="n">
-        <x:v>0.2026710288510487</x:v>
+        <x:v>0.4183096467682989</x:v>
       </x:c>
       <x:c r="J89" s="51" t="str">
         <x:v>N/D</x:v>
@@ -11421,49 +11438,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y89" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z89" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AA89" s="23" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AB89" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="AC89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="AE89" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF89" s="23" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG89" s="23" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>A política contempla direitos dos setores comercial, industrial, financeiro e de serviços. O foco oficial Multicarteira Agro, Indústria e Comércio é aderente.</x:v>
       </x:c>
       <x:c r="AI89" s="23" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=08632394000102</x:v>
       </x:c>
       <x:c r="AJ89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>1265950</x:v>
       </x:c>
       <x:c r="AK89" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>p. 24 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM89" s="23" t="str">
         <x:v>N/D</x:v>
@@ -11472,7 +11489,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO89" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="36" customHeight="1">
@@ -11486,109 +11503,109 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D90" s="38" t="n">
-        <x:v>23200289000198</x:v>
+        <x:v>38376526000143</x:v>
       </x:c>
       <x:c r="E90" s="24" t="str">
-        <x:v>23.200.289/0001-98</x:v>
+        <x:v>38.376.526/0001-43</x:v>
       </x:c>
       <x:c r="F90" s="24" t="str">
-        <x:v>CF FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>HOTFUND FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDAD</x:v>
       </x:c>
       <x:c r="G90" s="44" t="n">
-        <x:v>1481651371.98</x:v>
+        <x:v>1596122150.92</x:v>
       </x:c>
       <x:c r="H90" s="50" t="n">
-        <x:v>0.0018038966582156319</x:v>
+        <x:v>0.001890233882958548</x:v>
       </x:c>
       <x:c r="I90" s="50" t="n">
+        <x:v>0.7492493155245668</x:v>
+      </x:c>
+      <x:c r="J90" s="50" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="K90" s="50" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="L90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="M90" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="N90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="O90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="P90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="Q90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="R90" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="S90" s="32" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="T90" s="32" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="U90" s="44" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="V90" s="24" t="str">
+        <x:v>Hotmart</x:v>
+      </x:c>
+      <x:c r="W90" s="24" t="str">
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="X90" s="24" t="str">
+        <x:v>antecipação de parcelas de criadores de conteúdo</x:v>
+      </x:c>
+      <x:c r="Y90" s="24" t="str">
+        <x:v>Financeiro</x:v>
+      </x:c>
+      <x:c r="Z90" s="24" t="str">
+        <x:v>Multicarteira Financeiro</x:v>
+      </x:c>
+      <x:c r="AA90" s="24" t="str">
+        <x:v>Financeiro</x:v>
+      </x:c>
+      <x:c r="AB90" s="24" t="str">
+        <x:v>Adquirência</x:v>
+      </x:c>
+      <x:c r="AC90" s="24" t="str">
+        <x:v>Meios de Pagamento e Cartões</x:v>
+      </x:c>
+      <x:c r="AD90" s="24" t="str">
+        <x:v>Arranjos de pagamento/adquirência</x:v>
+      </x:c>
+      <x:c r="AE90" s="26" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J90" s="50" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="K90" s="50" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="L90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="M90" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="N90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="O90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="P90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="Q90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="R90" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="S90" s="32" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="T90" s="32" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="U90" s="44" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="V90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="W90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="X90" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="Y90" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
-      </x:c>
-      <x:c r="Z90" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
-      </x:c>
-      <x:c r="AA90" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
-      </x:c>
-      <x:c r="AB90" s="24" t="str">
-        <x:v>Fomento Mercantil</x:v>
-      </x:c>
-      <x:c r="AC90" s="24" t="str">
-        <x:v>Crédito PJ</x:v>
-      </x:c>
-      <x:c r="AD90" s="24" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
-      </x:c>
-      <x:c r="AE90" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
       <x:c r="AF90" s="24" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG90" s="24" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH90" s="24" t="str">
-        <x:v>COMO OBJETIVO PROPORCIONAR AOS COTISTAS A VALORIZACAO DAS COTAS DE SUAS RESPECTIVAS TITULARIDADES POR MEIO DA APLICACAO DOS RECURSOS DA CLASSE, PREPONDERANTEMENTE NA AQUISICAO DE DIREITOS CREDITORIOS, PADRONIZADOS E/OU NAO - PADRONIZADOS, NOS SEGMENTOS INDUSTRIAL, COMERCIAL, DO AGRONEG OCIO, FINANCEIRO E DE PRESTACAO DE SERVICOS, (“DIREITOS CREDITORIOS”) REPRESENTADOS POR: DIREITOS CREDITORIOS CONCENTRACAO (A) DIREITOS E TITULOS REPRESENTATIVOS DE CREDITO, TAIS COMO, MAS NAO LIMITADAMENTE A: DUPLICATAS, NOTAS PROMISSORIAS, CEDULAS DE CREDITO BANCARIO, CEDULAS DE CREDITO IMOBILIARIO, CEDULAS DE PRODUTOR RURAL, NUMERO SEQUENCIAL UNICO (“NSU”), CEDULAS E NOTAS DE CREDITOS A EXPORTACAO, INVOICES, CERTIFICADOS DE EMBARQUE, DIREITOS CREDITORIOS DECORRENTES DE OPERACOES DE CARTOES DE CREDITO, BEM COMO DE OPERACOES DE EXPORTACAO DE BENS E SERVICOS; ATE 100% (B) VALORES MOBILIARIOS REPRESENTATIVOS DE CREDITO, TAIS COMO, MAS NAO SE LIMITANDO, A: NOTAS COMERCIAIS, DEBENTURES (PUBLICAS E/OU PRIVADAS), CERTIFICADO DE DEPOSIT</x:v>
+        <x:v>Nota 6 (a): «…DECORRENTES DE TRANSAÇÕES DE PAGAMENTO REALIZADAS POR USUÁRIOS COMPRADORES COM CARTÃO, À VISTA OU PARCELADAS, OPERACIONALIZADA PELO SISTEMA HOTPAY NO ÂMBITO DO RESPECTIVO ARRANJO DE PAGAMENTO»; «A MAIS RELEVANTE PARA FINS DA OPERAÇÃO DA CLASSE É O CRÉDITO DO PRODUTOR EM FACE DA SUBCREDENCIADORA (I.E., HOTMART)». A liquidação descrita na mesma nota passa por bandeiras, CIP/SILOC e credenciadoras.</x:v>
       </x:c>
       <x:c r="AI90" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=23200289000198</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=38376526000143</x:v>
       </x:c>
       <x:c r="AJ90" s="24" t="str">
-        <x:v>1126088</x:v>
+        <x:v>1072072</x:v>
       </x:c>
       <x:c r="AK90" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL90" s="24" t="str">
-        <x:v>p. 51 — política/definição do lastro</x:v>
+        <x:v>Demonstrações financeiras, nota explicativa 6 (a) e 6 (e)</x:v>
       </x:c>
       <x:c r="AM90" s="24" t="str">
         <x:v>N/D</x:v>
@@ -11597,7 +11614,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO90" s="24" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>documentado — parte ou lastro identificado</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="36" customHeight="1">
@@ -11611,22 +11628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D91" s="39" t="n">
-        <x:v>57833038000162</x:v>
+        <x:v>8417544000165</x:v>
       </x:c>
       <x:c r="E91" s="23" t="str">
-        <x:v>57.833.038/0001-62</x:v>
+        <x:v>08.417.544/0001-65</x:v>
       </x:c>
       <x:c r="F91" s="23" t="str">
-        <x:v>ALDEBARAN II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>PRAVALER CRÉDITO UNIVERSITÁRIO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS - RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G91" s="45" t="n">
-        <x:v>1477350540.58</x:v>
+        <x:v>1572064332.62</x:v>
       </x:c>
       <x:c r="H91" s="51" t="n">
-        <x:v>0.0017986604362968135</x:v>
+        <x:v>0.001861743016345044</x:v>
       </x:c>
       <x:c r="I91" s="51" t="n">
-        <x:v>0.0467152180434417</x:v>
+        <x:v>0.2179779669744</x:v>
       </x:c>
       <x:c r="J91" s="51" t="str">
         <x:v>N/D</x:v>
@@ -11671,49 +11688,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X91" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y91" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z91" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA91" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB91" s="23" t="str">
-        <x:v>Fomento Mercantil</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AC91" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD91" s="23" t="str">
-        <x:v>Recebíveis comerciais/multissetorial</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AE91" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF91" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG91" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH91" s="23" t="str">
-        <x:v>A POLITICA DE EXERCICIO DE DIREITO DE VOTO DA GESTORA ESTA DISPONIVEL NA PAGINA DA GESTORA NA REDE MUNDIAL DE COMPUTADORES , NO SEGUINTE ENDERECO: HTTPS://WWW.EMERALD.COM.BR/ 11. DIREITOS CREDITORIOS CARACTERISTICAS DOS DIREITOS CREDITORIOS 11.1. OS DIREITOS CREDITORIOS A SEREM ADQUIRIDOS PELO FUNDO SERAO DECORRENTES DE OPERACOES REALIZADAS NOS SEGMENTOS MERCANTIL, COMERCIAL E FINANCEIRO, REPRESENTADOS POR (A) DIREITOS E TITULOS DE CREDITO, TAIS COMO, MAS NAO SE LIMITANDO DUPLICATAS, CHEQUES, NOTAS PROMISSORIAS, CEDULAS DE CREDITO BANCARIO (CCB), RECEBIVEIS DE CARTAO DE CREDITO, CEDULAS DE PRODUTOR RURAL FINANCEIRAS, CEDULAS DE CREDITO IMOBILIARIO, PARCELAS DE EMPRESTIMOS CONSIGNADOS, NOTAS COMERCIAIS (NC), NOTAS DE CREDITO DE EXPORTACAO (NCE) OU INSTRUMENTOS CONTRATUAIS DECORRENTES DE OPERACAO DE CREDITO; (B) VALORES MOBILIARIOS REPRESENTATIVOS DE CREDITO; (C) CERTIFICADOS DE RECEBIVEIS E OUTROS VALORES MOBILIARIOS REPRESENTATIVOS DE OPERACOES DE SECURITIZACAO, QUE NAO SEJAM LASTREADOS EM DI</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI91" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=57833038000162</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ91" s="23" t="str">
-        <x:v>1231073</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK91" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL91" s="23" t="str">
-        <x:v>p. 29 — política/definição do lastro</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM91" s="23" t="str">
         <x:v>N/D</x:v>
@@ -11722,7 +11739,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO91" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="36" customHeight="1">
@@ -11736,22 +11753,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D92" s="38" t="n">
-        <x:v>66929956000180</x:v>
+        <x:v>12428086000137</x:v>
       </x:c>
       <x:c r="E92" s="24" t="str">
-        <x:v>66.929.956/0001-80</x:v>
+        <x:v>12.428.086/0001-37</x:v>
       </x:c>
       <x:c r="F92" s="24" t="str">
-        <x:v>BV AUTO III SEGMENTO FINANCEIRO FIDC RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS MULTISSETORIAL BS NP</x:v>
       </x:c>
       <x:c r="G92" s="44" t="n">
-        <x:v>1461910524.62</x:v>
+        <x:v>1565448244.56</x:v>
       </x:c>
       <x:c r="H92" s="50" t="n">
-        <x:v>0.0017798623615811534</x:v>
+        <x:v>0.0018539078053516744</x:v>
       </x:c>
       <x:c r="I92" s="50" t="n">
-        <x:v>0.1500607076560145</x:v>
+        <x:v>0.2103059766797605</x:v>
       </x:c>
       <x:c r="J92" s="50" t="str">
         <x:v>N/D</x:v>
@@ -11796,25 +11813,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X92" s="24" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y92" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z92" s="24" t="str">
-        <x:v>Multicarteira Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA92" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB92" s="24" t="str">
-        <x:v>Financiamento de Veículos</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC92" s="24" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD92" s="24" t="str">
-        <x:v>Auto/Veículos</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="AE92" s="24" t="str">
         <x:v>N/D</x:v>
@@ -11826,19 +11843,19 @@
         <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH92" s="24" t="str">
-        <x:v>Def. "Devedores": pessoas físicas que adquiriram um Veículo Automotor mediante financiamento concedido pelo Emitente por meio de emissão de CCBs. É financiamento ao consumidor, o oposto do floor plan de montadora.</x:v>
+        <x:v>O PAGAMENTO PELO ACEITANTE, NO CASO DA DUPL ICATA DIGITAL, SAO FEITOS POR BOLETO BANCARIO. DESSA FORMA, O FUNDO PODERA ENCONTRAR DIFICULDADES PARA REALIZAR A EXECUCAO JUDICIAL DOS DIREITOS CREDITORIOS REPRESENTADOS POR DUPLICATAS DIGITAIS. 4CB475AF-2E14-457E-B966-D5E3A2BC507A</x:v>
       </x:c>
       <x:c r="AI92" s="24" t="str">
-        <x:v>Industria_FIDC_202606_auditada.xlsx#Auditoria classificação Top200</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=12428086000137</x:v>
       </x:c>
       <x:c r="AJ92" s="24" t="str">
-        <x:v>Regulamento arquivado no FundosNET</x:v>
+        <x:v>1138775</x:v>
       </x:c>
       <x:c r="AK92" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL92" s="24" t="str">
-        <x:v>Regulamento arquivado no FundosNET</x:v>
+        <x:v>p. 70 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM92" s="24" t="str">
         <x:v>N/D</x:v>
@@ -11861,22 +11878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D93" s="39" t="n">
-        <x:v>39669950000149</x:v>
+        <x:v>26722650000134</x:v>
       </x:c>
       <x:c r="E93" s="23" t="str">
-        <x:v>39.669.950/0001-49</x:v>
+        <x:v>26.722.650/0001-34</x:v>
       </x:c>
       <x:c r="F93" s="23" t="str">
-        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SOMACRED BACH - RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>VERDECARD FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G93" s="45" t="n">
-        <x:v>1461275229.61</x:v>
+        <x:v>1550515087.47</x:v>
       </x:c>
       <x:c r="H93" s="51" t="n">
-        <x:v>0.0017790888958609493</x:v>
+        <x:v>0.0018362229687025554</x:v>
       </x:c>
       <x:c r="I93" s="51" t="n">
-        <x:v>0.163315788124124</x:v>
+        <x:v>0.2164128724195619</x:v>
       </x:c>
       <x:c r="J93" s="51" t="str">
         <x:v>N/D</x:v>
@@ -11921,7 +11938,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X93" s="23" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="Y93" s="23" t="str">
         <x:v>Outros</x:v>
@@ -11933,13 +11950,13 @@
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB93" s="23" t="str">
-        <x:v>Crédito Consignado</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC93" s="23" t="str">
-        <x:v>Crédito PF</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD93" s="23" t="str">
-        <x:v>Consignado/INSS</x:v>
+        <x:v>Banco emissor/cartão de crédito</x:v>
       </x:c>
       <x:c r="AE93" s="27" t="b">
         <x:v>0</x:v>
@@ -11951,19 +11968,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH93" s="23" t="str">
-        <x:v>regulamento 1238679 p. 37 [crédito consignado]: PAGINA 46 DE 209 DE ATUACAO “CREDITO CONSIGNADO”. PARAGRAFO NONO O PRESENTE ANEXO DESCRITIVO CONSTITUI PARTE INTEGRANTE DO REGULAMENTO, BEM COMO SERA POR ELE SERA REGIDO, DEVENDO PREVALECER AS DISPOSICOES DO ANEXO DESCRITIVO EM CASO DE QUALQUER CONFLITO OU CONTROVERSIA EM RELACAO AS DISPOSICOES DA PARTE GERAL DO REGULAMENTO. ARTIGO 2O OS TERMOS E EXPRESSOES INICIAD || CEDENTE/ORIGINADOR: regulamento 1238679 p. 9: CEDENTE E SUAS RESPECTIVAS PARTES RELACIONADAS, TAL COMO DEFINIDO PELAS REGRAS CONTABEIS QUE TRATAM DESTE ASSUNTO, EXCETO CONFORME PREVISAO DOS §§ 3O E 4O DO ARTIGO 32 DO ANEXO NORMATIVO II</x:v>
+        <x:v>Direção aprovada: Financeiro / Cartão de crédito</x:v>
       </x:c>
       <x:c r="AI93" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=39669950000149</x:v>
+        <x:v>FundosNet/B3 — regulamento 899881</x:v>
       </x:c>
       <x:c r="AJ93" s="23" t="str">
-        <x:v>Regulamento id 1238679</x:v>
+        <x:v>899881</x:v>
       </x:c>
       <x:c r="AK93" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL93" s="23" t="str">
-        <x:v>regulamento 1238679 p. 37</x:v>
+        <x:v>pp. 47–48 — transações no arranjo Verdecard</x:v>
       </x:c>
       <x:c r="AM93" s="23" t="str">
         <x:v>N/D</x:v>
@@ -11986,22 +12003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D94" s="38" t="n">
-        <x:v>13764696000174</x:v>
+        <x:v>62310468000130</x:v>
       </x:c>
       <x:c r="E94" s="24" t="str">
-        <x:v>13.764.696/0001-74</x:v>
+        <x:v>62.310.468/0001-30</x:v>
       </x:c>
       <x:c r="F94" s="24" t="str">
-        <x:v>JC 4870 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
+        <x:v>MT INSS RECEIVABLES VI FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G94" s="44" t="n">
-        <x:v>1447126452.7</x:v>
+        <x:v>1544332585.59</x:v>
       </x:c>
       <x:c r="H94" s="50" t="n">
-        <x:v>0.0017618628925861845</x:v>
+        <x:v>0.0018289012392670638</x:v>
       </x:c>
       <x:c r="I94" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.2072216817801345</x:v>
       </x:c>
       <x:c r="J94" s="50" t="str">
         <x:v>N/D</x:v>
@@ -12046,49 +12063,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X94" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y94" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z94" s="24" t="str">
-        <x:v>Multicarteira Outros</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA94" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB94" s="24" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC94" s="24" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD94" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
-      </x:c>
-      <x:c r="AE94" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE94" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF94" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG94" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH94" s="24" t="str">
-        <x:v>regulamento 734547 p. 7 [precatórios e requisitórios contra entes públicos]: , NESSA MESMA DATA, QUOTAS REPRESENTATIVAS DO VALOR CORRESPONDENTE. “DEVEDOR(ES)” SIGNIFICA O(S) AUTOR(ES) DAS ACOES JUDICIAIS, OU SEJA, AS USINAS, SENDO QUE, CASO SEJAM EXPEDIDOS PRECATORIOS DISTINTOS (UM PARA O CREDITO DAS USINAS E OUTRO PARA O CREDITO REFERENTE AOS HONORARIOS ADVOCATICIOS - CONTRATUAIS E/OU SUCUMBENCIAIS - CORRESPONDENTES AOS DIREITOS CREDITORIOS), A UNIAO FEDERAL PASSARA A SER INCLUIDA NA DEFINICAO DE DEVEDORES. “DIA UTIL ” SIGNIFICA QUALQUER DIA, QUE NAO UM SABADO, DOMINGO, OU OUTRO D || CEDENTE/ORIGINADOR: regulamento 734547 p. 7: CEDENTE E OS AUTORES DAS ACOES PRINCIPAIS, NOS TERMOS DOS CONTRATOS DE SERVICOS JURIDICOS</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI94" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=13764696000174</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ94" s="24" t="str">
-        <x:v>Regulamento id 734547</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK94" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL94" s="24" t="str">
-        <x:v>regulamento 734547 p. 7</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM94" s="24" t="str">
         <x:v>N/D</x:v>
@@ -12097,7 +12114,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO94" s="24" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="36" customHeight="1">
@@ -12111,22 +12128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D95" s="39" t="n">
-        <x:v>47227790000106</x:v>
+        <x:v>53036495000175</x:v>
       </x:c>
       <x:c r="E95" s="23" t="str">
-        <x:v>47.227.790/0001-06</x:v>
+        <x:v>53.036.495/0001-75</x:v>
       </x:c>
       <x:c r="F95" s="23" t="str">
-        <x:v>SAPPHIRE FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>XP RETURN I CONSIGNADO FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS RESP LIMITADA</x:v>
       </x:c>
       <x:c r="G95" s="45" t="n">
-        <x:v>1425902192.06</x:v>
+        <x:v>1514334849.03</x:v>
       </x:c>
       <x:c r="H95" s="51" t="n">
-        <x:v>0.0017360225541869902</x:v>
+        <x:v>0.0017933759268559221</x:v>
       </x:c>
       <x:c r="I95" s="51" t="n">
-        <x:v>1</x:v>
+        <x:v>0.217904449537328</x:v>
       </x:c>
       <x:c r="J95" s="51" t="str">
         <x:v>N/D</x:v>
@@ -12171,49 +12188,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X95" s="23" t="str">
-        <x:v>Crédito privado/mercado de capitais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y95" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z95" s="23" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AA95" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB95" s="23" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC95" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD95" s="23" t="str">
-        <x:v>Crédito privado/mercado de capitais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AE95" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF95" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG95" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH95" s="23" t="str">
-        <x:v>regulamento 687608 p. 28 [crédito corporativo / mercado de capitais]: OMENTE PODERA ADQUIRIR DIREITOS CREDITORIOS E COTAS INVESTIDAS QUE ATENDAM AOS SEGUINTES CRITERIOS DE ELEGIBILIDADE, A SEREM VERIFICADOS PELA GESTORA. A) DIREITOS CREDITORIOS: (I) DEBENTURES DE DISTRIBUICAO PRIVADA E NOTAS COMERCIAIS OBJETO DE DISTRIBUICAO PRIVADA; (II) OS DIREITOS CREDITORIOS NAO PODERAO ESTAR VENCIDOS E INADIMPLIDOS QUANDO DA SUA CESSAO PARA O FUNDO; (III) OS DEVEDORES DOS DIREITOS CREDITORIOS NAO PODERAO TER DIREITOS CREDITORIOS INADIMPLIDOS COM O FUNDO, OU SEJA, JA CEDIDOS AO FUNDO, H | regulamento 687608 p. 26 [precatórios e requisitórios contra entes públicos]: O, DA ADMINISTRACAO DIRETA OU INDIRETA, FEDERAL, ESTADUAL OU MUNICIPAL, INCLUSIVE AUTARQUIAS E FUNDACOES, QUE, EM RAZAO DE SENTENCA TRANSITADA EM JULGADO, ESTEJAM REPRESENTADOS EM PRECATORIOS JA EXPEDIDOS (“PRECATORIO(S)”); (B) DEBENTURES; E (C) NOTAS COMERCIAIS. 7.1.1 E PERMITIDO A CLASSE ADQUIRIR DIREITOS CREDITORIOS NAO PERFORMADOS, OU SEJA, DIREITOS CREDITORIOS CUJA EXIGIBILIDADE AINDA DEPENDA DE CONTRAPRESTACAO PELOS RESPECTIVOS CEDENTES. 7.1.2 A CLASSE PODERA ADQUIRIR DIREITOS CREDITORIOS CUJOS CEDEN || CEDENTE/ORIGINADOR: regulamento 687608 p. 26: CEDENTE SERA RESPONSAVEL PELA EXISTENCIA DOS DIREITOS CREDITORIOS CEDIDOS, NOS TERMOS DO ARTIGO 295 DO CODIGO CIVIL</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI95" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=47227790000106</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ95" s="23" t="str">
-        <x:v>687608</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK95" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL95" s="23" t="str">
-        <x:v>regulamento 687608 p. 28, regulamento 687608 p. 26</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM95" s="23" t="str">
         <x:v>N/D</x:v>
@@ -12222,7 +12239,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO95" s="23" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="36" customHeight="1">
@@ -12236,22 +12253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D96" s="38" t="n">
-        <x:v>65839682000176</x:v>
+        <x:v>66732877000185</x:v>
       </x:c>
       <x:c r="E96" s="24" t="str">
-        <x:v>65.839.682/0001-76</x:v>
+        <x:v>66.732.877/0001-85</x:v>
       </x:c>
       <x:c r="F96" s="24" t="str">
-        <x:v>FUNDO DE INVESTIMENTOS EM DIREITOS CREDITÓRIOS PICPAY FGTS II DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS CONSIG PREMIUM II - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G96" s="44" t="n">
-        <x:v>1420614297.06</x:v>
+        <x:v>1502648710.95</x:v>
       </x:c>
       <x:c r="H96" s="50" t="n">
-        <x:v>0.001729584591586687</x:v>
+        <x:v>0.0017795364258208568</x:v>
       </x:c>
       <x:c r="I96" s="50" t="n">
-        <x:v>0.1042683773033183</x:v>
+        <x:v>0.150078915375806</x:v>
       </x:c>
       <x:c r="J96" s="50" t="str">
         <x:v>N/D</x:v>
@@ -12361,19 +12378,19 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D97" s="39" t="n">
-        <x:v>57325251000163</x:v>
+        <x:v>13764696000174</x:v>
       </x:c>
       <x:c r="E97" s="23" t="str">
-        <x:v>57.325.251/0001-63</x:v>
+        <x:v>13.764.696/0001-74</x:v>
       </x:c>
       <x:c r="F97" s="23" t="str">
-        <x:v>ANGICO FIDC SEGMENTO INFRAESTRUTURA E AGRONEGÓCIO DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>JC 4870 FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
       </x:c>
       <x:c r="G97" s="45" t="n">
-        <x:v>1391099575.18</x:v>
+        <x:v>1498192276.83</x:v>
       </x:c>
       <x:c r="H97" s="51" t="n">
-        <x:v>0.0016936506943323372</x:v>
+        <x:v>0.0017742588204910008</x:v>
       </x:c>
       <x:c r="I97" s="51" t="n">
         <x:v>0</x:v>
@@ -12421,25 +12438,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X97" s="23" t="str">
-        <x:v>Agro</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="Y97" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z97" s="23" t="str">
-        <x:v>Agronegócio</x:v>
+        <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA97" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB97" s="23" t="str">
-        <x:v>Agronegócio</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC97" s="23" t="str">
-        <x:v>Agro</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD97" s="23" t="str">
-        <x:v>Agro</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="AE97" s="27" t="b">
         <x:v>0</x:v>
@@ -12451,19 +12468,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH97" s="23" t="str">
-        <x:v>O fundo adquire títulos emitidos por empresas de infraestrutura ou agronegócio descritas apenas como Devedores.</x:v>
+        <x:v>regulamento 734547 p. 7 [precatórios e requisitórios contra entes públicos]: , NESSA MESMA DATA, QUOTAS REPRESENTATIVAS DO VALOR CORRESPONDENTE. “DEVEDOR(ES)” SIGNIFICA O(S) AUTOR(ES) DAS ACOES JUDICIAIS, OU SEJA, AS USINAS, SENDO QUE, CASO SEJAM EXPEDIDOS PRECATORIOS DISTINTOS (UM PARA O CREDITO DAS USINAS E OUTRO PARA O CREDITO REFERENTE AOS HONORARIOS ADVOCATICIOS - CONTRATUAIS E/OU SUCUMBENCIAIS - CORRESPONDENTES AOS DIREITOS CREDITORIOS), A UNIAO FEDERAL PASSARA A SER INCLUIDA NA DEFINICAO DE DEVEDORES. “DIA UTIL ” SIGNIFICA QUALQUER DIA, QUE NAO UM SABADO, DOMINGO, OU OUTRO D || CEDENTE/ORIGINADOR: regulamento 734547 p. 7: CEDENTE E OS AUTORES DAS ACOES PRINCIPAIS, NOS TERMOS DOS CONTRATOS DE SERVICOS JURIDICOS</x:v>
       </x:c>
       <x:c r="AI97" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=57325251000163</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=13764696000174</x:v>
       </x:c>
       <x:c r="AJ97" s="23" t="str">
-        <x:v>1086644</x:v>
+        <x:v>Regulamento id 734547</x:v>
       </x:c>
       <x:c r="AK97" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL97" s="23" t="str">
-        <x:v>p. 8 — objetivo e política de investimento</x:v>
+        <x:v>regulamento 734547 p. 7</x:v>
       </x:c>
       <x:c r="AM97" s="23" t="str">
         <x:v>N/D</x:v>
@@ -12486,22 +12503,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D98" s="38" t="n">
-        <x:v>52327260000170</x:v>
+        <x:v>45207707000101</x:v>
       </x:c>
       <x:c r="E98" s="24" t="str">
-        <x:v>52.327.260/0001-70</x:v>
+        <x:v>45.207.707/0001-01</x:v>
       </x:c>
       <x:c r="F98" s="24" t="str">
-        <x:v>IFOOD I FIDC SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDADA</x:v>
+        <x:v>LASSIE EDUCATION CRÉDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
       </x:c>
       <x:c r="G98" s="44" t="n">
-        <x:v>1389238751.96</x:v>
+        <x:v>1487482332.28</x:v>
       </x:c>
       <x:c r="H98" s="50" t="n">
-        <x:v>0.0016913851595030459</x:v>
+        <x:v>0.0017615753926835812</x:v>
       </x:c>
       <x:c r="I98" s="50" t="n">
-        <x:v>0.1320517245293331</x:v>
+        <x:v>0.4359813410538953</x:v>
       </x:c>
       <x:c r="J98" s="50" t="str">
         <x:v>N/D</x:v>
@@ -12546,25 +12563,25 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X98" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="Y98" s="24" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="Z98" s="24" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Poder Público</x:v>
       </x:c>
       <x:c r="AA98" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Outros</x:v>
       </x:c>
       <x:c r="AB98" s="24" t="str">
-        <x:v>Adquirência</x:v>
+        <x:v>Recuperação</x:v>
       </x:c>
       <x:c r="AC98" s="24" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>Judicial/Precatórios/NPL</x:v>
       </x:c>
       <x:c r="AD98" s="24" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
+        <x:v>Precatórios/direitos judiciais</x:v>
       </x:c>
       <x:c r="AE98" s="26" t="b">
         <x:v>0</x:v>
@@ -12576,19 +12593,19 @@
         <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH98" s="24" t="str">
-        <x:v>OBSERVADOS OS CRITERIOS DE COMPOSICAO E DIVERSIFICACAO DA CARTEIRA DO FUNDO, CONFORME ESTABELECIDOS NESTE REGULAMENTO. 4.2. ORIGEM DOS DIREITOS CREDITORIOS . O FUNDO ADQUIRIRA (A) DIREITOS CREDITORIOS CARTOES E DIREITOS CREDITORIOS OUTROS, QUE SAO ORIUNDOS DO PAGAMENTO DEVIDO PELO DEVEDOR AOS CEDENTES DECORRENTES DE TRANSACOES DE PAGAMENTO REALIZADAS POR CLIENTES DOS PARCEIROS, A VISTA OU PARCELADAS, NO AMBITO DO RESPECTIVO ARRANJO DE PAGAMENTO, E (B) DIREITOS CREDITORIOS CONTA DIGITAL, QUE SAO ORIUNDOS DOS DIREITOS CREDITORIOS A PERFORMAR DETIDOS PELOS PARCEIROS EM FACE DO PROVEDOR DE DOCUSIGN ENVELOPE ID: EA3E46E7-E426-401E-A595-139E0C2E9BCF</x:v>
+        <x:v>regulamento 779778 p. 7 [classificação ANBIMA declarada no regulamento]: ER A SER DELIBERADO PELOS COTISTAS REUNIDOS EM ASSEMBLEIA ESPECIAL DE COTISTAS. CLASSIFICACAO ANBIMA TIPO “OUTROS”. FOCO DE ATUACAO “PODER PUBLICO”. OBJETIVO O OBJETIVO DA CLASSE E PROPORCIONAR RENDIMENTO DE LONGO PRAZO AS SUAS COTAS POR MEIO DO INVESTIMENTO DA PARCELA PREPONDERANTE DE SEUS RECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS (CONFORME DISPOSTO NO CAPITULO 4 DESTE ANEXO). O OBJETIVO DA CL || regulamento 779778 p. 1 [direitos judiciais privados]: REGULAMENTO LASSIE EDUCATION CREDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS BTG PACTUAL SAC: 0800 772 28 27 - OUVIDORIA: 0800 722 00 48 - BTGPACTUAL.COM 1 PARTE GERAL CAPITULO 1 FUNDO 1.1 LASSIE EDUC ATION CREDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS (“FUNDO”), INSCRITO NO CNPJ SOB O N° 45.207.707/0001-01, REGIDO PELA LEI NO 10 | regulamento 779778 p. 10 [precatórios e requisitórios contra entes públicos]: COM SENTENCA TRANSITADA EM JULGADO OU NAO, PROLATADAS OU QUE SERAO PROLATADAS NO CURSO DE ACOES JUDICIAIS CONTRA OS ENTES FEDERATIVOS, CUJOS CREDITOS PODERAO SER REPRESENTADOS POR PRECATORIOS JA EMITIDOS OU A SEREM EMITIDOS EM VIRTUDE DE EXECU CAO DAS SENTENCAS RESPECTIVAS, QUE PODERAO PREVER, CONFORME SUA ORIGEM E NATUREZA, INCIDENCIA DE JUROS E CORRECAO MONETARIA; E/OU (II) DIREITOS RELATIVOS A HONORARIOS ADVOCATICIOS RELACIONADOS AOS CREDITOS ANTERIORMENTE MENCIONADOS. 4.4 A CLASSE NAO INVESTIRA EM WARR | regulamento 779778 p. 13 [agronegócio]: EVENTUALMENTE COMPOR A CARTEIRA DA CLASSE IMOVEIS (OU DIREITOS REAIS RELACIONADOS), PARTICIPACOES SOCIETARIAS, COTAS DE FUNDOS DE INVESTIMENTO, BENS MOVEIS E M GERAL, PRODUTOS OU INSUMOS AGRICOLAS, DIREITOS DISPONIVEIS, DENTRE OUTROS ATIVOS, BENS OU DIREITOS QUE NAO OS DIREITOS CREDITORIOS OU OS ATIVOS FINANCEIROS (“ ATIVOS RECUPERADOS”), EM DECORRENCIA, EXCLUSIVAMENTE, DOS PROCEDIMENTOS JUDICIAIS OU EXTRAJUDICI AIS ENVOLVIDOS NA RECUPERACAO DOS DIREITOS CREDITORIOS INADIMPLIDOS, SEJA POR FORCA DE: (I) EXPROPRI</x:v>
       </x:c>
       <x:c r="AI98" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=52327260000170</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=45207707000101</x:v>
       </x:c>
       <x:c r="AJ98" s="24" t="str">
-        <x:v>1179906</x:v>
+        <x:v>Regulamento id 779778</x:v>
       </x:c>
       <x:c r="AK98" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL98" s="24" t="str">
-        <x:v>p. 36 — política/definição do lastro</x:v>
+        <x:v>regulamento 779778 p. 7; regulamento 779778 p. 1, regulamento 779778 p. 10, regulamento 779778 p. 13</x:v>
       </x:c>
       <x:c r="AM98" s="24" t="str">
         <x:v>N/D</x:v>
@@ -12611,22 +12628,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D99" s="39" t="n">
-        <x:v>31739396000117</x:v>
+        <x:v>65839682000176</x:v>
       </x:c>
       <x:c r="E99" s="23" t="str">
-        <x:v>31.739.396/0001-17</x:v>
+        <x:v>65.839.682/0001-76</x:v>
       </x:c>
       <x:c r="F99" s="23" t="str">
-        <x:v>LF III FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DE RESPONSABILIDADE LIMITADA</x:v>
+        <x:v>FUNDO DE INVESTIMENTOS EM DIREITOS CREDITÓRIOS PICPAY FGTS II DE RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G99" s="45" t="n">
-        <x:v>1385981646.72</x:v>
+        <x:v>1472677074.3</x:v>
       </x:c>
       <x:c r="H99" s="51" t="n">
-        <x:v>0.0016874196644014277</x:v>
+        <x:v>0.0017440420226569778</x:v>
       </x:c>
       <x:c r="I99" s="51" t="n">
-        <x:v>0.0800310134462825</x:v>
+        <x:v>0.1141825541295485</x:v>
       </x:c>
       <x:c r="J99" s="51" t="str">
         <x:v>N/D</x:v>
@@ -12665,55 +12682,55 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="V99" s="23" t="str">
-        <x:v>Listo IP</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="W99" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X99" s="23" t="str">
-        <x:v>Risco Bancos Emissores Diversos</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y99" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z99" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AA99" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB99" s="23" t="str">
-        <x:v>Recebíveis Comerciais</x:v>
+        <x:v>Multicarteira Financeiro</x:v>
       </x:c>
       <x:c r="AC99" s="23" t="str">
-        <x:v>Meios de Pagamento e Cartões</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD99" s="23" t="str">
-        <x:v>Arranjos de pagamento/adquirência</x:v>
-      </x:c>
-      <x:c r="AE99" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE99" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF99" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG99" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH99" s="23" t="str">
-        <x:v>ANSACOES DE PAGAMENTO NECESSARIAS AO RECEBIMENTO PELOS ESTABELECIMENTOS CREDENCIADOS OU O DIREITO AO RECEBIMENTO DESSES RECURSOS PARA O CUMPRIMENTO DESSA MESMA FINALIDADE, COMO OS DIREITOS CREDITORIOS, NAO PODEM SER OBJETO DE CESSAO DE DIREITOS CREDITORIOS NEM SER DADOS EM GARANTIA, EXCETO SE O PRODUTO DA CESSAO DOS CREDITOS OU DA OPERACAO GARANTIDA FOR DESTINADO PARA CUMPRIR AS OBRIGACOES DE LIQUIDACAO ENTRE OS PARTICIPANTES DOS ARRANJOS DE PAGAMENTO REFERENTES AS TRANSACOES DE PAGAMENTO ATE O RECEBIMENTO PELOS ESTABELECIMENTOS CREDENCIADOS, OU PARA ASSEGURAR O CUMPRIMENTO DESSAS OBRIGACOES, CONFORME AS REGRAS DOS ARRANJO DE PAGAMENTO. AINDA NAO EXISTE JURISPRUDENCIA DOS TRIBUNAIS BRASILEIROS SOBRE A APLICACAO DA REFERIDA NORMA, DE MODO QUE, C ASO A CESSAO DE DIREITOS CREDITORIOS CEDIDOS PELA CEDENTE AO FUNDO VENHA A SER QUESTIONADA JUDICIALMENTE, A AQUISICAO DE DIREITOS CREDITORIOS CEDIDOS PELO FUNDO PODERA SER ANULADA OU SE TORNAR INEFICAZ, GERANDO PERDAS AO</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI99" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=31739396000117</x:v>
+        <x:v>equivalência metodológica a partir do segmento CVM</x:v>
       </x:c>
       <x:c r="AJ99" s="23" t="str">
-        <x:v>1146939</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK99" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL99" s="23" t="str">
-        <x:v>p. 59 — política/definição do lastro</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM99" s="23" t="str">
         <x:v>N/D</x:v>
@@ -12722,7 +12739,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO99" s="23" t="str">
-        <x:v>documentado — parte ou lastro identificado</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="36" customHeight="1">
@@ -12745,10 +12762,10 @@
         <x:v>BLC FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
       </x:c>
       <x:c r="G100" s="44" t="n">
-        <x:v>1385172155.96</x:v>
+        <x:v>1465748408.7</x:v>
       </x:c>
       <x:c r="H100" s="50" t="n">
-        <x:v>0.0016864341169882942</x:v>
+        <x:v>0.0017358366365759312</x:v>
       </x:c>
       <x:c r="I100" s="50" t="n">
         <x:v>0</x:v>
@@ -12861,22 +12878,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D101" s="39" t="n">
-        <x:v>45207707000101</x:v>
+        <x:v>57833038000162</x:v>
       </x:c>
       <x:c r="E101" s="23" t="str">
-        <x:v>45.207.707/0001-01</x:v>
+        <x:v>57.833.038/0001-62</x:v>
       </x:c>
       <x:c r="F101" s="23" t="str">
-        <x:v>LASSIE EDUCATION CRÉDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>ALDEBARAN II FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G101" s="45" t="n">
-        <x:v>1380228129.74</x:v>
+        <x:v>1457599019.29</x:v>
       </x:c>
       <x:c r="H101" s="51" t="n">
-        <x:v>0.0016804148114046397</x:v>
+        <x:v>0.0017261855882652949</x:v>
       </x:c>
       <x:c r="I101" s="51" t="n">
-        <x:v>0.4149784846743287</x:v>
+        <x:v>0.0490927291065483</x:v>
       </x:c>
       <x:c r="J101" s="51" t="str">
         <x:v>N/D</x:v>
@@ -12921,49 +12938,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X101" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
       </x:c>
       <x:c r="Y101" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="Z101" s="23" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AA101" s="23" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AB101" s="23" t="str">
-        <x:v>Recuperação</x:v>
+        <x:v>Fomento Mercantil</x:v>
       </x:c>
       <x:c r="AC101" s="23" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>Crédito PJ</x:v>
       </x:c>
       <x:c r="AD101" s="23" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
-      </x:c>
-      <x:c r="AE101" s="27" t="b">
-        <x:v>0</x:v>
+        <x:v>Recebíveis comerciais/multissetorial</x:v>
+      </x:c>
+      <x:c r="AE101" s="23" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF101" s="23" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>Indício de crédito corporativo; porte N/D</x:v>
       </x:c>
       <x:c r="AG101" s="23" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
       </x:c>
       <x:c r="AH101" s="23" t="str">
-        <x:v>regulamento 779778 p. 7 [classificação ANBIMA declarada no regulamento]: ER A SER DELIBERADO PELOS COTISTAS REUNIDOS EM ASSEMBLEIA ESPECIAL DE COTISTAS. CLASSIFICACAO ANBIMA TIPO “OUTROS”. FOCO DE ATUACAO “PODER PUBLICO”. OBJETIVO O OBJETIVO DA CLASSE E PROPORCIONAR RENDIMENTO DE LONGO PRAZO AS SUAS COTAS POR MEIO DO INVESTIMENTO DA PARCELA PREPONDERANTE DE SEUS RECURSOS NA AQUISICAO DE DIREITOS CREDITORIOS (CONFORME DISPOSTO NO CAPITULO 4 DESTE ANEXO). O OBJETIVO DA CL || regulamento 779778 p. 1 [direitos judiciais privados]: REGULAMENTO LASSIE EDUCATION CREDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS BTG PACTUAL SAC: 0800 772 28 27 - OUVIDORIA: 0800 722 00 48 - BTGPACTUAL.COM 1 PARTE GERAL CAPITULO 1 FUNDO 1.1 LASSIE EDUC ATION CREDITOS JUDICIAIS FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS (“FUNDO”), INSCRITO NO CNPJ SOB O N° 45.207.707/0001-01, REGIDO PELA LEI NO 10 | regulamento 779778 p. 10 [precatórios e requisitórios contra entes públicos]: COM SENTENCA TRANSITADA EM JULGADO OU NAO, PROLATADAS OU QUE SERAO PROLATADAS NO CURSO DE ACOES JUDICIAIS CONTRA OS ENTES FEDERATIVOS, CUJOS CREDITOS PODERAO SER REPRESENTADOS POR PRECATORIOS JA EMITIDOS OU A SEREM EMITIDOS EM VIRTUDE DE EXECU CAO DAS SENTENCAS RESPECTIVAS, QUE PODERAO PREVER, CONFORME SUA ORIGEM E NATUREZA, INCIDENCIA DE JUROS E CORRECAO MONETARIA; E/OU (II) DIREITOS RELATIVOS A HONORARIOS ADVOCATICIOS RELACIONADOS AOS CREDITOS ANTERIORMENTE MENCIONADOS. 4.4 A CLASSE NAO INVESTIRA EM WARR | regulamento 779778 p. 13 [agronegócio]: EVENTUALMENTE COMPOR A CARTEIRA DA CLASSE IMOVEIS (OU DIREITOS REAIS RELACIONADOS), PARTICIPACOES SOCIETARIAS, COTAS DE FUNDOS DE INVESTIMENTO, BENS MOVEIS E M GERAL, PRODUTOS OU INSUMOS AGRICOLAS, DIREITOS DISPONIVEIS, DENTRE OUTROS ATIVOS, BENS OU DIREITOS QUE NAO OS DIREITOS CREDITORIOS OU OS ATIVOS FINANCEIROS (“ ATIVOS RECUPERADOS”), EM DECORRENCIA, EXCLUSIVAMENTE, DOS PROCEDIMENTOS JUDICIAIS OU EXTRAJUDICI AIS ENVOLVIDOS NA RECUPERACAO DOS DIREITOS CREDITORIOS INADIMPLIDOS, SEJA POR FORCA DE: (I) EXPROPRI</x:v>
+        <x:v>A POLITICA DE EXERCICIO DE DIREITO DE VOTO DA GESTORA ESTA DISPONIVEL NA PAGINA DA GESTORA NA REDE MUNDIAL DE COMPUTADORES , NO SEGUINTE ENDERECO: HTTPS://WWW.EMERALD.COM.BR/ 11. DIREITOS CREDITORIOS CARACTERISTICAS DOS DIREITOS CREDITORIOS 11.1. OS DIREITOS CREDITORIOS A SEREM ADQUIRIDOS PELO FUNDO SERAO DECORRENTES DE OPERACOES REALIZADAS NOS SEGMENTOS MERCANTIL, COMERCIAL E FINANCEIRO, REPRESENTADOS POR (A) DIREITOS E TITULOS DE CREDITO, TAIS COMO, MAS NAO SE LIMITANDO DUPLICATAS, CHEQUES, NOTAS PROMISSORIAS, CEDULAS DE CREDITO BANCARIO (CCB), RECEBIVEIS DE CARTAO DE CREDITO, CEDULAS DE PRODUTOR RURAL FINANCEIRAS, CEDULAS DE CREDITO IMOBILIARIO, PARCELAS DE EMPRESTIMOS CONSIGNADOS, NOTAS COMERCIAIS (NC), NOTAS DE CREDITO DE EXPORTACAO (NCE) OU INSTRUMENTOS CONTRATUAIS DECORRENTES DE OPERACAO DE CREDITO; (B) VALORES MOBILIARIOS REPRESENTATIVOS DE CREDITO; (C) CERTIFICADOS DE RECEBIVEIS E OUTROS VALORES MOBILIARIOS REPRESENTATIVOS DE OPERACOES DE SECURITIZACAO, QUE NAO SEJAM LASTREADOS EM DI</x:v>
       </x:c>
       <x:c r="AI101" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=45207707000101</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=57833038000162</x:v>
       </x:c>
       <x:c r="AJ101" s="23" t="str">
-        <x:v>Regulamento id 779778</x:v>
+        <x:v>1231073</x:v>
       </x:c>
       <x:c r="AK101" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL101" s="23" t="str">
-        <x:v>regulamento 779778 p. 7; regulamento 779778 p. 1, regulamento 779778 p. 10, regulamento 779778 p. 13</x:v>
+        <x:v>p. 29 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM101" s="23" t="str">
         <x:v>N/D</x:v>
@@ -12986,22 +13003,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D102" s="38" t="n">
-        <x:v>47669805000196</x:v>
+        <x:v>52327260000170</x:v>
       </x:c>
       <x:c r="E102" s="24" t="str">
-        <x:v>47.669.805/0001-96</x:v>
+        <x:v>52.327.260/0001-70</x:v>
       </x:c>
       <x:c r="F102" s="24" t="str">
-        <x:v>GONN FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS</x:v>
+        <x:v>IFOOD I FIDC SEGMENTO MEIOS DE PAGAMENTO DE RESPONSABILIDADA</x:v>
       </x:c>
       <x:c r="G102" s="44" t="n">
-        <x:v>1370830378.37</x:v>
+        <x:v>1455000054.14</x:v>
       </x:c>
       <x:c r="H102" s="50" t="n">
-        <x:v>0.001668973137194579</x:v>
+        <x:v>0.0017231077210830578</x:v>
       </x:c>
       <x:c r="I102" s="50" t="n">
-        <x:v>0.7645925252609076</x:v>
+        <x:v>0.1712974829590509</x:v>
       </x:c>
       <x:c r="J102" s="50" t="str">
         <x:v>N/D</x:v>
@@ -13046,49 +13063,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
       </x:c>
       <x:c r="Y102" s="24" t="str">
-        <x:v>Financeiro</x:v>
+        <x:v>Agro, Indústria e Comércio</x:v>
       </x:c>
       <x:c r="Z102" s="24" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Recebíveis Comerciais</x:v>
       </x:c>
       <x:c r="AA102" s="24" t="str">
         <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB102" s="24" t="str">
-        <x:v>Crédito Pessoal</x:v>
+        <x:v>Adquirência</x:v>
       </x:c>
       <x:c r="AC102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Meios de Pagamento e Cartões</x:v>
       </x:c>
       <x:c r="AD102" s="24" t="str">
-        <x:v>N/D</x:v>
-      </x:c>
-      <x:c r="AE102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Arranjos de pagamento/adquirência</x:v>
+      </x:c>
+      <x:c r="AE102" s="26" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF102" s="24" t="str">
-        <x:v>N/D — dados insuficientes</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG102" s="24" t="str">
-        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>OBSERVADOS OS CRITERIOS DE COMPOSICAO E DIVERSIFICACAO DA CARTEIRA DO FUNDO, CONFORME ESTABELECIDOS NESTE REGULAMENTO. 4.2. ORIGEM DOS DIREITOS CREDITORIOS . O FUNDO ADQUIRIRA (A) DIREITOS CREDITORIOS CARTOES E DIREITOS CREDITORIOS OUTROS, QUE SAO ORIUNDOS DO PAGAMENTO DEVIDO PELO DEVEDOR AOS CEDENTES DECORRENTES DE TRANSACOES DE PAGAMENTO REALIZADAS POR CLIENTES DOS PARCEIROS, A VISTA OU PARCELADAS, NO AMBITO DO RESPECTIVO ARRANJO DE PAGAMENTO, E (B) DIREITOS CREDITORIOS CONTA DIGITAL, QUE SAO ORIUNDOS DOS DIREITOS CREDITORIOS A PERFORMAR DETIDOS PELOS PARCEIROS EM FACE DO PROVEDOR DE DOCUSIGN ENVELOPE ID: EA3E46E7-E426-401E-A595-139E0C2E9BCF</x:v>
       </x:c>
       <x:c r="AI102" s="24" t="str">
-        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=52327260000170</x:v>
       </x:c>
       <x:c r="AJ102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>1179906</x:v>
       </x:c>
       <x:c r="AK102" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>p. 36 — política/definição do lastro</x:v>
       </x:c>
       <x:c r="AM102" s="24" t="str">
         <x:v>N/D</x:v>
@@ -13097,7 +13114,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO102" s="24" t="str">
-        <x:v>N/D</x:v>
+        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="36" customHeight="1">
@@ -13111,22 +13128,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D103" s="39" t="n">
-        <x:v>62681110000113</x:v>
+        <x:v>39669950000149</x:v>
       </x:c>
       <x:c r="E103" s="23" t="str">
-        <x:v>62.681.110/0001-13</x:v>
+        <x:v>39.669.950/0001-49</x:v>
       </x:c>
       <x:c r="F103" s="23" t="str">
-        <x:v>ÁSIA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS</x:v>
+        <x:v>FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS SOMACRED BACH - RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G103" s="45" t="n">
-        <x:v>1337788554.49</x:v>
+        <x:v>1453818390.53</x:v>
       </x:c>
       <x:c r="H103" s="51" t="n">
-        <x:v>0.0016287450263139274</x:v>
+        <x:v>0.0017217083165371125</x:v>
       </x:c>
       <x:c r="I103" s="51" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1498724384837788</x:v>
       </x:c>
       <x:c r="J103" s="51" t="str">
         <x:v>N/D</x:v>
@@ -13171,7 +13188,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X103" s="23" t="str">
-        <x:v>Crédito privado/mercado de capitais</x:v>
+        <x:v>Consignado/INSS</x:v>
       </x:c>
       <x:c r="Y103" s="23" t="str">
         <x:v>Outros</x:v>
@@ -13180,40 +13197,40 @@
         <x:v>Multicarteira Outros</x:v>
       </x:c>
       <x:c r="AA103" s="23" t="str">
-        <x:v>Agro, Indústria e Comércio</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB103" s="23" t="str">
-        <x:v>Crédito Corporativo</x:v>
+        <x:v>Crédito Consignado</x:v>
       </x:c>
       <x:c r="AC103" s="23" t="str">
-        <x:v>Crédito PJ</x:v>
+        <x:v>Crédito PF</x:v>
       </x:c>
       <x:c r="AD103" s="23" t="str">
-        <x:v>Crédito privado/mercado de capitais</x:v>
-      </x:c>
-      <x:c r="AE103" s="23" t="str">
-        <x:v>N/D</x:v>
+        <x:v>Consignado/INSS</x:v>
+      </x:c>
+      <x:c r="AE103" s="27" t="b">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AF103" s="23" t="str">
-        <x:v>Indício de crédito corporativo; porte N/D</x:v>
+        <x:v>Sem indício documental de Middle Market</x:v>
       </x:c>
       <x:c r="AG103" s="23" t="str">
-        <x:v>O lastro é compatível com crédito corporativo tradicional, mas a base não documenta o porte do tomador.</x:v>
+        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
       </x:c>
       <x:c r="AH103" s="23" t="str">
-        <x:v>Informe Mensal Estruturado 2026-06: segmento Financeiro = 100% da carteira de direitos creditórios reportada à CVM. regulamento 1023671 p. 53 [créditos inadimplidos / NPL]: OU A REALIZACAO DOS DIREITOS DE CREDITO PODERA SER ADVERSAMENTE AFETADA, PREJUDICANDO O DESEMPENHO DA CLASSE. 17.1.17. RISCO DE COBRANCA . O INSUCESSO NA COBRANCA DOS DIREITOS DE CREDITO INADIMPLIDOS PODERA ACARRETAR PERDAS PARA A CLASSE E SEUS COTISTAS. 17.1.18. RISCO REFERENTE A VERIFICACAO DO LASTRO POR AMOSTRAGEM. O GESTOR REALIZARA AUDITORIA PERIODICA, POR AMOSTRAGEM, NOS DIREITOS DE CREDITO, DE FORMA A VERIFICAR A REGULARIDADE DOS DOCUMENTOS COMPROBATORIOS E DA TRANSFERENCIA REALIZADA, CONFORME PROCEDIMENTOS | regulamento 1023671 p. 54 [receitas e dívidas do poder público]: OS CEDENTES, QUANDO DA FORMALIZACAO DA TRANSFERENCIA DE CREDITOS, SENDO SUJEITOS PASSIVOS POR DEBITO PARA COM A FAZ ENDA PUBLICA, POR CREDITO TRIBUTARIO REGULARMENTE INSCRITO COMO DIVIDA ATIVA, NAO DISPUSEREM DE BENS PARA TOTAL PAGAMENTO DA DIVIDA FISCAL. OUTROS RISCOS 17.1.20. RISCOS E CUSTOS DE COBRANCA. OS CUSTOS INCORRIDOS COM OS PROCEDIMENTOS JUDICIAIS OU EXTRAJUDICIAIS NECESSARIOS A COBRANCA E A SALVAGUARDA DOS DIREITOS DA CLASSE SOBRE OS DIREITOS DE CREDITO E DOS ATIVOS FINANCEIROS INTEGRANTES DA CAR | regulamento 1023671 p. 32 [crédito corporativo / mercado de capitais]: ITOS CREDITORIOS LIMITE MAXIMO DO PATRIMONIO LIQUIDO DUPLICATA DIGITAL MERCANTIL OU DE SERVICOS: CONTRATO DIGITAL OU FISICO; E DIREITOS CREDITORIOS REPRESENTADOS POR CCBS, CRI S E NOTAS COMERCIAIS MAIOR QUE 50% DO PATRIMONIO LIQUIDO COTAS DE FUNDOS DE INVESTIMENTO DO ITEM "V"; PARAGRAFO 2.12 MENOR DE 33% DO PATRIMONIO LIQUIDO || CEDENTE/ORIGINADOR: regulamento 1023671 p. 34: CEDENTE SERA RESPONSAVEL POR DAR CIENCIA AS RESPECTIVAS DEVEDORAS ACERCA DA CESSAO DOS DIREITOS DE CREDITO AO FUNDO, NOS TERMOS DO ARTIGO 290 DO CODIGO CIVIL, FICANDO O AGENTE O GESTOR RESPONSA</x:v>
+        <x:v>regulamento 1238679 p. 37 [crédito consignado]: PAGINA 46 DE 209 DE ATUACAO “CREDITO CONSIGNADO”. PARAGRAFO NONO O PRESENTE ANEXO DESCRITIVO CONSTITUI PARTE INTEGRANTE DO REGULAMENTO, BEM COMO SERA POR ELE SERA REGIDO, DEVENDO PREVALECER AS DISPOSICOES DO ANEXO DESCRITIVO EM CASO DE QUALQUER CONFLITO OU CONTROVERSIA EM RELACAO AS DISPOSICOES DA PARTE GERAL DO REGULAMENTO. ARTIGO 2O OS TERMOS E EXPRESSOES INICIAD || CEDENTE/ORIGINADOR: regulamento 1238679 p. 9: CEDENTE E SUAS RESPECTIVAS PARTES RELACIONADAS, TAL COMO DEFINIDO PELAS REGRAS CONTABEIS QUE TRATAM DESTE ASSUNTO, EXCETO CONFORME PREVISAO DOS §§ 3O E 4O DO ARTIGO 32 DO ANEXO NORMATIVO II</x:v>
       </x:c>
       <x:c r="AI103" s="23" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=62681110000113</x:v>
+        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=39669950000149</x:v>
       </x:c>
       <x:c r="AJ103" s="23" t="str">
-        <x:v>1023671</x:v>
+        <x:v>Regulamento id 1238679</x:v>
       </x:c>
       <x:c r="AK103" s="23" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL103" s="23" t="str">
-        <x:v>regulamento 1023671 p. 53, regulamento 1023671 p. 54, regulamento 1023671 p. 32</x:v>
+        <x:v>regulamento 1238679 p. 37</x:v>
       </x:c>
       <x:c r="AM103" s="23" t="str">
         <x:v>N/D</x:v>
@@ -13236,22 +13253,22 @@
         <x:v>Top 100 por PL ex-FIC</x:v>
       </x:c>
       <x:c r="D104" s="38" t="n">
-        <x:v>41240321000140</x:v>
+        <x:v>47669805000196</x:v>
       </x:c>
       <x:c r="E104" s="24" t="str">
-        <x:v>41.240.321/0001-40</x:v>
+        <x:v>47.669.805/0001-96</x:v>
       </x:c>
       <x:c r="F104" s="24" t="str">
-        <x:v>LAGUZ I FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS NÃO-PADRONIZADOS</x:v>
+        <x:v>GONN FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS</x:v>
       </x:c>
       <x:c r="G104" s="44" t="n">
-        <x:v>1302594039.08</x:v>
+        <x:v>1443190109.93</x:v>
       </x:c>
       <x:c r="H104" s="50" t="n">
-        <x:v>0.001585896033672172</x:v>
+        <x:v>0.0017091216006042932</x:v>
       </x:c>
       <x:c r="I104" s="50" t="n">
-        <x:v>0</x:v>
+        <x:v>0.7773601887411222</x:v>
       </x:c>
       <x:c r="J104" s="50" t="str">
         <x:v>N/D</x:v>
@@ -13296,49 +13313,49 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="X104" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="Y104" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="Z104" s="24" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AA104" s="24" t="str">
-        <x:v>Outros</x:v>
+        <x:v>Financeiro</x:v>
       </x:c>
       <x:c r="AB104" s="24" t="str">
-        <x:v>Poder Público</x:v>
+        <x:v>Crédito Pessoal</x:v>
       </x:c>
       <x:c r="AC104" s="24" t="str">
-        <x:v>Judicial/Precatórios/NPL</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AD104" s="24" t="str">
-        <x:v>Precatórios/direitos judiciais</x:v>
-      </x:c>
-      <x:c r="AE104" s="26" t="b">
-        <x:v>0</x:v>
+        <x:v>N/D</x:v>
+      </x:c>
+      <x:c r="AE104" s="24" t="str">
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AF104" s="24" t="str">
-        <x:v>Sem indício documental de Middle Market</x:v>
+        <x:v>N/D — dados insuficientes</x:v>
       </x:c>
       <x:c r="AG104" s="24" t="str">
-        <x:v>A evidência disponível aponta outro tipo de risco ou não traz crédito corporativo.</x:v>
+        <x:v>Cedente, sacado e tipo de recebível não foram localizados.</x:v>
       </x:c>
       <x:c r="AH104" s="24" t="str">
-        <x:v>regulamento 1168358 p. 18 [classificação ANBIMA declarada no regulamento]: O E/OU NA CLASSE. TIPO DE CONDOMINIO: FECHADO. PRAZO DE DURACAO: INDETERMINADO. CLASSIFICACAO ANBIMA: PARA OS FINS DE CLASSIFICACAO ANBIMA, ESTA CLASSE E CLASSIFICADA COMO UM FUNDO DE INVESTIMENTO EM DIREITOS CREDITORIOS DO TIPO ANBIMA “OUTROS – PODER PUBLICO”. OBJETIVO: E OBJETIVO DA CLASSE PROPORCIONAR AOS COTISTAS A VALORIZACAO DE SUAS COTAS, POR MEIO DA APLICACAO DOS RECURSOS DA CLASSE NA AQUISI || regulamento 1168358 p. 22 [precatórios e requisitórios contra entes públicos]: ACAO DO RESPECTIVO CEDENTE. 3.2.2. OBSERVADO O DISPOSTO NO PRESENTE ANEXO, A CLASSE PODERA ADQUIRIR DO(S) CEDENTE(S) DIREITOS CREDITORIOS, TOTAL OU PARCIALMENTE: I –ORIGINARIOS DE PRECATORIOS OU AINDA CREDITOS DECORRENTES DE RECEITAS OU DIVIDAS PUBLICAS ORIGINARIAS OU DERIVADAS DA UNIAO, ESTADOS, DISTRITO FEDERAL E MUNICIPIOS, AUTARQUIAS E FUNDACOES. II - QUE ESTEJAM VENCIDOS E PENDENTES DE PAGAMENTO QUANDO DE SUA CESSAO PARA A CLASSE; III – QUE RESULTEM DE ACOES JUDICIAIS OU PROCEDIMENTOS ARBITRAIS EM CUR</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AI104" s="24" t="str">
-        <x:v>https://fnet.bmfbovespa.com.br/fnet/publico/abrirGerenciadorDocumentosCVM?cnpjFundo=41240321000140</x:v>
+        <x:v>ANBIMA Data — Fundos 175: características público</x:v>
       </x:c>
       <x:c r="AJ104" s="24" t="str">
-        <x:v>1168358</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AK104" s="24" t="str">
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AL104" s="24" t="str">
-        <x:v>regulamento 1168358 p. 18; regulamento 1168358 p. 22</x:v>
+        <x:v>N/D</x:v>
       </x:c>
       <x:c r="AM104" s="24" t="str">
         <x:v>N/D</x:v>
@@ -13347,7 +13364,7 @@
         <x:v>N/D</x:v>
       </x:c>
       <x:c r="AO104" s="24" t="str">
-        <x:v>taxonomia disponível — partes e lastro documental N/D</x:v>
+        <x:v>N/D</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="36" customHeight="1">
@@ -13355,7 +13372,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="33" t="n">
-        <x:v>134</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C105" s="23" t="str">
         <x:v>Inclusão adicional · emissão encerrada em 2026</x:v>
@@ -13370,13 +13387,13 @@
         <x:v>CLASSE ÚNICA FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS AGRO CITI-BAYER RESPONSABILIDADE LIMITADA</x:v>
       </x:c>
       <x:c r="G105" s="45" t="n">
-        <x:v>1021572769.62</x:v>
+        <x:v>790811150.71</x:v>
       </x:c>
       <x:c r="H105" s="51" t="n">
-        <x:v>0.001243755272050921</x:v>
+        <x:v>0.0009365310989712611</x:v>
       </x:c>
       <x:c r="I105" s="51" t="n">
-        <x:v>0.1562191402092739</x:v>
+        <x:v>0.2027501641420936</x:v>
       </x:c>
       <x:c r="J105" s="51" t="str">
         <x:v>N/D</x:v>
@@ -13480,7 +13497,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="32" t="n">
-        <x:v>2324</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="C106" s="24" t="str">
         <x:v>Inclusão adicional · emissão encerrada em 2026</x:v>
@@ -13495,10 +13512,10 @@
         <x:v>LAVORO FORNECEDORES FUNDO DE INVESTIMENTO EM DIREITOS CREDITÓRIOS DO AGRONEGÓCIO - RESP LTDA</x:v>
       </x:c>
       <x:c r="G106" s="44" t="n">
-        <x:v>20713043.47</x:v>
+        <x:v>19475122.44</x:v>
       </x:c>
       <x:c r="H106" s="50" t="n">
-        <x:v>0.000025217936286237562</x:v>
+        <x:v>0.00002306373374345799</x:v>
       </x:c>
       <x:c r="I106" s="50" t="n">
         <x:v>1</x:v>

--- a/data/industry_study/generated_revision/top100_fidcs_middle_market.xlsx
+++ b/data/industry_study/generated_revision/top100_fidcs_middle_market.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="R94c6953f19e74020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 100 FIDCs" sheetId="2" r:id="R7fb71cc8fb0a461f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="1" r:id="R264c4324ac4d4d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 100 FIDCs" sheetId="2" r:id="Rf8e2aecf45c2441f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -890,7 +890,7 @@
         <x:v>58815322507.62</x:v>
       </x:c>
       <x:c r="H5" s="49" t="n">
-        <x:v>0.06965301206862962</x:v>
+        <x:v>0.06965277452767916</x:v>
       </x:c>
       <x:c r="I5" s="49" t="n">
         <x:v>0.0012711173696075</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>33455157284.84</x:v>
       </x:c>
       <x:c r="H6" s="50" t="n">
-        <x:v>0.03961981971308513</x:v>
+        <x:v>0.03961968459574631</x:v>
       </x:c>
       <x:c r="I6" s="50" t="n">
         <x:v>1</x:v>
@@ -1140,7 +1140,7 @@
         <x:v>20198291907.77</x:v>
       </x:c>
       <x:c r="H7" s="51" t="n">
-        <x:v>0.023920159067993482</x:v>
+        <x:v>0.023920077491947432</x:v>
       </x:c>
       <x:c r="I7" s="51" t="n">
         <x:v>0</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>10699481597.570002</x:v>
       </x:c>
       <x:c r="H8" s="50" t="n">
-        <x:v>0.012671036884088674</x:v>
+        <x:v>0.012670993671454283</x:v>
       </x:c>
       <x:c r="I8" s="50" t="n">
         <x:v>0.0326072904035432</x:v>
@@ -1390,7 +1390,7 @@
         <x:v>10070614364.8</x:v>
       </x:c>
       <x:c r="H9" s="51" t="n">
-        <x:v>0.011926290530822998</x:v>
+        <x:v>0.011926249858032202</x:v>
       </x:c>
       <x:c r="I9" s="51" t="n">
         <x:v>0.1603537622701268</x:v>
@@ -1515,7 +1515,7 @@
         <x:v>8932735715.03</x:v>
       </x:c>
       <x:c r="H10" s="50" t="n">
-        <x:v>0.010578739043456804</x:v>
+        <x:v>0.010578702966284369</x:v>
       </x:c>
       <x:c r="I10" s="50" t="n">
         <x:v>0</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>8239227134.05</x:v>
       </x:c>
       <x:c r="H11" s="51" t="n">
-        <x:v>0.009757440111457582</x:v>
+        <x:v>0.009757406835199609</x:v>
       </x:c>
       <x:c r="I11" s="51" t="n">
         <x:v>0</x:v>
@@ -1765,7 +1765,7 @@
         <x:v>7959831126.05</x:v>
       </x:c>
       <x:c r="H12" s="50" t="n">
-        <x:v>0.009426560798254298</x:v>
+        <x:v>0.009426528650409645</x:v>
       </x:c>
       <x:c r="I12" s="50" t="n">
         <x:v>0.1110477241038992</x:v>
@@ -1890,7 +1890,7 @@
         <x:v>7174237038.23</x:v>
       </x:c>
       <x:c r="H13" s="51" t="n">
-        <x:v>0.008496208091731584</x:v>
+        <x:v>0.008496179116712622</x:v>
       </x:c>
       <x:c r="I13" s="51" t="n">
         <x:v>0.7364651414444897</x:v>
@@ -2015,7 +2015,7 @@
         <x:v>6705565454.97</x:v>
       </x:c>
       <x:c r="H14" s="50" t="n">
-        <x:v>0.007941176068557636</x:v>
+        <x:v>0.007941148986390548</x:v>
       </x:c>
       <x:c r="I14" s="50" t="n">
         <x:v>0.84310494226191</x:v>
@@ -2140,7 +2140,7 @@
         <x:v>6476101048.84</x:v>
       </x:c>
       <x:c r="H15" s="51" t="n">
-        <x:v>0.007669429075290311</x:v>
+        <x:v>0.007669402919874803</x:v>
       </x:c>
       <x:c r="I15" s="51" t="n">
         <x:v>1</x:v>
@@ -2265,7 +2265,7 @@
         <x:v>6460522602.03</x:v>
       </x:c>
       <x:c r="H16" s="50" t="n">
-        <x:v>0.007650980043687587</x:v>
+        <x:v>0.007650953951189681</x:v>
       </x:c>
       <x:c r="I16" s="50" t="n">
         <x:v>1</x:v>
@@ -2390,7 +2390,7 @@
         <x:v>6390290390.09</x:v>
       </x:c>
       <x:c r="H17" s="51" t="n">
-        <x:v>0.007567806392718836</x:v>
+        <x:v>0.007567780583871952</x:v>
       </x:c>
       <x:c r="I17" s="51" t="n">
         <x:v>0</x:v>
@@ -2515,7 +2515,7 @@
         <x:v>6111960853.79</x:v>
       </x:c>
       <x:c r="H18" s="50" t="n">
-        <x:v>0.007238190066149372</x:v>
+        <x:v>0.007238165381408586</x:v>
       </x:c>
       <x:c r="I18" s="50" t="n">
         <x:v>0</x:v>
@@ -2640,7 +2640,7 @@
         <x:v>5933688515.09</x:v>
       </x:c>
       <x:c r="H19" s="51" t="n">
-        <x:v>0.0070270681198680235</x:v>
+        <x:v>0.007027044155126363</x:v>
       </x:c>
       <x:c r="I19" s="51" t="n">
         <x:v>0</x:v>
@@ -2765,7 +2765,7 @@
         <x:v>4985976955.36</x:v>
       </x:c>
       <x:c r="H20" s="50" t="n">
-        <x:v>0.005904725133499101</x:v>
+        <x:v>0.005904704996336633</x:v>
       </x:c>
       <x:c r="I20" s="50" t="n">
         <x:v>1</x:v>
@@ -2890,7 +2890,7 @@
         <x:v>4670319122.88</x:v>
       </x:c>
       <x:c r="H21" s="51" t="n">
-        <x:v>0.005530902158840782</x:v>
+        <x:v>0.005530883296544427</x:v>
       </x:c>
       <x:c r="I21" s="51" t="n">
         <x:v>0.1272759196611239</x:v>
@@ -3015,7 +3015,7 @@
         <x:v>4584487367.37</x:v>
       </x:c>
       <x:c r="H22" s="50" t="n">
-        <x:v>0.005429254492084638</x:v>
+        <x:v>0.005429235976442112</x:v>
       </x:c>
       <x:c r="I22" s="50" t="n">
         <x:v>0</x:v>
@@ -3140,7 +3140,7 @@
         <x:v>4231296076.69</x:v>
       </x:c>
       <x:c r="H23" s="51" t="n">
-        <x:v>0.0050109819028442805</x:v>
+        <x:v>0.005010964813656483</x:v>
       </x:c>
       <x:c r="I23" s="51" t="n">
         <x:v>1</x:v>
@@ -3265,7 +3265,7 @@
         <x:v>3772944315.34</x:v>
       </x:c>
       <x:c r="H24" s="50" t="n">
-        <x:v>0.004468171298331265</x:v>
+        <x:v>0.0044681560603160595</x:v>
       </x:c>
       <x:c r="I24" s="50" t="n">
         <x:v>0.7056380854286087</x:v>
@@ -3390,7 +3390,7 @@
         <x:v>3771058923.75</x:v>
       </x:c>
       <x:c r="H25" s="51" t="n">
-        <x:v>0.004465938492362117</x:v>
+        <x:v>0.004465923261961555</x:v>
       </x:c>
       <x:c r="I25" s="51" t="n">
         <x:v>0.0303918848813086</x:v>
@@ -3515,7 +3515,7 @@
         <x:v>3765650088.95</x:v>
       </x:c>
       <x:c r="H26" s="50" t="n">
-        <x:v>0.0044595329908781655</x:v>
+        <x:v>0.0044595177823225874</x:v>
       </x:c>
       <x:c r="I26" s="50" t="n">
         <x:v>1</x:v>
@@ -3640,7 +3640,7 @@
         <x:v>3686239660.81</x:v>
       </x:c>
       <x:c r="H27" s="51" t="n">
-        <x:v>0.0043654898865681645</x:v>
+        <x:v>0.004365474998732218</x:v>
       </x:c>
       <x:c r="I27" s="51" t="n">
         <x:v>0</x:v>
@@ -3765,7 +3765,7 @@
         <x:v>3658919018.85</x:v>
       </x:c>
       <x:c r="H28" s="50" t="n">
-        <x:v>0.0043331349674241605</x:v>
+        <x:v>0.00433312018992972</x:v>
       </x:c>
       <x:c r="I28" s="50" t="n">
         <x:v>0</x:v>
@@ -3890,7 +3890,7 @@
         <x:v>3599560973.43</x:v>
       </x:c>
       <x:c r="H29" s="51" t="n">
-        <x:v>0.004262839226829116</x:v>
+        <x:v>0.004262824689067553</x:v>
       </x:c>
       <x:c r="I29" s="51" t="n">
         <x:v>1</x:v>
@@ -4015,7 +4015,7 @@
         <x:v>3389462172.19</x:v>
       </x:c>
       <x:c r="H30" s="50" t="n">
-        <x:v>0.004014026269347188</x:v>
+        <x:v>0.004014012580124183</x:v>
       </x:c>
       <x:c r="I30" s="50" t="n">
         <x:v>0.0534980276932435</x:v>
@@ -4140,7 +4140,7 @@
         <x:v>3371226156.53</x:v>
       </x:c>
       <x:c r="H31" s="51" t="n">
-        <x:v>0.003992429968167592</x:v>
+        <x:v>0.0039924163525954705</x:v>
       </x:c>
       <x:c r="I31" s="51" t="n">
         <x:v>0</x:v>
@@ -4265,7 +4265,7 @@
         <x:v>3334605706.65</x:v>
       </x:c>
       <x:c r="H32" s="50" t="n">
-        <x:v>0.003949061598690066</x:v>
+        <x:v>0.003949048131019139</x:v>
       </x:c>
       <x:c r="I32" s="50" t="n">
         <x:v>0.4811159979432757</x:v>
@@ -4390,7 +4390,7 @@
         <x:v>3311135945.94</x:v>
       </x:c>
       <x:c r="H33" s="51" t="n">
-        <x:v>0.003921267148939838</x:v>
+        <x:v>0.003921253776057634</x:v>
       </x:c>
       <x:c r="I33" s="51" t="n">
         <x:v>0.7289331396097506</x:v>
@@ -4515,7 +4515,7 @@
         <x:v>3256435200.06</x:v>
       </x:c>
       <x:c r="H34" s="50" t="n">
-        <x:v>0.0038564868918486853</x:v>
+        <x:v>0.0038564737398896457</x:v>
       </x:c>
       <x:c r="I34" s="50" t="n">
         <x:v>0.1617789634703957</x:v>
@@ -4640,7 +4640,7 @@
         <x:v>3196029095.69</x:v>
       </x:c>
       <x:c r="H35" s="51" t="n">
-        <x:v>0.0037849499702215465</x:v>
+        <x:v>0.003784937062228243</x:v>
       </x:c>
       <x:c r="I35" s="51" t="n">
         <x:v>0</x:v>
@@ -4765,7 +4765,7 @@
         <x:v>3141061787.79</x:v>
       </x:c>
       <x:c r="H36" s="50" t="n">
-        <x:v>0.0037198540326783534</x:v>
+        <x:v>0.0037198413466847944</x:v>
       </x:c>
       <x:c r="I36" s="50" t="n">
         <x:v>1</x:v>
@@ -4890,7 +4890,7 @@
         <x:v>3100556826.01</x:v>
       </x:c>
       <x:c r="H37" s="51" t="n">
-        <x:v>0.003671885366157207</x:v>
+        <x:v>0.0036718728437534526</x:v>
       </x:c>
       <x:c r="I37" s="51" t="n">
         <x:v>0.1896520557500736</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>3091810070.76</x:v>
       </x:c>
       <x:c r="H38" s="50" t="n">
-        <x:v>0.0036615268775352892</x:v>
+        <x:v>0.0036615143904575767</x:v>
       </x:c>
       <x:c r="I38" s="50" t="n">
         <x:v>0</x:v>
@@ -5140,7 +5140,7 @@
         <x:v>3058103926.17</x:v>
       </x:c>
       <x:c r="H39" s="51" t="n">
-        <x:v>0.00362160982198212</x:v>
+        <x:v>0.003621597471035423</x:v>
       </x:c>
       <x:c r="I39" s="51" t="n">
         <x:v>0</x:v>
@@ -5265,7 +5265,7 @@
         <x:v>3000510455.02</x:v>
       </x:c>
       <x:c r="H40" s="50" t="n">
-        <x:v>0.003553403807459875</x:v>
+        <x:v>0.0035533916891193652</x:v>
       </x:c>
       <x:c r="I40" s="50" t="n">
         <x:v>0</x:v>
@@ -5390,7 +5390,7 @@
         <x:v>2966345679.42</x:v>
       </x:c>
       <x:c r="H41" s="51" t="n">
-        <x:v>0.003512943610597391</x:v>
+        <x:v>0.0035129316302401977</x:v>
       </x:c>
       <x:c r="I41" s="51" t="n">
         <x:v>0.1524969562841521</x:v>
@@ -5515,7 +5515,7 @@
         <x:v>2940889060.03</x:v>
       </x:c>
       <x:c r="H42" s="50" t="n">
-        <x:v>0.003482796190809487</x:v>
+        <x:v>0.0034827843132654605</x:v>
       </x:c>
       <x:c r="I42" s="50" t="n">
         <x:v>0</x:v>
@@ -5640,7 +5640,7 @@
         <x:v>2758097886.13</x:v>
       </x:c>
       <x:c r="H43" s="51" t="n">
-        <x:v>0.0032663227396939865</x:v>
+        <x:v>0.0032663116003995747</x:v>
       </x:c>
       <x:c r="I43" s="51" t="n">
         <x:v>1</x:v>
@@ -5765,7 +5765,7 @@
         <x:v>2703044510.17</x:v>
       </x:c>
       <x:c r="H44" s="50" t="n">
-        <x:v>0.003201124874636562</x:v>
+        <x:v>0.003201113957689503</x:v>
       </x:c>
       <x:c r="I44" s="50" t="n">
         <x:v>0.1623408260106682</x:v>
@@ -5890,7 +5890,7 @@
         <x:v>2661374071.86</x:v>
       </x:c>
       <x:c r="H45" s="51" t="n">
-        <x:v>0.003151775973384929</x:v>
+        <x:v>0.0031517652247347538</x:v>
       </x:c>
       <x:c r="I45" s="51" t="n">
         <x:v>0.6957359372662582</x:v>
@@ -6015,7 +6015,7 @@
         <x:v>2641955191.86</x:v>
       </x:c>
       <x:c r="H46" s="50" t="n">
-        <x:v>0.003128778845675155</x:v>
+        <x:v>0.003128768175453169</x:v>
       </x:c>
       <x:c r="I46" s="50" t="n">
         <x:v>0.3493155766177357</x:v>
@@ -6140,7 +6140,7 @@
         <x:v>2579461850.15</x:v>
       </x:c>
       <x:c r="H47" s="51" t="n">
-        <x:v>0.0030547700789329223</x:v>
+        <x:v>0.003054759661106522</x:v>
       </x:c>
       <x:c r="I47" s="51" t="n">
         <x:v>0.4829575505614513</x:v>
@@ -6265,7 +6265,7 @@
         <x:v>2575168330.09</x:v>
       </x:c>
       <x:c r="H48" s="50" t="n">
-        <x:v>0.003049685407255447</x:v>
+        <x:v>0.0030496750067695423</x:v>
       </x:c>
       <x:c r="I48" s="50" t="n">
         <x:v>0.0876860137103579</x:v>
@@ -6390,7 +6390,7 @@
         <x:v>2567223636.65</x:v>
       </x:c>
       <x:c r="H49" s="51" t="n">
-        <x:v>0.0030402767735106234</x:v>
+        <x:v>0.0030402664051114255</x:v>
       </x:c>
       <x:c r="I49" s="51" t="n">
         <x:v>1</x:v>
@@ -6515,7 +6515,7 @@
         <x:v>2543457792.98</x:v>
       </x:c>
       <x:c r="H50" s="50" t="n">
-        <x:v>0.0030121316826501043</x:v>
+        <x:v>0.003012121410235437</x:v>
       </x:c>
       <x:c r="I50" s="50" t="n">
         <x:v>0.0760103608607955</x:v>
@@ -6640,7 +6640,7 @@
         <x:v>2539517617.4</x:v>
       </x:c>
       <x:c r="H51" s="51" t="n">
-        <x:v>0.003007465464978839</x:v>
+        <x:v>0.0030074552084775933</x:v>
       </x:c>
       <x:c r="I51" s="51" t="n">
         <x:v>0</x:v>
@@ -6765,7 +6765,7 @@
         <x:v>2531012852.93</x:v>
       </x:c>
       <x:c r="H52" s="50" t="n">
-        <x:v>0.002997393557914263</x:v>
+        <x:v>0.002997383335761717</x:v>
       </x:c>
       <x:c r="I52" s="50" t="n">
         <x:v>0</x:v>
@@ -6890,7 +6890,7 @@
         <x:v>2498979874.47</x:v>
       </x:c>
       <x:c r="H53" s="51" t="n">
-        <x:v>0.00295945797684218</x:v>
+        <x:v>0.0029594478840631344</x:v>
       </x:c>
       <x:c r="I53" s="51" t="n">
         <x:v>0.2593848573902249</x:v>
@@ -7015,7 +7015,7 @@
         <x:v>2464338064.69</x:v>
       </x:c>
       <x:c r="H54" s="50" t="n">
-        <x:v>0.0029184328444139276</x:v>
+        <x:v>0.002918422891544825</x:v>
       </x:c>
       <x:c r="I54" s="50" t="n">
         <x:v>0.180905841005734</x:v>
@@ -7140,7 +7140,7 @@
         <x:v>2420168048.15</x:v>
       </x:c>
       <x:c r="H55" s="51" t="n">
-        <x:v>0.002866123776573084</x:v>
+        <x:v>0.0028661140020960615</x:v>
       </x:c>
       <x:c r="I55" s="51" t="n">
         <x:v>0</x:v>
@@ -7265,7 +7265,7 @@
         <x:v>2402205778.31</x:v>
       </x:c>
       <x:c r="H56" s="50" t="n">
-        <x:v>0.0028448516633787133</x:v>
+        <x:v>0.002844841961446981</x:v>
       </x:c>
       <x:c r="I56" s="50" t="n">
         <x:v>0.0864587494545391</x:v>
@@ -7390,7 +7390,7 @@
         <x:v>2373894609.18</x:v>
       </x:c>
       <x:c r="H57" s="51" t="n">
-        <x:v>0.0028113236961583785</x:v>
+        <x:v>0.0028113141085686533</x:v>
       </x:c>
       <x:c r="I57" s="51" t="n">
         <x:v>0.1527059368171675</x:v>
@@ -7515,7 +7515,7 @@
         <x:v>2373588339.88</x:v>
       </x:c>
       <x:c r="H58" s="50" t="n">
-        <x:v>0.002810960991707572</x:v>
+        <x:v>0.0028109514053547948</x:v>
       </x:c>
       <x:c r="I58" s="50" t="n">
         <x:v>1</x:v>
@@ -7640,7 +7640,7 @@
         <x:v>2234066329.65</x:v>
       </x:c>
       <x:c r="H59" s="51" t="n">
-        <x:v>0.0026457297586197893</x:v>
+        <x:v>0.0026457207357628754</x:v>
       </x:c>
       <x:c r="I59" s="51" t="n">
         <x:v>0.1327136681119272</x:v>
@@ -7765,7 +7765,7 @@
         <x:v>2220692700.39</x:v>
       </x:c>
       <x:c r="H60" s="50" t="n">
-        <x:v>0.0026298918184278013</x:v>
+        <x:v>0.0026298828495837615</x:v>
       </x:c>
       <x:c r="I60" s="50" t="n">
         <x:v>0</x:v>
@@ -7890,7 +7890,7 @@
         <x:v>2207595143.13</x:v>
       </x:c>
       <x:c r="H61" s="51" t="n">
-        <x:v>0.002614380821037927</x:v>
+        <x:v>0.0026143719050917722</x:v>
       </x:c>
       <x:c r="I61" s="51" t="n">
         <x:v>0</x:v>
@@ -8015,7 +8015,7 @@
         <x:v>2162550453.27</x:v>
       </x:c>
       <x:c r="H62" s="50" t="n">
-        <x:v>0.002561035906946199</x:v>
+        <x:v>0.0025610271729247197</x:v>
       </x:c>
       <x:c r="I62" s="50" t="n">
         <x:v>0.4168932745358105</x:v>
@@ -8140,7 +8140,7 @@
         <x:v>2125721812.65</x:v>
       </x:c>
       <x:c r="H63" s="51" t="n">
-        <x:v>0.002517420984164066</x:v>
+        <x:v>0.002517412398884614</x:v>
       </x:c>
       <x:c r="I63" s="51" t="n">
         <x:v>0.1507558774200163</x:v>
@@ -8265,7 +8265,7 @@
         <x:v>2090403784.62</x:v>
       </x:c>
       <x:c r="H64" s="50" t="n">
-        <x:v>0.0024755950291623727</x:v>
+        <x:v>0.0024755865865239467</x:v>
       </x:c>
       <x:c r="I64" s="50" t="n">
         <x:v>0.4527500152326454</x:v>
@@ -8390,7 +8390,7 @@
         <x:v>2082486408.15</x:v>
       </x:c>
       <x:c r="H65" s="51" t="n">
-        <x:v>0.0024662187459881142</x:v>
+        <x:v>0.0024662103353260685</x:v>
       </x:c>
       <x:c r="I65" s="51" t="n">
         <x:v>0</x:v>
@@ -8515,7 +8515,7 @@
         <x:v>2045856427.66</x:v>
       </x:c>
       <x:c r="H66" s="50" t="n">
-        <x:v>0.0024228390897290996</x:v>
+        <x:v>0.002422830827006741</x:v>
       </x:c>
       <x:c r="I66" s="50" t="n">
         <x:v>0.0393499895555923</x:v>
@@ -8640,7 +8640,7 @@
         <x:v>2040649598.42</x:v>
       </x:c>
       <x:c r="H67" s="51" t="n">
-        <x:v>0.0024166728166487125</x:v>
+        <x:v>0.0024166645749554854</x:v>
       </x:c>
       <x:c r="I67" s="51" t="n">
         <x:v>0</x:v>
@@ -8765,7 +8765,7 @@
         <x:v>2040580910.81</x:v>
       </x:c>
       <x:c r="H68" s="50" t="n">
-        <x:v>0.0024165914722179705</x:v>
+        <x:v>0.002416583230802156</x:v>
       </x:c>
       <x:c r="I68" s="50" t="n">
         <x:v>0</x:v>
@@ -8890,7 +8890,7 @@
         <x:v>1999981369.56</x:v>
       </x:c>
       <x:c r="H69" s="51" t="n">
-        <x:v>0.0023685107984054497</x:v>
+        <x:v>0.002368502720961424</x:v>
       </x:c>
       <x:c r="I69" s="51" t="n">
         <x:v>0.0930889101736938</x:v>
@@ -9015,7 +9015,7 @@
         <x:v>1960417320.47</x:v>
       </x:c>
       <x:c r="H70" s="50" t="n">
-        <x:v>0.0023216564231974828</x:v>
+        <x:v>0.002321648505543141</x:v>
       </x:c>
       <x:c r="I70" s="50" t="n">
         <x:v>0</x:v>
@@ -9140,7 +9140,7 @@
         <x:v>1944596528.21</x:v>
       </x:c>
       <x:c r="H71" s="51" t="n">
-        <x:v>0.002302920390013642</x:v>
+        <x:v>0.0023029125362556777</x:v>
       </x:c>
       <x:c r="I71" s="51" t="n">
         <x:v>1</x:v>
@@ -9265,7 +9265,7 @@
         <x:v>1927443335.68</x:v>
       </x:c>
       <x:c r="H72" s="50" t="n">
-        <x:v>0.0022826064399175117</x:v>
+        <x:v>0.0022825986554371688</x:v>
       </x:c>
       <x:c r="I72" s="50" t="n">
         <x:v>0</x:v>
@@ -9390,7 +9390,7 @@
         <x:v>1925682597.46</x:v>
       </x:c>
       <x:c r="H73" s="51" t="n">
-        <x:v>0.002280521256749954</x:v>
+        <x:v>0.0022805134793808094</x:v>
       </x:c>
       <x:c r="I73" s="51" t="n">
         <x:v>0.1027449904369085</x:v>
@@ -9515,7 +9515,7 @@
         <x:v>1925498329.61</x:v>
       </x:c>
       <x:c r="H74" s="50" t="n">
-        <x:v>0.0022803030345209035</x:v>
+        <x:v>0.002280295257895973</x:v>
       </x:c>
       <x:c r="I74" s="50" t="n">
         <x:v>0.1153248886507287</x:v>
@@ -9640,7 +9640,7 @@
         <x:v>1924331624.55</x:v>
       </x:c>
       <x:c r="H75" s="51" t="n">
-        <x:v>0.0022789213448835785</x:v>
+        <x:v>0.002278913572970689</x:v>
       </x:c>
       <x:c r="I75" s="51" t="n">
         <x:v>0.3851477559871331</x:v>
@@ -9765,7 +9765,7 @@
         <x:v>1919387163.23</x:v>
       </x:c>
       <x:c r="H76" s="50" t="n">
-        <x:v>0.0022730657853233943</x:v>
+        <x:v>0.0022730580333799955</x:v>
       </x:c>
       <x:c r="I76" s="50" t="n">
         <x:v>1</x:v>
@@ -9890,7 +9890,7 @@
         <x:v>1911439961.8</x:v>
       </x:c>
       <x:c r="H77" s="51" t="n">
-        <x:v>0.002263654181450204</x:v>
+        <x:v>0.0022636464616036423</x:v>
       </x:c>
       <x:c r="I77" s="51" t="n">
         <x:v>0.3289671657228036</x:v>
@@ -10015,7 +10015,7 @@
         <x:v>1911426358.03</x:v>
       </x:c>
       <x:c r="H78" s="50" t="n">
-        <x:v>0.0022636380709620597</x:v>
+        <x:v>0.0022636303511704395</x:v>
       </x:c>
       <x:c r="I78" s="50" t="n">
         <x:v>0.4739448173839156</x:v>
@@ -10140,7 +10140,7 @@
         <x:v>1897667543.94</x:v>
       </x:c>
       <x:c r="H79" s="51" t="n">
-        <x:v>0.0022473439693062093</x:v>
+        <x:v>0.0022473363050831323</x:v>
       </x:c>
       <x:c r="I79" s="51" t="n">
         <x:v>0.8815886150370092</x:v>
@@ -10265,7 +10265,7 @@
         <x:v>1866969812.56</x:v>
       </x:c>
       <x:c r="H80" s="50" t="n">
-        <x:v>0.002210989676527934</x:v>
+        <x:v>0.0022109821362856154</x:v>
       </x:c>
       <x:c r="I80" s="50" t="n">
         <x:v>0</x:v>
@@ -10390,7 +10390,7 @@
         <x:v>1855894253.21</x:v>
       </x:c>
       <x:c r="H81" s="51" t="n">
-        <x:v>0.002197873263386232</x:v>
+        <x:v>0.0021978657678754358</x:v>
       </x:c>
       <x:c r="I81" s="51" t="n">
         <x:v>0.1873702924545502</x:v>
@@ -10515,7 +10515,7 @@
         <x:v>1847170248.89</x:v>
       </x:c>
       <x:c r="H82" s="50" t="n">
-        <x:v>0.0021875417179269855</x:v>
+        <x:v>0.0021875342576503456</x:v>
       </x:c>
       <x:c r="I82" s="50" t="n">
         <x:v>0.3460699773697318</x:v>
@@ -10640,7 +10640,7 @@
         <x:v>1800909934.43</x:v>
       </x:c>
       <x:c r="H83" s="51" t="n">
-        <x:v>0.0021327571804288952</x:v>
+        <x:v>0.002132749906986546</x:v>
       </x:c>
       <x:c r="I83" s="51" t="n">
         <x:v>0</x:v>
@@ -10765,7 +10765,7 @@
         <x:v>1755240553.43</x:v>
       </x:c>
       <x:c r="H84" s="50" t="n">
-        <x:v>0.0020786724655903815</x:v>
+        <x:v>0.0020786653765956847</x:v>
       </x:c>
       <x:c r="I84" s="50" t="n">
         <x:v>0</x:v>
@@ -10890,7 +10890,7 @@
         <x:v>1737053741.97</x:v>
       </x:c>
       <x:c r="H85" s="51" t="n">
-        <x:v>0.002057134435293104</x:v>
+        <x:v>0.002057127419750567</x:v>
       </x:c>
       <x:c r="I85" s="51" t="n">
         <x:v>1</x:v>
@@ -11015,7 +11015,7 @@
         <x:v>1717939470.45</x:v>
       </x:c>
       <x:c r="H86" s="50" t="n">
-        <x:v>0.0020344980451807632</x:v>
+        <x:v>0.0020344911068361747</x:v>
       </x:c>
       <x:c r="I86" s="50" t="n">
         <x:v>0</x:v>
@@ -11140,7 +11140,7 @@
         <x:v>1717932634.87</x:v>
       </x:c>
       <x:c r="H87" s="51" t="n">
-        <x:v>0.0020344899500328332</x:v>
+        <x:v>0.002034483011715852</x:v>
       </x:c>
       <x:c r="I87" s="51" t="n">
         <x:v>0.1505283858312573</x:v>
@@ -11265,7 +11265,7 @@
         <x:v>1695951362.31</x:v>
       </x:c>
       <x:c r="H88" s="50" t="n">
-        <x:v>0.0020084582668314505</x:v>
+        <x:v>0.0020084514172915456</x:v>
       </x:c>
       <x:c r="I88" s="50" t="n">
         <x:v>0.7583035475960594</x:v>
@@ -11390,7 +11390,7 @@
         <x:v>1626299680.36</x:v>
       </x:c>
       <x:c r="H89" s="51" t="n">
-        <x:v>0.0019259721180419891</x:v>
+        <x:v>0.0019259655498084858</x:v>
       </x:c>
       <x:c r="I89" s="51" t="n">
         <x:v>0.4183096467682989</x:v>
@@ -11515,7 +11515,7 @@
         <x:v>1596122150.92</x:v>
       </x:c>
       <x:c r="H90" s="50" t="n">
-        <x:v>0.001890233882958548</x:v>
+        <x:v>0.0018902274366048323</x:v>
       </x:c>
       <x:c r="I90" s="50" t="n">
         <x:v>0.7492493155245668</x:v>
@@ -11640,10 +11640,10 @@
         <x:v>1572064332.62</x:v>
       </x:c>
       <x:c r="H91" s="51" t="n">
-        <x:v>0.001861743016345044</x:v>
+        <x:v>0.001861736667155074</x:v>
       </x:c>
       <x:c r="I91" s="51" t="n">
-        <x:v>0.2179779669744</x:v>
+        <x:v>0.2032424948441643</x:v>
       </x:c>
       <x:c r="J91" s="51" t="str">
         <x:v>N/D</x:v>
@@ -11765,7 +11765,7 @@
         <x:v>1565448244.56</x:v>
       </x:c>
       <x:c r="H92" s="50" t="n">
-        <x:v>0.0018539078053516744</x:v>
+        <x:v>0.0018539014828824936</x:v>
       </x:c>
       <x:c r="I92" s="50" t="n">
         <x:v>0.2103059766797605</x:v>
@@ -11890,7 +11890,7 @@
         <x:v>1550515087.47</x:v>
       </x:c>
       <x:c r="H93" s="51" t="n">
-        <x:v>0.0018362229687025554</x:v>
+        <x:v>0.0018362167065448067</x:v>
       </x:c>
       <x:c r="I93" s="51" t="n">
         <x:v>0.2164128724195619</x:v>
@@ -12015,7 +12015,7 @@
         <x:v>1544332585.59</x:v>
       </x:c>
       <x:c r="H94" s="50" t="n">
-        <x:v>0.0018289012392670638</x:v>
+        <x:v>0.0018288950020789543</x:v>
       </x:c>
       <x:c r="I94" s="50" t="n">
         <x:v>0.2072216817801345</x:v>
@@ -12140,7 +12140,7 @@
         <x:v>1514334849.03</x:v>
       </x:c>
       <x:c r="H95" s="51" t="n">
-        <x:v>0.0017933759268559221</x:v>
+        <x:v>0.00179336981082146</x:v>
       </x:c>
       <x:c r="I95" s="51" t="n">
         <x:v>0.217904449537328</x:v>
@@ -12265,7 +12265,7 @@
         <x:v>1502648710.95</x:v>
       </x:c>
       <x:c r="H96" s="50" t="n">
-        <x:v>0.0017795364258208568</x:v>
+        <x:v>0.0017795303569838976</x:v>
       </x:c>
       <x:c r="I96" s="50" t="n">
         <x:v>0.150078915375806</x:v>
@@ -12390,7 +12390,7 @@
         <x:v>1498192276.83</x:v>
       </x:c>
       <x:c r="H97" s="51" t="n">
-        <x:v>0.0017742588204910008</x:v>
+        <x:v>0.0017742527696525078</x:v>
       </x:c>
       <x:c r="I97" s="51" t="n">
         <x:v>0</x:v>
@@ -12515,7 +12515,7 @@
         <x:v>1487482332.28</x:v>
       </x:c>
       <x:c r="H98" s="50" t="n">
-        <x:v>0.0017615753926835812</x:v>
+        <x:v>0.0017615693850999798</x:v>
       </x:c>
       <x:c r="I98" s="50" t="n">
         <x:v>0.4359813410538953</x:v>
@@ -12640,7 +12640,7 @@
         <x:v>1472677074.3</x:v>
       </x:c>
       <x:c r="H99" s="51" t="n">
-        <x:v>0.0017440420226569778</x:v>
+        <x:v>0.0017440360748682548</x:v>
       </x:c>
       <x:c r="I99" s="51" t="n">
         <x:v>0.1141825541295485</x:v>
@@ -12765,7 +12765,7 @@
         <x:v>1465748408.7</x:v>
       </x:c>
       <x:c r="H100" s="50" t="n">
-        <x:v>0.0017358366365759312</x:v>
+        <x:v>0.001735830716770423</x:v>
       </x:c>
       <x:c r="I100" s="50" t="n">
         <x:v>0</x:v>
@@ -12890,7 +12890,7 @@
         <x:v>1457599019.29</x:v>
       </x:c>
       <x:c r="H101" s="51" t="n">
-        <x:v>0.0017261855882652949</x:v>
+        <x:v>0.0017261797013732117</x:v>
       </x:c>
       <x:c r="I101" s="51" t="n">
         <x:v>0.0490927291065483</x:v>
@@ -13015,7 +13015,7 @@
         <x:v>1455000054.14</x:v>
       </x:c>
       <x:c r="H102" s="50" t="n">
-        <x:v>0.0017231077210830578</x:v>
+        <x:v>0.0017231018446875704</x:v>
       </x:c>
       <x:c r="I102" s="50" t="n">
         <x:v>0.1712974829590509</x:v>
@@ -13140,7 +13140,7 @@
         <x:v>1453818390.53</x:v>
       </x:c>
       <x:c r="H103" s="51" t="n">
-        <x:v>0.0017217083165371125</x:v>
+        <x:v>0.0017217024449140803</x:v>
       </x:c>
       <x:c r="I103" s="51" t="n">
         <x:v>0.1498724384837788</x:v>
@@ -13265,7 +13265,7 @@
         <x:v>1443190109.93</x:v>
       </x:c>
       <x:c r="H104" s="50" t="n">
-        <x:v>0.0017091216006042932</x:v>
+        <x:v>0.0017091157719063316</x:v>
       </x:c>
       <x:c r="I104" s="50" t="n">
         <x:v>0.7773601887411222</x:v>
@@ -13390,7 +13390,7 @@
         <x:v>790811150.71</x:v>
       </x:c>
       <x:c r="H105" s="51" t="n">
-        <x:v>0.0009365310989712611</x:v>
+        <x:v>0.0009365279050751068</x:v>
       </x:c>
       <x:c r="I105" s="51" t="n">
         <x:v>0.2027501641420936</x:v>
@@ -13515,7 +13515,7 @@
         <x:v>19475122.44</x:v>
       </x:c>
       <x:c r="H106" s="50" t="n">
-        <x:v>0.00002306373374345799</x:v>
+        <x:v>0.000023063655088119593</x:v>
       </x:c>
       <x:c r="I106" s="50" t="n">
         <x:v>1</x:v>
